--- a/assets/Listados/CRFK - 3415087 - 2026.xlsx
+++ b/assets/Listados/CRFK - 3415087 - 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Documents\Bot_sena_seguimiento\assets\Listados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{531F44D3-932B-463C-85CC-97AE4FC0BDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81382DF1-A789-42A8-80BB-23C5BA363C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ASISTENCIA " sheetId="1" r:id="rId1"/>
@@ -165,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="355">
   <si>
     <r>
       <rPr>
@@ -386,9 +386,6 @@
     <t>12 COMUNICACIÓN COMERCIAL Y MARKETING.</t>
   </si>
   <si>
-    <t>NO MATRICULADO</t>
-  </si>
-  <si>
     <t>ASIATE</t>
   </si>
   <si>
@@ -579,69 +576,6 @@
     <t>Teléfono de Acudiente</t>
   </si>
   <si>
-    <t>vale.abri2010@gmail.com</t>
-  </si>
-  <si>
-    <t>robert.f.senapaulaaguirre@gmail.com</t>
-  </si>
-  <si>
-    <t>robert.fsenaangelaalarcon@gmail.com</t>
-  </si>
-  <si>
-    <t>kevinalarconkfam@gmail.com</t>
-  </si>
-  <si>
-    <t>aaaxel.alarcon1017@gmail.com</t>
-  </si>
-  <si>
-    <t>robert.f.senayanisbustos@gmail.com</t>
-  </si>
-  <si>
-    <t>mariajimenacabezasrodriguez@gmail.com</t>
-  </si>
-  <si>
-    <t>julian2010gomez@gmail.com</t>
-  </si>
-  <si>
-    <t>robert.f.senajuancorrea@gmail.com</t>
-  </si>
-  <si>
-    <t>rober.f.senajeronimoescorcia@gmail.com</t>
-  </si>
-  <si>
-    <t>florianmafe49@gmail.com</t>
-  </si>
-  <si>
-    <t>axel.ajp4@gmail.com</t>
-  </si>
-  <si>
-    <t>soloxd825@gmail.com</t>
-  </si>
-  <si>
-    <t>matallanaacostaisaidavid@gmail.com</t>
-  </si>
-  <si>
-    <t>robert.f.senavalentinapachon@gmail.com</t>
-  </si>
-  <si>
-    <t>sofiaparada0909@gmail.com</t>
-  </si>
-  <si>
-    <t>perezcastrorut@gmail.com</t>
-  </si>
-  <si>
-    <t>santiagopicoguerrero23@gmail.com</t>
-  </si>
-  <si>
-    <t>dannapulgarin68@gmail.com</t>
-  </si>
-  <si>
-    <t>rfkfredtorres@gmail.com</t>
-  </si>
-  <si>
-    <t>robert.f.senalaurayara@gmail.com</t>
-  </si>
-  <si>
     <t xml:space="preserve">                                </t>
   </si>
   <si>
@@ -663,217 +597,25 @@
     <t>NOMBRE DEL GRUPO</t>
   </si>
   <si>
-    <t>Santiago</t>
-  </si>
-  <si>
-    <t>Pico Guerrero</t>
-  </si>
-  <si>
-    <t>Yanis Susana</t>
-  </si>
-  <si>
-    <t>Bustos Romero</t>
-  </si>
-  <si>
-    <t>Juan  Jose</t>
-  </si>
-  <si>
-    <t>Correa Tabares</t>
-  </si>
-  <si>
-    <t>Manuela</t>
-  </si>
-  <si>
-    <t>Silva Guevara</t>
-  </si>
-  <si>
-    <t>rober.f.sena.manuelasilva@gmail.com</t>
-  </si>
-  <si>
-    <t>Juan David</t>
-  </si>
-  <si>
-    <t>Lindarte Becerra</t>
-  </si>
-  <si>
-    <t>robertfsenadavidlinarte@gmail.com</t>
-  </si>
-  <si>
     <t xml:space="preserve">N° 2 </t>
-  </si>
-  <si>
-    <t>Maria Jimena</t>
-  </si>
-  <si>
-    <t>Cabezas Rodriguez</t>
-  </si>
-  <si>
-    <t>Laura Ximena</t>
-  </si>
-  <si>
-    <t>Yara Mazo</t>
-  </si>
-  <si>
-    <t>Angela Natalia</t>
-  </si>
-  <si>
-    <t>Alarcon Barrera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kevin Felipe </t>
-  </si>
-  <si>
-    <t>Alarcon Moreno</t>
   </si>
   <si>
     <t xml:space="preserve">N° 3 </t>
   </si>
   <si>
-    <t>Jeronimo</t>
-  </si>
-  <si>
-    <t>Escorcia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damian </t>
-  </si>
-  <si>
-    <t>Veracierta</t>
-  </si>
-  <si>
-    <t>damianveca302@gmail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pablo </t>
-  </si>
-  <si>
-    <t>Lucero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karla </t>
-  </si>
-  <si>
-    <t>Gil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julian </t>
-  </si>
-  <si>
-    <t>Casallas</t>
-  </si>
-  <si>
     <t xml:space="preserve">N° 4 </t>
-  </si>
-  <si>
-    <t>Axel Alejandro</t>
-  </si>
-  <si>
-    <t>Alarcon Torres</t>
-  </si>
-  <si>
-    <t>Jostin Estiven</t>
-  </si>
-  <si>
-    <t>Ocampo Camargo</t>
-  </si>
-  <si>
-    <t>camargoestiven@gmail.com</t>
-  </si>
-  <si>
-    <t>Sofia</t>
-  </si>
-  <si>
-    <t>Parada Garcia</t>
-  </si>
-  <si>
-    <t>Isai David</t>
-  </si>
-  <si>
-    <t>Matallana Acosta</t>
-  </si>
-  <si>
-    <t>Maria Fernanda</t>
-  </si>
-  <si>
-    <t>Florian Reyes</t>
   </si>
   <si>
     <t>N° 5</t>
   </si>
   <si>
-    <t>Felipe</t>
-  </si>
-  <si>
-    <t>Roncancio</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Rut</t>
-  </si>
-  <si>
-    <t>Perez Castro</t>
-  </si>
-  <si>
-    <t>Laura Camila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reina </t>
-  </si>
-  <si>
-    <t>laurareina12346@gmail,com</t>
-  </si>
-  <si>
-    <t>Alejandra</t>
-  </si>
-  <si>
-    <t>camejo</t>
-  </si>
-  <si>
-    <t>Danna</t>
-  </si>
-  <si>
-    <t>pulgarin</t>
-  </si>
-  <si>
     <t>N° 6</t>
-  </si>
-  <si>
-    <t>Paula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aguirre </t>
-  </si>
-  <si>
-    <t>Valentina</t>
-  </si>
-  <si>
-    <t>Pachon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jose </t>
-  </si>
-  <si>
-    <t>Urrego</t>
-  </si>
-  <si>
-    <t>Axel</t>
-  </si>
-  <si>
-    <t>Jamaica</t>
-  </si>
-  <si>
-    <t>Abril</t>
   </si>
   <si>
     <t>CARLOS ALBERTO SALCEDO DURAN</t>
   </si>
   <si>
     <t>csalcedo@sena.edu.co</t>
-  </si>
-  <si>
-    <t>Arciniegas Ávila Karoll Sofia</t>
   </si>
   <si>
     <t xml:space="preserve">Ariza Caicedo Edwin Vicente </t>
@@ -1437,6 +1179,228 @@
   <si>
     <t>Tipo de documento</t>
   </si>
+  <si>
+    <t>Karoll Sofia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arciniegas Ávila </t>
+  </si>
+  <si>
+    <t>María Fernanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cáceres Franco </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deiby Andrés </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joven Benavidez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rafael Eduardo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Díaz Devia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santiago </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pineda Diaz </t>
+  </si>
+  <si>
+    <t>Karen Dayana</t>
+  </si>
+  <si>
+    <t>Ballen Sáenz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karoll Sofia Arciniegas Ávila </t>
+  </si>
+  <si>
+    <t>Marina Valentina</t>
+  </si>
+  <si>
+    <t>Luengas Cantero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eduin Jesús </t>
+  </si>
+  <si>
+    <t>Molina Hernández</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>Ruiz Ripe</t>
+  </si>
+  <si>
+    <t>Juan Felipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedraza Páez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edwin Vicente </t>
+  </si>
+  <si>
+    <t>Ariza Caicedo</t>
+  </si>
+  <si>
+    <t>Cruz Garces</t>
+  </si>
+  <si>
+    <t>Luna Valentina</t>
+  </si>
+  <si>
+    <t>Ordoñez Martínez</t>
+  </si>
+  <si>
+    <t>Alan Shimon</t>
+  </si>
+  <si>
+    <t>Corredor Franco</t>
+  </si>
+  <si>
+    <t>Pablo Alejandro</t>
+  </si>
+  <si>
+    <t>Vargas Martínez</t>
+  </si>
+  <si>
+    <t>Julián Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bohórquez Sánchez </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laura Daniela </t>
+  </si>
+  <si>
+    <t>Gacharna Jiméne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Paola </t>
+  </si>
+  <si>
+    <t>Jaramillo Leguia</t>
+  </si>
+  <si>
+    <t>Antonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Felipe </t>
+  </si>
+  <si>
+    <t>Muñoz Soler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicolas </t>
+  </si>
+  <si>
+    <t>Cárdenas Camino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armando Elías </t>
+  </si>
+  <si>
+    <t>Zapata Medina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrea </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vélez Melo </t>
+  </si>
+  <si>
+    <t>Juan Manuel</t>
+  </si>
+  <si>
+    <t>Fino Ortega</t>
+  </si>
+  <si>
+    <t>Daniel Alejandro</t>
+  </si>
+  <si>
+    <t>Navarro Hurtado</t>
+  </si>
+  <si>
+    <t>Diana Milena</t>
+  </si>
+  <si>
+    <t>Navarro Villarruel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N° </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerónimo </t>
+  </si>
+  <si>
+    <t>Casallas Riaño</t>
+  </si>
+  <si>
+    <t>Tomás</t>
+  </si>
+  <si>
+    <t>Poveda Vega</t>
+  </si>
+  <si>
+    <t>Thomas Steven</t>
+  </si>
+  <si>
+    <t>Gómez Dueñas</t>
+  </si>
+  <si>
+    <t>Alejandra Isabella</t>
+  </si>
+  <si>
+    <t>Velandia Jiménez</t>
+  </si>
+  <si>
+    <t>Luisana Darianna</t>
+  </si>
+  <si>
+    <t>Diaz Artahona</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> María José</t>
+  </si>
+  <si>
+    <t>Parra Salazar</t>
+  </si>
+  <si>
+    <t>Juan Esteban</t>
+  </si>
+  <si>
+    <t>Pulido Gómez</t>
+  </si>
+  <si>
+    <t>Julián Josué</t>
+  </si>
+  <si>
+    <t>Montes Carrillo</t>
+  </si>
+  <si>
+    <t>Eudis Josué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molina Hernández </t>
+  </si>
+  <si>
+    <t>molinaeudis812@gmail.com}</t>
+  </si>
+  <si>
+    <t>María Luisa</t>
+  </si>
+  <si>
+    <t>Rodríguez Sotelo</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1-rW_UlDG94R3X7LZ8jMxB4AYYDRAgMYI</t>
+  </si>
 </sst>
 </file>
 
@@ -1447,7 +1411,7 @@
     <numFmt numFmtId="165" formatCode="d"/>
     <numFmt numFmtId="166" formatCode="ddd"/>
   </numFmts>
-  <fonts count="64">
+  <fonts count="65">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -1844,6 +1808,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="18">
     <fill>
@@ -1949,7 +1920,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="72">
+  <borders count="82">
     <border>
       <left/>
       <right/>
@@ -2818,12 +2789,154 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="207">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2995,9 +3108,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3071,6 +3182,37 @@
     </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="68" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="68" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="17" borderId="68" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="63" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="16" borderId="68" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="67" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="76" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="60" fillId="16" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="60" fillId="17" borderId="81" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3286,11 +3428,13 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="54" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="68" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4684,125 +4828,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:129" ht="24.75" customHeight="1">
-      <c r="A1" s="134"/>
-      <c r="B1" s="103"/>
-      <c r="C1" s="135" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="139" t="s">
+      <c r="A1" s="147"/>
+      <c r="B1" s="116"/>
+      <c r="C1" s="148" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="116"/>
+      <c r="G1" s="152" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="138"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="100"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="114"/>
-      <c r="V1" s="114"/>
-      <c r="W1" s="114"/>
-      <c r="X1" s="113"/>
-      <c r="Y1" s="114"/>
-      <c r="Z1" s="114"/>
-      <c r="AA1" s="114"/>
-      <c r="AB1" s="115"/>
-      <c r="AC1" s="114"/>
-      <c r="AD1" s="114"/>
-      <c r="AE1" s="114"/>
-      <c r="AF1" s="114"/>
-      <c r="AG1" s="114"/>
-      <c r="AH1" s="114"/>
-      <c r="AI1" s="114"/>
-      <c r="AJ1" s="114"/>
-      <c r="AK1" s="116"/>
-      <c r="AL1" s="166"/>
-      <c r="AM1" s="114"/>
-      <c r="AN1" s="114"/>
-      <c r="AO1" s="114"/>
-      <c r="AP1" s="114"/>
-      <c r="AQ1" s="114"/>
-      <c r="AR1" s="114"/>
-      <c r="AS1" s="114"/>
-      <c r="AT1" s="114"/>
-      <c r="AU1" s="167"/>
-      <c r="AV1" s="114"/>
-      <c r="AW1" s="114"/>
-      <c r="AX1" s="114"/>
-      <c r="AY1" s="114"/>
-      <c r="AZ1" s="114"/>
-      <c r="BA1" s="114"/>
-      <c r="BB1" s="114"/>
-      <c r="BC1" s="114"/>
-      <c r="BD1" s="114"/>
-      <c r="BE1" s="114"/>
-      <c r="BF1" s="114"/>
-      <c r="BG1" s="114"/>
-      <c r="BH1" s="114"/>
-      <c r="BI1" s="114"/>
-      <c r="BJ1" s="114"/>
-      <c r="BK1" s="114"/>
-      <c r="BL1" s="114"/>
-      <c r="BM1" s="114"/>
-      <c r="BN1" s="114"/>
-      <c r="BO1" s="114"/>
-      <c r="BP1" s="114"/>
-      <c r="BQ1" s="114"/>
-      <c r="BR1" s="114"/>
-      <c r="BS1" s="114"/>
-      <c r="BT1" s="114"/>
-      <c r="BU1" s="114"/>
-      <c r="BV1" s="168"/>
-      <c r="BW1" s="114"/>
-      <c r="BX1" s="114"/>
-      <c r="BY1" s="114"/>
-      <c r="BZ1" s="114"/>
-      <c r="CA1" s="114"/>
-      <c r="CB1" s="114"/>
-      <c r="CC1" s="114"/>
-      <c r="CD1" s="114"/>
-      <c r="CE1" s="114"/>
-      <c r="CF1" s="114"/>
-      <c r="CG1" s="114"/>
-      <c r="CH1" s="114"/>
-      <c r="CI1" s="114"/>
-      <c r="CJ1" s="114"/>
-      <c r="CK1" s="114"/>
-      <c r="CL1" s="114"/>
-      <c r="CM1" s="114"/>
-      <c r="CN1" s="114"/>
-      <c r="CO1" s="114"/>
-      <c r="CP1" s="114"/>
-      <c r="CQ1" s="114"/>
-      <c r="CR1" s="116"/>
-      <c r="CS1" s="170" t="s">
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="113"/>
+      <c r="T1" s="128"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="126"/>
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
+      <c r="AA1" s="127"/>
+      <c r="AB1" s="128"/>
+      <c r="AC1" s="127"/>
+      <c r="AD1" s="127"/>
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="127"/>
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
+      <c r="AK1" s="129"/>
+      <c r="AL1" s="179"/>
+      <c r="AM1" s="127"/>
+      <c r="AN1" s="127"/>
+      <c r="AO1" s="127"/>
+      <c r="AP1" s="127"/>
+      <c r="AQ1" s="127"/>
+      <c r="AR1" s="127"/>
+      <c r="AS1" s="127"/>
+      <c r="AT1" s="127"/>
+      <c r="AU1" s="180"/>
+      <c r="AV1" s="127"/>
+      <c r="AW1" s="127"/>
+      <c r="AX1" s="127"/>
+      <c r="AY1" s="127"/>
+      <c r="AZ1" s="127"/>
+      <c r="BA1" s="127"/>
+      <c r="BB1" s="127"/>
+      <c r="BC1" s="127"/>
+      <c r="BD1" s="127"/>
+      <c r="BE1" s="127"/>
+      <c r="BF1" s="127"/>
+      <c r="BG1" s="127"/>
+      <c r="BH1" s="127"/>
+      <c r="BI1" s="127"/>
+      <c r="BJ1" s="127"/>
+      <c r="BK1" s="127"/>
+      <c r="BL1" s="127"/>
+      <c r="BM1" s="127"/>
+      <c r="BN1" s="127"/>
+      <c r="BO1" s="127"/>
+      <c r="BP1" s="127"/>
+      <c r="BQ1" s="127"/>
+      <c r="BR1" s="127"/>
+      <c r="BS1" s="127"/>
+      <c r="BT1" s="127"/>
+      <c r="BU1" s="127"/>
+      <c r="BV1" s="181"/>
+      <c r="BW1" s="127"/>
+      <c r="BX1" s="127"/>
+      <c r="BY1" s="127"/>
+      <c r="BZ1" s="127"/>
+      <c r="CA1" s="127"/>
+      <c r="CB1" s="127"/>
+      <c r="CC1" s="127"/>
+      <c r="CD1" s="127"/>
+      <c r="CE1" s="127"/>
+      <c r="CF1" s="127"/>
+      <c r="CG1" s="127"/>
+      <c r="CH1" s="127"/>
+      <c r="CI1" s="127"/>
+      <c r="CJ1" s="127"/>
+      <c r="CK1" s="127"/>
+      <c r="CL1" s="127"/>
+      <c r="CM1" s="127"/>
+      <c r="CN1" s="127"/>
+      <c r="CO1" s="127"/>
+      <c r="CP1" s="127"/>
+      <c r="CQ1" s="127"/>
+      <c r="CR1" s="129"/>
+      <c r="CS1" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="CT1" s="171"/>
-      <c r="CU1" s="171"/>
-      <c r="CV1" s="171"/>
-      <c r="CW1" s="172"/>
+      <c r="CT1" s="184"/>
+      <c r="CU1" s="184"/>
+      <c r="CV1" s="184"/>
+      <c r="CW1" s="185"/>
       <c r="CX1" s="1"/>
-      <c r="CY1" s="160" t="s">
+      <c r="CY1" s="173" t="s">
         <v>3</v>
       </c>
-      <c r="CZ1" s="161"/>
-      <c r="DA1" s="161"/>
-      <c r="DB1" s="161"/>
-      <c r="DC1" s="161"/>
-      <c r="DD1" s="161"/>
-      <c r="DE1" s="161"/>
-      <c r="DF1" s="161"/>
-      <c r="DG1" s="161"/>
+      <c r="CZ1" s="174"/>
+      <c r="DA1" s="174"/>
+      <c r="DB1" s="174"/>
+      <c r="DC1" s="174"/>
+      <c r="DD1" s="174"/>
+      <c r="DE1" s="174"/>
+      <c r="DF1" s="174"/>
+      <c r="DG1" s="174"/>
       <c r="DH1" s="1"/>
       <c r="DI1" s="1"/>
       <c r="DJ1" s="1"/>
@@ -4821,122 +4965,122 @@
       <c r="DW1" s="1"/>
     </row>
     <row r="2" spans="1:129" ht="16.5">
-      <c r="A2" s="104"/>
-      <c r="B2" s="106"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="139" t="s">
+      <c r="A2" s="117"/>
+      <c r="B2" s="119"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="152" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="105"/>
-      <c r="R2" s="105"/>
-      <c r="S2" s="105"/>
-      <c r="T2" s="141"/>
-      <c r="U2" s="99"/>
-      <c r="V2" s="99"/>
-      <c r="W2" s="118"/>
-      <c r="X2" s="142"/>
-      <c r="Y2" s="99"/>
-      <c r="Z2" s="99"/>
-      <c r="AA2" s="99"/>
-      <c r="AB2" s="117"/>
-      <c r="AC2" s="99"/>
-      <c r="AD2" s="99"/>
-      <c r="AE2" s="99"/>
-      <c r="AF2" s="99"/>
-      <c r="AG2" s="99"/>
-      <c r="AH2" s="99"/>
-      <c r="AI2" s="99"/>
-      <c r="AJ2" s="99"/>
-      <c r="AK2" s="118"/>
-      <c r="AL2" s="142"/>
-      <c r="AM2" s="99"/>
-      <c r="AN2" s="99"/>
-      <c r="AO2" s="99"/>
-      <c r="AP2" s="99"/>
-      <c r="AQ2" s="99"/>
-      <c r="AR2" s="99"/>
-      <c r="AS2" s="99"/>
-      <c r="AT2" s="99"/>
-      <c r="AU2" s="141"/>
-      <c r="AV2" s="99"/>
-      <c r="AW2" s="99"/>
-      <c r="AX2" s="99"/>
-      <c r="AY2" s="99"/>
-      <c r="AZ2" s="99"/>
-      <c r="BA2" s="99"/>
-      <c r="BB2" s="99"/>
-      <c r="BC2" s="99"/>
-      <c r="BD2" s="99"/>
-      <c r="BE2" s="99"/>
-      <c r="BF2" s="99"/>
-      <c r="BG2" s="99"/>
-      <c r="BH2" s="99"/>
-      <c r="BI2" s="99"/>
-      <c r="BJ2" s="99"/>
-      <c r="BK2" s="99"/>
-      <c r="BL2" s="99"/>
-      <c r="BM2" s="99"/>
-      <c r="BN2" s="99"/>
-      <c r="BO2" s="99"/>
-      <c r="BP2" s="99"/>
-      <c r="BQ2" s="99"/>
-      <c r="BR2" s="99"/>
-      <c r="BS2" s="99"/>
-      <c r="BT2" s="99"/>
-      <c r="BU2" s="99"/>
-      <c r="BV2" s="175"/>
-      <c r="BW2" s="99"/>
-      <c r="BX2" s="99"/>
-      <c r="BY2" s="99"/>
-      <c r="BZ2" s="99"/>
-      <c r="CA2" s="99"/>
-      <c r="CB2" s="99"/>
-      <c r="CC2" s="99"/>
-      <c r="CD2" s="99"/>
-      <c r="CE2" s="99"/>
-      <c r="CF2" s="99"/>
-      <c r="CG2" s="99"/>
-      <c r="CH2" s="99"/>
-      <c r="CI2" s="99"/>
-      <c r="CJ2" s="99"/>
-      <c r="CK2" s="99"/>
-      <c r="CL2" s="99"/>
-      <c r="CM2" s="99"/>
-      <c r="CN2" s="99"/>
-      <c r="CO2" s="99"/>
-      <c r="CP2" s="99"/>
-      <c r="CQ2" s="99"/>
-      <c r="CR2" s="118"/>
-      <c r="CS2" s="173"/>
-      <c r="CT2" s="161"/>
-      <c r="CU2" s="161"/>
-      <c r="CV2" s="161"/>
-      <c r="CW2" s="174"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="112"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="112"/>
+      <c r="L2" s="112"/>
+      <c r="M2" s="112"/>
+      <c r="N2" s="112"/>
+      <c r="O2" s="112"/>
+      <c r="P2" s="160"/>
+      <c r="Q2" s="118"/>
+      <c r="R2" s="118"/>
+      <c r="S2" s="118"/>
+      <c r="T2" s="154"/>
+      <c r="U2" s="112"/>
+      <c r="V2" s="112"/>
+      <c r="W2" s="131"/>
+      <c r="X2" s="155"/>
+      <c r="Y2" s="112"/>
+      <c r="Z2" s="112"/>
+      <c r="AA2" s="112"/>
+      <c r="AB2" s="130"/>
+      <c r="AC2" s="112"/>
+      <c r="AD2" s="112"/>
+      <c r="AE2" s="112"/>
+      <c r="AF2" s="112"/>
+      <c r="AG2" s="112"/>
+      <c r="AH2" s="112"/>
+      <c r="AI2" s="112"/>
+      <c r="AJ2" s="112"/>
+      <c r="AK2" s="131"/>
+      <c r="AL2" s="155"/>
+      <c r="AM2" s="112"/>
+      <c r="AN2" s="112"/>
+      <c r="AO2" s="112"/>
+      <c r="AP2" s="112"/>
+      <c r="AQ2" s="112"/>
+      <c r="AR2" s="112"/>
+      <c r="AS2" s="112"/>
+      <c r="AT2" s="112"/>
+      <c r="AU2" s="154"/>
+      <c r="AV2" s="112"/>
+      <c r="AW2" s="112"/>
+      <c r="AX2" s="112"/>
+      <c r="AY2" s="112"/>
+      <c r="AZ2" s="112"/>
+      <c r="BA2" s="112"/>
+      <c r="BB2" s="112"/>
+      <c r="BC2" s="112"/>
+      <c r="BD2" s="112"/>
+      <c r="BE2" s="112"/>
+      <c r="BF2" s="112"/>
+      <c r="BG2" s="112"/>
+      <c r="BH2" s="112"/>
+      <c r="BI2" s="112"/>
+      <c r="BJ2" s="112"/>
+      <c r="BK2" s="112"/>
+      <c r="BL2" s="112"/>
+      <c r="BM2" s="112"/>
+      <c r="BN2" s="112"/>
+      <c r="BO2" s="112"/>
+      <c r="BP2" s="112"/>
+      <c r="BQ2" s="112"/>
+      <c r="BR2" s="112"/>
+      <c r="BS2" s="112"/>
+      <c r="BT2" s="112"/>
+      <c r="BU2" s="112"/>
+      <c r="BV2" s="188"/>
+      <c r="BW2" s="112"/>
+      <c r="BX2" s="112"/>
+      <c r="BY2" s="112"/>
+      <c r="BZ2" s="112"/>
+      <c r="CA2" s="112"/>
+      <c r="CB2" s="112"/>
+      <c r="CC2" s="112"/>
+      <c r="CD2" s="112"/>
+      <c r="CE2" s="112"/>
+      <c r="CF2" s="112"/>
+      <c r="CG2" s="112"/>
+      <c r="CH2" s="112"/>
+      <c r="CI2" s="112"/>
+      <c r="CJ2" s="112"/>
+      <c r="CK2" s="112"/>
+      <c r="CL2" s="112"/>
+      <c r="CM2" s="112"/>
+      <c r="CN2" s="112"/>
+      <c r="CO2" s="112"/>
+      <c r="CP2" s="112"/>
+      <c r="CQ2" s="112"/>
+      <c r="CR2" s="131"/>
+      <c r="CS2" s="186"/>
+      <c r="CT2" s="174"/>
+      <c r="CU2" s="174"/>
+      <c r="CV2" s="174"/>
+      <c r="CW2" s="187"/>
       <c r="CX2" s="1"/>
-      <c r="CY2" s="162">
+      <c r="CY2" s="175">
         <f>COUNTA('BASE DE DATOS'!B10:B49)</f>
         <v>35</v>
       </c>
-      <c r="CZ2" s="123"/>
-      <c r="DA2" s="123"/>
-      <c r="DB2" s="123"/>
-      <c r="DC2" s="123"/>
-      <c r="DD2" s="123"/>
-      <c r="DE2" s="123"/>
-      <c r="DF2" s="123"/>
-      <c r="DG2" s="123"/>
+      <c r="CZ2" s="136"/>
+      <c r="DA2" s="136"/>
+      <c r="DB2" s="136"/>
+      <c r="DC2" s="136"/>
+      <c r="DD2" s="136"/>
+      <c r="DE2" s="136"/>
+      <c r="DF2" s="136"/>
+      <c r="DG2" s="136"/>
       <c r="DH2" s="1"/>
       <c r="DI2" s="1"/>
       <c r="DJ2" s="1"/>
@@ -4955,113 +5099,113 @@
       <c r="DW2" s="1"/>
     </row>
     <row r="3" spans="1:129" ht="16.5">
-      <c r="A3" s="98" t="s">
+      <c r="A3" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="99"/>
-      <c r="C3" s="100"/>
-      <c r="D3" s="136" t="s">
+      <c r="B3" s="112"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="149" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="99"/>
-      <c r="F3" s="100"/>
-      <c r="G3" s="120" t="s">
+      <c r="E3" s="112"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="133" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="99"/>
-      <c r="I3" s="99"/>
-      <c r="J3" s="99"/>
-      <c r="K3" s="99"/>
-      <c r="L3" s="99"/>
-      <c r="M3" s="99"/>
-      <c r="N3" s="99"/>
-      <c r="O3" s="99"/>
-      <c r="P3" s="137"/>
-      <c r="Q3" s="99"/>
-      <c r="R3" s="99"/>
-      <c r="S3" s="99"/>
-      <c r="T3" s="133"/>
-      <c r="U3" s="99"/>
-      <c r="V3" s="99"/>
-      <c r="W3" s="118"/>
-      <c r="X3" s="143"/>
-      <c r="Y3" s="99"/>
-      <c r="Z3" s="99"/>
-      <c r="AA3" s="99"/>
-      <c r="AB3" s="133"/>
-      <c r="AC3" s="99"/>
-      <c r="AD3" s="99"/>
-      <c r="AE3" s="99"/>
-      <c r="AF3" s="99"/>
-      <c r="AG3" s="99"/>
-      <c r="AH3" s="99"/>
-      <c r="AI3" s="99"/>
-      <c r="AJ3" s="99"/>
-      <c r="AK3" s="118"/>
-      <c r="AL3" s="169"/>
-      <c r="AM3" s="99"/>
-      <c r="AN3" s="99"/>
-      <c r="AO3" s="99"/>
-      <c r="AP3" s="99"/>
-      <c r="AQ3" s="99"/>
-      <c r="AR3" s="99"/>
-      <c r="AS3" s="99"/>
-      <c r="AT3" s="99"/>
-      <c r="AU3" s="163"/>
-      <c r="AV3" s="99"/>
-      <c r="AW3" s="99"/>
-      <c r="AX3" s="99"/>
-      <c r="AY3" s="99"/>
-      <c r="AZ3" s="99"/>
-      <c r="BA3" s="99"/>
-      <c r="BB3" s="99"/>
-      <c r="BC3" s="99"/>
-      <c r="BD3" s="99"/>
-      <c r="BE3" s="99"/>
-      <c r="BF3" s="99"/>
-      <c r="BG3" s="99"/>
-      <c r="BH3" s="99"/>
-      <c r="BI3" s="99"/>
-      <c r="BJ3" s="99"/>
-      <c r="BK3" s="99"/>
-      <c r="BL3" s="99"/>
-      <c r="BM3" s="99"/>
-      <c r="BN3" s="99"/>
-      <c r="BO3" s="99"/>
-      <c r="BP3" s="99"/>
-      <c r="BQ3" s="99"/>
-      <c r="BR3" s="99"/>
-      <c r="BS3" s="99"/>
-      <c r="BT3" s="99"/>
-      <c r="BU3" s="99"/>
-      <c r="BV3" s="176"/>
-      <c r="BW3" s="99"/>
-      <c r="BX3" s="99"/>
-      <c r="BY3" s="99"/>
-      <c r="BZ3" s="99"/>
-      <c r="CA3" s="99"/>
-      <c r="CB3" s="99"/>
-      <c r="CC3" s="99"/>
-      <c r="CD3" s="99"/>
-      <c r="CE3" s="99"/>
-      <c r="CF3" s="99"/>
-      <c r="CG3" s="99"/>
-      <c r="CH3" s="99"/>
-      <c r="CI3" s="99"/>
-      <c r="CJ3" s="99"/>
-      <c r="CK3" s="99"/>
-      <c r="CL3" s="99"/>
-      <c r="CM3" s="99"/>
-      <c r="CN3" s="99"/>
-      <c r="CO3" s="99"/>
-      <c r="CP3" s="99"/>
-      <c r="CQ3" s="99"/>
-      <c r="CR3" s="118"/>
-      <c r="CS3" s="173"/>
-      <c r="CT3" s="161"/>
-      <c r="CU3" s="161"/>
-      <c r="CV3" s="161"/>
-      <c r="CW3" s="174"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
+      <c r="K3" s="112"/>
+      <c r="L3" s="112"/>
+      <c r="M3" s="112"/>
+      <c r="N3" s="112"/>
+      <c r="O3" s="112"/>
+      <c r="P3" s="150"/>
+      <c r="Q3" s="112"/>
+      <c r="R3" s="112"/>
+      <c r="S3" s="112"/>
+      <c r="T3" s="146"/>
+      <c r="U3" s="112"/>
+      <c r="V3" s="112"/>
+      <c r="W3" s="131"/>
+      <c r="X3" s="156"/>
+      <c r="Y3" s="112"/>
+      <c r="Z3" s="112"/>
+      <c r="AA3" s="112"/>
+      <c r="AB3" s="146"/>
+      <c r="AC3" s="112"/>
+      <c r="AD3" s="112"/>
+      <c r="AE3" s="112"/>
+      <c r="AF3" s="112"/>
+      <c r="AG3" s="112"/>
+      <c r="AH3" s="112"/>
+      <c r="AI3" s="112"/>
+      <c r="AJ3" s="112"/>
+      <c r="AK3" s="131"/>
+      <c r="AL3" s="182"/>
+      <c r="AM3" s="112"/>
+      <c r="AN3" s="112"/>
+      <c r="AO3" s="112"/>
+      <c r="AP3" s="112"/>
+      <c r="AQ3" s="112"/>
+      <c r="AR3" s="112"/>
+      <c r="AS3" s="112"/>
+      <c r="AT3" s="112"/>
+      <c r="AU3" s="176"/>
+      <c r="AV3" s="112"/>
+      <c r="AW3" s="112"/>
+      <c r="AX3" s="112"/>
+      <c r="AY3" s="112"/>
+      <c r="AZ3" s="112"/>
+      <c r="BA3" s="112"/>
+      <c r="BB3" s="112"/>
+      <c r="BC3" s="112"/>
+      <c r="BD3" s="112"/>
+      <c r="BE3" s="112"/>
+      <c r="BF3" s="112"/>
+      <c r="BG3" s="112"/>
+      <c r="BH3" s="112"/>
+      <c r="BI3" s="112"/>
+      <c r="BJ3" s="112"/>
+      <c r="BK3" s="112"/>
+      <c r="BL3" s="112"/>
+      <c r="BM3" s="112"/>
+      <c r="BN3" s="112"/>
+      <c r="BO3" s="112"/>
+      <c r="BP3" s="112"/>
+      <c r="BQ3" s="112"/>
+      <c r="BR3" s="112"/>
+      <c r="BS3" s="112"/>
+      <c r="BT3" s="112"/>
+      <c r="BU3" s="112"/>
+      <c r="BV3" s="189"/>
+      <c r="BW3" s="112"/>
+      <c r="BX3" s="112"/>
+      <c r="BY3" s="112"/>
+      <c r="BZ3" s="112"/>
+      <c r="CA3" s="112"/>
+      <c r="CB3" s="112"/>
+      <c r="CC3" s="112"/>
+      <c r="CD3" s="112"/>
+      <c r="CE3" s="112"/>
+      <c r="CF3" s="112"/>
+      <c r="CG3" s="112"/>
+      <c r="CH3" s="112"/>
+      <c r="CI3" s="112"/>
+      <c r="CJ3" s="112"/>
+      <c r="CK3" s="112"/>
+      <c r="CL3" s="112"/>
+      <c r="CM3" s="112"/>
+      <c r="CN3" s="112"/>
+      <c r="CO3" s="112"/>
+      <c r="CP3" s="112"/>
+      <c r="CQ3" s="112"/>
+      <c r="CR3" s="131"/>
+      <c r="CS3" s="186"/>
+      <c r="CT3" s="174"/>
+      <c r="CU3" s="174"/>
+      <c r="CV3" s="174"/>
+      <c r="CW3" s="187"/>
       <c r="CX3" s="1"/>
       <c r="CY3" s="1"/>
       <c r="CZ3" s="1"/>
@@ -5090,142 +5234,142 @@
       <c r="DW3" s="1"/>
     </row>
     <row r="4" spans="1:129" ht="15.75">
-      <c r="A4" s="98" t="s">
+      <c r="A4" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="99"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="119" t="s">
+      <c r="B4" s="112"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="132" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="99"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="121" t="s">
+      <c r="E4" s="112"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="102"/>
-      <c r="M4" s="102"/>
-      <c r="N4" s="102"/>
-      <c r="O4" s="102"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="102"/>
-      <c r="R4" s="102"/>
-      <c r="S4" s="102"/>
-      <c r="T4" s="127"/>
-      <c r="U4" s="102"/>
-      <c r="V4" s="102"/>
-      <c r="W4" s="128"/>
-      <c r="X4" s="130"/>
-      <c r="Y4" s="102"/>
-      <c r="Z4" s="102"/>
-      <c r="AA4" s="102"/>
-      <c r="AB4" s="131"/>
-      <c r="AC4" s="102"/>
-      <c r="AD4" s="102"/>
-      <c r="AE4" s="102"/>
-      <c r="AF4" s="102"/>
-      <c r="AG4" s="102"/>
-      <c r="AH4" s="102"/>
-      <c r="AI4" s="102"/>
-      <c r="AJ4" s="102"/>
-      <c r="AK4" s="128"/>
-      <c r="AL4" s="177"/>
-      <c r="AM4" s="102"/>
-      <c r="AN4" s="102"/>
-      <c r="AO4" s="102"/>
-      <c r="AP4" s="102"/>
-      <c r="AQ4" s="102"/>
-      <c r="AR4" s="102"/>
-      <c r="AS4" s="102"/>
-      <c r="AT4" s="128"/>
-      <c r="AU4" s="164"/>
-      <c r="AV4" s="102"/>
-      <c r="AW4" s="102"/>
-      <c r="AX4" s="102"/>
-      <c r="AY4" s="102"/>
-      <c r="AZ4" s="102"/>
-      <c r="BA4" s="102"/>
-      <c r="BB4" s="102"/>
-      <c r="BC4" s="102"/>
-      <c r="BD4" s="102"/>
-      <c r="BE4" s="102"/>
-      <c r="BF4" s="102"/>
-      <c r="BG4" s="102"/>
-      <c r="BH4" s="102"/>
-      <c r="BI4" s="102"/>
-      <c r="BJ4" s="102"/>
-      <c r="BK4" s="102"/>
-      <c r="BL4" s="102"/>
-      <c r="BM4" s="102"/>
-      <c r="BN4" s="102"/>
-      <c r="BO4" s="102"/>
-      <c r="BP4" s="102"/>
-      <c r="BQ4" s="102"/>
-      <c r="BR4" s="102"/>
-      <c r="BS4" s="102"/>
-      <c r="BT4" s="102"/>
-      <c r="BU4" s="102"/>
-      <c r="BV4" s="165"/>
-      <c r="BW4" s="102"/>
-      <c r="BX4" s="102"/>
-      <c r="BY4" s="102"/>
-      <c r="BZ4" s="102"/>
-      <c r="CA4" s="102"/>
-      <c r="CB4" s="102"/>
-      <c r="CC4" s="102"/>
-      <c r="CD4" s="102"/>
-      <c r="CE4" s="102"/>
-      <c r="CF4" s="102"/>
-      <c r="CG4" s="102"/>
-      <c r="CH4" s="102"/>
-      <c r="CI4" s="102"/>
-      <c r="CJ4" s="102"/>
-      <c r="CK4" s="102"/>
-      <c r="CL4" s="102"/>
-      <c r="CM4" s="102"/>
-      <c r="CN4" s="102"/>
-      <c r="CO4" s="102"/>
-      <c r="CP4" s="102"/>
-      <c r="CQ4" s="102"/>
-      <c r="CR4" s="128"/>
-      <c r="CS4" s="173"/>
-      <c r="CT4" s="161"/>
-      <c r="CU4" s="161"/>
-      <c r="CV4" s="161"/>
-      <c r="CW4" s="174"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="115"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
+      <c r="N4" s="115"/>
+      <c r="O4" s="115"/>
+      <c r="P4" s="137"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="115"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="140"/>
+      <c r="U4" s="115"/>
+      <c r="V4" s="115"/>
+      <c r="W4" s="141"/>
+      <c r="X4" s="143"/>
+      <c r="Y4" s="115"/>
+      <c r="Z4" s="115"/>
+      <c r="AA4" s="115"/>
+      <c r="AB4" s="144"/>
+      <c r="AC4" s="115"/>
+      <c r="AD4" s="115"/>
+      <c r="AE4" s="115"/>
+      <c r="AF4" s="115"/>
+      <c r="AG4" s="115"/>
+      <c r="AH4" s="115"/>
+      <c r="AI4" s="115"/>
+      <c r="AJ4" s="115"/>
+      <c r="AK4" s="141"/>
+      <c r="AL4" s="190"/>
+      <c r="AM4" s="115"/>
+      <c r="AN4" s="115"/>
+      <c r="AO4" s="115"/>
+      <c r="AP4" s="115"/>
+      <c r="AQ4" s="115"/>
+      <c r="AR4" s="115"/>
+      <c r="AS4" s="115"/>
+      <c r="AT4" s="141"/>
+      <c r="AU4" s="177"/>
+      <c r="AV4" s="115"/>
+      <c r="AW4" s="115"/>
+      <c r="AX4" s="115"/>
+      <c r="AY4" s="115"/>
+      <c r="AZ4" s="115"/>
+      <c r="BA4" s="115"/>
+      <c r="BB4" s="115"/>
+      <c r="BC4" s="115"/>
+      <c r="BD4" s="115"/>
+      <c r="BE4" s="115"/>
+      <c r="BF4" s="115"/>
+      <c r="BG4" s="115"/>
+      <c r="BH4" s="115"/>
+      <c r="BI4" s="115"/>
+      <c r="BJ4" s="115"/>
+      <c r="BK4" s="115"/>
+      <c r="BL4" s="115"/>
+      <c r="BM4" s="115"/>
+      <c r="BN4" s="115"/>
+      <c r="BO4" s="115"/>
+      <c r="BP4" s="115"/>
+      <c r="BQ4" s="115"/>
+      <c r="BR4" s="115"/>
+      <c r="BS4" s="115"/>
+      <c r="BT4" s="115"/>
+      <c r="BU4" s="115"/>
+      <c r="BV4" s="178"/>
+      <c r="BW4" s="115"/>
+      <c r="BX4" s="115"/>
+      <c r="BY4" s="115"/>
+      <c r="BZ4" s="115"/>
+      <c r="CA4" s="115"/>
+      <c r="CB4" s="115"/>
+      <c r="CC4" s="115"/>
+      <c r="CD4" s="115"/>
+      <c r="CE4" s="115"/>
+      <c r="CF4" s="115"/>
+      <c r="CG4" s="115"/>
+      <c r="CH4" s="115"/>
+      <c r="CI4" s="115"/>
+      <c r="CJ4" s="115"/>
+      <c r="CK4" s="115"/>
+      <c r="CL4" s="115"/>
+      <c r="CM4" s="115"/>
+      <c r="CN4" s="115"/>
+      <c r="CO4" s="115"/>
+      <c r="CP4" s="115"/>
+      <c r="CQ4" s="115"/>
+      <c r="CR4" s="141"/>
+      <c r="CS4" s="186"/>
+      <c r="CT4" s="174"/>
+      <c r="CU4" s="174"/>
+      <c r="CV4" s="174"/>
+      <c r="CW4" s="187"/>
       <c r="CX4" s="1"/>
-      <c r="CY4" s="151" t="s">
+      <c r="CY4" s="164" t="s">
         <v>11</v>
       </c>
-      <c r="CZ4" s="152"/>
-      <c r="DA4" s="153" t="s">
+      <c r="CZ4" s="165"/>
+      <c r="DA4" s="166" t="s">
         <v>12</v>
       </c>
-      <c r="DB4" s="154"/>
-      <c r="DC4" s="154"/>
-      <c r="DD4" s="154"/>
-      <c r="DE4" s="154"/>
-      <c r="DF4" s="154"/>
-      <c r="DG4" s="152"/>
+      <c r="DB4" s="167"/>
+      <c r="DC4" s="167"/>
+      <c r="DD4" s="167"/>
+      <c r="DE4" s="167"/>
+      <c r="DF4" s="167"/>
+      <c r="DG4" s="165"/>
       <c r="DH4" s="1"/>
       <c r="DI4" s="1"/>
-      <c r="DJ4" s="151" t="s">
+      <c r="DJ4" s="164" t="s">
         <v>13</v>
       </c>
-      <c r="DK4" s="152"/>
-      <c r="DL4" s="153" t="s">
+      <c r="DK4" s="165"/>
+      <c r="DL4" s="166" t="s">
         <v>14</v>
       </c>
-      <c r="DM4" s="154"/>
-      <c r="DN4" s="154"/>
-      <c r="DO4" s="154"/>
-      <c r="DP4" s="154"/>
-      <c r="DQ4" s="154"/>
-      <c r="DR4" s="152"/>
+      <c r="DM4" s="167"/>
+      <c r="DN4" s="167"/>
+      <c r="DO4" s="167"/>
+      <c r="DP4" s="167"/>
+      <c r="DQ4" s="167"/>
+      <c r="DR4" s="165"/>
       <c r="DS4" s="1"/>
       <c r="DT4" s="1"/>
       <c r="DU4" s="1"/>
@@ -5233,112 +5377,112 @@
       <c r="DW4" s="1"/>
     </row>
     <row r="5" spans="1:129" ht="15.75">
-      <c r="A5" s="98" t="s">
+      <c r="A5" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="99"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="132" t="str">
+      <c r="B5" s="112"/>
+      <c r="C5" s="113"/>
+      <c r="D5" s="145" t="str">
         <f>'BASE DE DATOS'!C7</f>
         <v>COLEGIO ROBERT F. KENNEDY</v>
       </c>
-      <c r="E5" s="99"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="122"/>
-      <c r="H5" s="123"/>
-      <c r="I5" s="123"/>
-      <c r="J5" s="123"/>
-      <c r="K5" s="123"/>
-      <c r="L5" s="123"/>
-      <c r="M5" s="123"/>
-      <c r="N5" s="123"/>
-      <c r="O5" s="123"/>
-      <c r="P5" s="125"/>
-      <c r="Q5" s="126"/>
-      <c r="R5" s="126"/>
-      <c r="S5" s="126"/>
-      <c r="T5" s="125"/>
-      <c r="U5" s="126"/>
-      <c r="V5" s="126"/>
-      <c r="W5" s="129"/>
-      <c r="X5" s="125"/>
-      <c r="Y5" s="126"/>
-      <c r="Z5" s="126"/>
-      <c r="AA5" s="126"/>
-      <c r="AB5" s="125"/>
-      <c r="AC5" s="126"/>
-      <c r="AD5" s="126"/>
-      <c r="AE5" s="126"/>
-      <c r="AF5" s="126"/>
-      <c r="AG5" s="126"/>
-      <c r="AH5" s="126"/>
-      <c r="AI5" s="126"/>
-      <c r="AJ5" s="126"/>
-      <c r="AK5" s="129"/>
-      <c r="AL5" s="125"/>
-      <c r="AM5" s="126"/>
-      <c r="AN5" s="126"/>
-      <c r="AO5" s="126"/>
-      <c r="AP5" s="126"/>
-      <c r="AQ5" s="126"/>
-      <c r="AR5" s="126"/>
-      <c r="AS5" s="126"/>
-      <c r="AT5" s="129"/>
-      <c r="AU5" s="125"/>
-      <c r="AV5" s="126"/>
-      <c r="AW5" s="126"/>
-      <c r="AX5" s="126"/>
-      <c r="AY5" s="126"/>
-      <c r="AZ5" s="126"/>
-      <c r="BA5" s="126"/>
-      <c r="BB5" s="126"/>
-      <c r="BC5" s="126"/>
-      <c r="BD5" s="126"/>
-      <c r="BE5" s="126"/>
-      <c r="BF5" s="126"/>
-      <c r="BG5" s="126"/>
-      <c r="BH5" s="126"/>
-      <c r="BI5" s="126"/>
-      <c r="BJ5" s="126"/>
-      <c r="BK5" s="126"/>
-      <c r="BL5" s="126"/>
-      <c r="BM5" s="126"/>
-      <c r="BN5" s="126"/>
-      <c r="BO5" s="126"/>
-      <c r="BP5" s="126"/>
-      <c r="BQ5" s="126"/>
-      <c r="BR5" s="126"/>
-      <c r="BS5" s="126"/>
-      <c r="BT5" s="126"/>
-      <c r="BU5" s="126"/>
-      <c r="BV5" s="125"/>
-      <c r="BW5" s="126"/>
-      <c r="BX5" s="126"/>
-      <c r="BY5" s="126"/>
-      <c r="BZ5" s="126"/>
-      <c r="CA5" s="126"/>
-      <c r="CB5" s="126"/>
-      <c r="CC5" s="126"/>
-      <c r="CD5" s="126"/>
-      <c r="CE5" s="126"/>
-      <c r="CF5" s="126"/>
-      <c r="CG5" s="126"/>
-      <c r="CH5" s="126"/>
-      <c r="CI5" s="126"/>
-      <c r="CJ5" s="126"/>
-      <c r="CK5" s="126"/>
-      <c r="CL5" s="126"/>
-      <c r="CM5" s="126"/>
-      <c r="CN5" s="126"/>
-      <c r="CO5" s="126"/>
-      <c r="CP5" s="126"/>
-      <c r="CQ5" s="126"/>
-      <c r="CR5" s="129"/>
-      <c r="CS5" s="125"/>
-      <c r="CT5" s="126"/>
-      <c r="CU5" s="126"/>
-      <c r="CV5" s="126"/>
-      <c r="CW5" s="129"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="113"/>
+      <c r="G5" s="135"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
+      <c r="K5" s="136"/>
+      <c r="L5" s="136"/>
+      <c r="M5" s="136"/>
+      <c r="N5" s="136"/>
+      <c r="O5" s="136"/>
+      <c r="P5" s="138"/>
+      <c r="Q5" s="139"/>
+      <c r="R5" s="139"/>
+      <c r="S5" s="139"/>
+      <c r="T5" s="138"/>
+      <c r="U5" s="139"/>
+      <c r="V5" s="139"/>
+      <c r="W5" s="142"/>
+      <c r="X5" s="138"/>
+      <c r="Y5" s="139"/>
+      <c r="Z5" s="139"/>
+      <c r="AA5" s="139"/>
+      <c r="AB5" s="138"/>
+      <c r="AC5" s="139"/>
+      <c r="AD5" s="139"/>
+      <c r="AE5" s="139"/>
+      <c r="AF5" s="139"/>
+      <c r="AG5" s="139"/>
+      <c r="AH5" s="139"/>
+      <c r="AI5" s="139"/>
+      <c r="AJ5" s="139"/>
+      <c r="AK5" s="142"/>
+      <c r="AL5" s="138"/>
+      <c r="AM5" s="139"/>
+      <c r="AN5" s="139"/>
+      <c r="AO5" s="139"/>
+      <c r="AP5" s="139"/>
+      <c r="AQ5" s="139"/>
+      <c r="AR5" s="139"/>
+      <c r="AS5" s="139"/>
+      <c r="AT5" s="142"/>
+      <c r="AU5" s="138"/>
+      <c r="AV5" s="139"/>
+      <c r="AW5" s="139"/>
+      <c r="AX5" s="139"/>
+      <c r="AY5" s="139"/>
+      <c r="AZ5" s="139"/>
+      <c r="BA5" s="139"/>
+      <c r="BB5" s="139"/>
+      <c r="BC5" s="139"/>
+      <c r="BD5" s="139"/>
+      <c r="BE5" s="139"/>
+      <c r="BF5" s="139"/>
+      <c r="BG5" s="139"/>
+      <c r="BH5" s="139"/>
+      <c r="BI5" s="139"/>
+      <c r="BJ5" s="139"/>
+      <c r="BK5" s="139"/>
+      <c r="BL5" s="139"/>
+      <c r="BM5" s="139"/>
+      <c r="BN5" s="139"/>
+      <c r="BO5" s="139"/>
+      <c r="BP5" s="139"/>
+      <c r="BQ5" s="139"/>
+      <c r="BR5" s="139"/>
+      <c r="BS5" s="139"/>
+      <c r="BT5" s="139"/>
+      <c r="BU5" s="139"/>
+      <c r="BV5" s="138"/>
+      <c r="BW5" s="139"/>
+      <c r="BX5" s="139"/>
+      <c r="BY5" s="139"/>
+      <c r="BZ5" s="139"/>
+      <c r="CA5" s="139"/>
+      <c r="CB5" s="139"/>
+      <c r="CC5" s="139"/>
+      <c r="CD5" s="139"/>
+      <c r="CE5" s="139"/>
+      <c r="CF5" s="139"/>
+      <c r="CG5" s="139"/>
+      <c r="CH5" s="139"/>
+      <c r="CI5" s="139"/>
+      <c r="CJ5" s="139"/>
+      <c r="CK5" s="139"/>
+      <c r="CL5" s="139"/>
+      <c r="CM5" s="139"/>
+      <c r="CN5" s="139"/>
+      <c r="CO5" s="139"/>
+      <c r="CP5" s="139"/>
+      <c r="CQ5" s="139"/>
+      <c r="CR5" s="142"/>
+      <c r="CS5" s="138"/>
+      <c r="CT5" s="139"/>
+      <c r="CU5" s="139"/>
+      <c r="CV5" s="139"/>
+      <c r="CW5" s="142"/>
       <c r="CX5" s="1"/>
       <c r="CY5" s="1"/>
       <c r="CZ5" s="1"/>
@@ -5367,14 +5511,14 @@
       <c r="DW5" s="1"/>
     </row>
     <row r="6" spans="1:129" ht="15.75">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="99"/>
-      <c r="C6" s="100"/>
+      <c r="B6" s="112"/>
+      <c r="C6" s="113"/>
       <c r="D6" s="3">
         <f>'BASE DE DATOS'!C4</f>
-        <v>3151042</v>
+        <v>3415087</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>17</v>
@@ -5383,18 +5527,18 @@
         <f>'BASE DE DATOS'!G7</f>
         <v>10</v>
       </c>
-      <c r="G6" s="101" t="str">
+      <c r="G6" s="114" t="str">
         <f>CY1 &amp; " " &amp; CY2</f>
         <v>TOTAL APRENDICES MATRICULADOS: 35</v>
       </c>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="102"/>
-      <c r="M6" s="102"/>
-      <c r="N6" s="102"/>
-      <c r="O6" s="103"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="115"/>
+      <c r="N6" s="115"/>
+      <c r="O6" s="116"/>
       <c r="P6" s="6" t="str">
         <f t="shared" ref="P6:CW6" si="0">TEXT(P7,"MMM")</f>
         <v>mar</v>
@@ -5739,41 +5883,41 @@
         <f t="shared" si="0"/>
         <v>dic</v>
       </c>
-      <c r="CX6" s="155" t="s">
+      <c r="CX6" s="168" t="s">
         <v>18</v>
       </c>
-      <c r="CY6" s="156"/>
-      <c r="CZ6" s="156"/>
-      <c r="DA6" s="156"/>
-      <c r="DB6" s="156"/>
-      <c r="DC6" s="156"/>
-      <c r="DD6" s="156"/>
-      <c r="DE6" s="156"/>
-      <c r="DF6" s="156"/>
-      <c r="DG6" s="156"/>
-      <c r="DH6" s="156"/>
-      <c r="DI6" s="156"/>
-      <c r="DJ6" s="156"/>
-      <c r="DK6" s="156"/>
-      <c r="DL6" s="156"/>
-      <c r="DM6" s="156"/>
-      <c r="DN6" s="156"/>
-      <c r="DO6" s="156"/>
-      <c r="DP6" s="156"/>
-      <c r="DQ6" s="156"/>
-      <c r="DR6" s="156"/>
-      <c r="DS6" s="156"/>
-      <c r="DT6" s="156"/>
-      <c r="DU6" s="156"/>
-      <c r="DV6" s="156"/>
-      <c r="DW6" s="156"/>
+      <c r="CY6" s="169"/>
+      <c r="CZ6" s="169"/>
+      <c r="DA6" s="169"/>
+      <c r="DB6" s="169"/>
+      <c r="DC6" s="169"/>
+      <c r="DD6" s="169"/>
+      <c r="DE6" s="169"/>
+      <c r="DF6" s="169"/>
+      <c r="DG6" s="169"/>
+      <c r="DH6" s="169"/>
+      <c r="DI6" s="169"/>
+      <c r="DJ6" s="169"/>
+      <c r="DK6" s="169"/>
+      <c r="DL6" s="169"/>
+      <c r="DM6" s="169"/>
+      <c r="DN6" s="169"/>
+      <c r="DO6" s="169"/>
+      <c r="DP6" s="169"/>
+      <c r="DQ6" s="169"/>
+      <c r="DR6" s="169"/>
+      <c r="DS6" s="169"/>
+      <c r="DT6" s="169"/>
+      <c r="DU6" s="169"/>
+      <c r="DV6" s="169"/>
+      <c r="DW6" s="169"/>
     </row>
     <row r="7" spans="1:129" ht="22.5">
-      <c r="A7" s="107" t="s">
+      <c r="A7" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="100"/>
+      <c r="B7" s="112"/>
+      <c r="C7" s="113"/>
       <c r="D7" s="8">
         <f>'BASE DE DATOS'!G5</f>
         <v>46084</v>
@@ -5785,15 +5929,15 @@
         <f>'BASE DE DATOS'!G6</f>
         <v>46087</v>
       </c>
-      <c r="G7" s="104"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="105"/>
-      <c r="M7" s="105"/>
-      <c r="N7" s="105"/>
-      <c r="O7" s="106"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="118"/>
+      <c r="K7" s="118"/>
+      <c r="L7" s="118"/>
+      <c r="M7" s="118"/>
+      <c r="N7" s="118"/>
+      <c r="O7" s="119"/>
       <c r="P7" s="11">
         <f>D7</f>
         <v>46084</v>
@@ -6138,58 +6282,58 @@
         <f>IF('BASE DE DATOS'!$G$4=1,(CV7+7),IF('BASE DE DATOS'!$G$4=2,(CU7+7)))</f>
         <v>46381</v>
       </c>
-      <c r="CX7" s="157" t="s">
+      <c r="CX7" s="170" t="s">
         <v>21</v>
       </c>
-      <c r="CY7" s="158"/>
-      <c r="CZ7" s="157" t="s">
+      <c r="CY7" s="171"/>
+      <c r="CZ7" s="170" t="s">
         <v>22</v>
       </c>
-      <c r="DA7" s="156"/>
-      <c r="DB7" s="157" t="s">
+      <c r="DA7" s="169"/>
+      <c r="DB7" s="170" t="s">
         <v>23</v>
       </c>
-      <c r="DC7" s="158"/>
-      <c r="DD7" s="157" t="s">
+      <c r="DC7" s="171"/>
+      <c r="DD7" s="170" t="s">
         <v>24</v>
       </c>
-      <c r="DE7" s="158"/>
-      <c r="DF7" s="157" t="s">
+      <c r="DE7" s="171"/>
+      <c r="DF7" s="170" t="s">
         <v>25</v>
       </c>
-      <c r="DG7" s="158"/>
-      <c r="DH7" s="157" t="s">
+      <c r="DG7" s="171"/>
+      <c r="DH7" s="170" t="s">
         <v>26</v>
       </c>
-      <c r="DI7" s="158"/>
-      <c r="DJ7" s="157" t="s">
+      <c r="DI7" s="171"/>
+      <c r="DJ7" s="170" t="s">
         <v>27</v>
       </c>
-      <c r="DK7" s="158"/>
-      <c r="DL7" s="157" t="s">
+      <c r="DK7" s="171"/>
+      <c r="DL7" s="170" t="s">
         <v>28</v>
       </c>
-      <c r="DM7" s="158"/>
-      <c r="DN7" s="157" t="s">
+      <c r="DM7" s="171"/>
+      <c r="DN7" s="170" t="s">
         <v>29</v>
       </c>
-      <c r="DO7" s="158"/>
-      <c r="DP7" s="157" t="s">
+      <c r="DO7" s="171"/>
+      <c r="DP7" s="170" t="s">
         <v>30</v>
       </c>
-      <c r="DQ7" s="158"/>
-      <c r="DR7" s="157" t="s">
+      <c r="DQ7" s="171"/>
+      <c r="DR7" s="170" t="s">
         <v>31</v>
       </c>
-      <c r="DS7" s="158"/>
-      <c r="DT7" s="157" t="s">
+      <c r="DS7" s="171"/>
+      <c r="DT7" s="170" t="s">
         <v>32</v>
       </c>
-      <c r="DU7" s="158"/>
-      <c r="DV7" s="159" t="s">
+      <c r="DU7" s="171"/>
+      <c r="DV7" s="172" t="s">
         <v>33</v>
       </c>
-      <c r="DW7" s="156"/>
+      <c r="DW7" s="169"/>
     </row>
     <row r="8" spans="1:129" ht="30.75" customHeight="1">
       <c r="A8" s="13" t="s">
@@ -6201,13 +6345,13 @@
       <c r="C8" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="71" t="s">
+      <c r="D8" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="71" t="s">
+      <c r="E8" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="71" t="s">
+      <c r="F8" s="69" t="s">
         <v>39</v>
       </c>
       <c r="G8" s="16" t="s">
@@ -6677,7 +6821,7 @@
       </c>
       <c r="D9" s="28" t="str">
         <f>'BASE DE DATOS'!B10</f>
-        <v>Arciniegas Ávila Karoll Sofia</v>
+        <v xml:space="preserve">Karoll Sofia Arciniegas Ávila </v>
       </c>
       <c r="E9" s="29" t="s">
         <v>48</v>
@@ -6688,7 +6832,7 @@
       </c>
       <c r="G9" s="31">
         <f t="shared" ref="G9:G37" si="3">COUNTIF(P9:CR9,"A")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" s="32">
         <f t="shared" ref="H9:H37" si="4">COUNTIF(P9:CR9,"CE")</f>
@@ -6737,7 +6881,9 @@
         <v>40</v>
       </c>
       <c r="V9" s="35"/>
-      <c r="W9" s="35"/>
+      <c r="W9" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X9" s="35"/>
       <c r="Y9" s="35"/>
       <c r="Z9" s="35"/>
@@ -6817,29 +6963,29 @@
       <c r="CV9" s="35"/>
       <c r="CW9" s="35"/>
       <c r="CX9" s="36"/>
-      <c r="CY9" s="72"/>
+      <c r="CY9" s="70"/>
       <c r="CZ9" s="36"/>
-      <c r="DA9" s="72"/>
+      <c r="DA9" s="70"/>
       <c r="DB9" s="36"/>
-      <c r="DC9" s="72"/>
+      <c r="DC9" s="70"/>
       <c r="DD9" s="36"/>
-      <c r="DE9" s="72"/>
+      <c r="DE9" s="70"/>
       <c r="DF9" s="36"/>
-      <c r="DG9" s="72"/>
+      <c r="DG9" s="70"/>
       <c r="DH9" s="36"/>
-      <c r="DI9" s="72"/>
+      <c r="DI9" s="70"/>
       <c r="DJ9" s="36"/>
-      <c r="DK9" s="72"/>
+      <c r="DK9" s="70"/>
       <c r="DL9" s="36"/>
-      <c r="DM9" s="72"/>
+      <c r="DM9" s="70"/>
       <c r="DN9" s="36"/>
-      <c r="DO9" s="72"/>
+      <c r="DO9" s="70"/>
       <c r="DP9" s="36"/>
-      <c r="DQ9" s="72"/>
+      <c r="DQ9" s="70"/>
       <c r="DR9" s="36"/>
-      <c r="DS9" s="72"/>
+      <c r="DS9" s="70"/>
       <c r="DT9" s="36"/>
-      <c r="DU9" s="72"/>
+      <c r="DU9" s="70"/>
       <c r="DV9" s="37">
         <f t="shared" ref="DV9:DW9" si="12">CX9+CZ9+DB9+DD9+DF9+DH9+DJ9+DL9+DN9+DP9+DR9+DT9</f>
         <v>0</v>
@@ -6878,7 +7024,7 @@
       </c>
       <c r="G10" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="41">
         <f t="shared" si="4"/>
@@ -6927,7 +7073,9 @@
         <v>40</v>
       </c>
       <c r="V10" s="35"/>
-      <c r="W10" s="35"/>
+      <c r="W10" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X10" s="35"/>
       <c r="Y10" s="35"/>
       <c r="Z10" s="35"/>
@@ -7007,29 +7155,29 @@
       <c r="CV10" s="35"/>
       <c r="CW10" s="35"/>
       <c r="CX10" s="36"/>
-      <c r="CY10" s="72"/>
+      <c r="CY10" s="70"/>
       <c r="CZ10" s="36"/>
-      <c r="DA10" s="72"/>
+      <c r="DA10" s="70"/>
       <c r="DB10" s="36"/>
-      <c r="DC10" s="72"/>
+      <c r="DC10" s="70"/>
       <c r="DD10" s="36"/>
-      <c r="DE10" s="72"/>
+      <c r="DE10" s="70"/>
       <c r="DF10" s="36"/>
-      <c r="DG10" s="72"/>
+      <c r="DG10" s="70"/>
       <c r="DH10" s="36"/>
-      <c r="DI10" s="72"/>
+      <c r="DI10" s="70"/>
       <c r="DJ10" s="36"/>
-      <c r="DK10" s="72"/>
+      <c r="DK10" s="70"/>
       <c r="DL10" s="36"/>
-      <c r="DM10" s="72"/>
+      <c r="DM10" s="70"/>
       <c r="DN10" s="36"/>
-      <c r="DO10" s="72"/>
+      <c r="DO10" s="70"/>
       <c r="DP10" s="36"/>
-      <c r="DQ10" s="72"/>
+      <c r="DQ10" s="70"/>
       <c r="DR10" s="36"/>
-      <c r="DS10" s="72"/>
+      <c r="DS10" s="70"/>
       <c r="DT10" s="36"/>
-      <c r="DU10" s="72"/>
+      <c r="DU10" s="70"/>
       <c r="DV10" s="37">
         <f t="shared" ref="DV10:DW10" si="13">CX10+CZ10+DB10+DD10+DF10+DH10+DJ10+DL10+DN10+DP10+DR10+DT10</f>
         <v>0</v>
@@ -7068,7 +7216,7 @@
       </c>
       <c r="G11" s="40">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="41">
         <f t="shared" si="4"/>
@@ -7100,7 +7248,7 @@
       </c>
       <c r="O11" s="42">
         <f t="shared" si="11"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="P11" s="35" t="s">
         <v>40</v>
@@ -7117,7 +7265,9 @@
         <v>40</v>
       </c>
       <c r="V11" s="35"/>
-      <c r="W11" s="35"/>
+      <c r="W11" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X11" s="35"/>
       <c r="Y11" s="35"/>
       <c r="Z11" s="35"/>
@@ -7197,29 +7347,29 @@
       <c r="CV11" s="35"/>
       <c r="CW11" s="35"/>
       <c r="CX11" s="36"/>
-      <c r="CY11" s="72"/>
+      <c r="CY11" s="70"/>
       <c r="CZ11" s="36"/>
-      <c r="DA11" s="72"/>
+      <c r="DA11" s="70"/>
       <c r="DB11" s="36"/>
-      <c r="DC11" s="72"/>
+      <c r="DC11" s="70"/>
       <c r="DD11" s="36"/>
-      <c r="DE11" s="72"/>
+      <c r="DE11" s="70"/>
       <c r="DF11" s="36"/>
-      <c r="DG11" s="72"/>
+      <c r="DG11" s="70"/>
       <c r="DH11" s="36"/>
-      <c r="DI11" s="72"/>
+      <c r="DI11" s="70"/>
       <c r="DJ11" s="36"/>
-      <c r="DK11" s="72"/>
+      <c r="DK11" s="70"/>
       <c r="DL11" s="36"/>
-      <c r="DM11" s="72"/>
+      <c r="DM11" s="70"/>
       <c r="DN11" s="36"/>
-      <c r="DO11" s="72"/>
+      <c r="DO11" s="70"/>
       <c r="DP11" s="36"/>
-      <c r="DQ11" s="72"/>
+      <c r="DQ11" s="70"/>
       <c r="DR11" s="36"/>
-      <c r="DS11" s="72"/>
+      <c r="DS11" s="70"/>
       <c r="DT11" s="36"/>
-      <c r="DU11" s="72"/>
+      <c r="DU11" s="70"/>
       <c r="DV11" s="37">
         <f t="shared" ref="DV11:DW11" si="15">CX11+CZ11+DB11+DD11+DF11+DH11+DJ11+DL11+DN11+DP11+DR11+DT11</f>
         <v>0</v>
@@ -7258,7 +7408,7 @@
       </c>
       <c r="G12" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" s="41">
         <f t="shared" si="4"/>
@@ -7307,7 +7457,9 @@
         <v>40</v>
       </c>
       <c r="V12" s="35"/>
-      <c r="W12" s="35"/>
+      <c r="W12" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X12" s="35"/>
       <c r="Y12" s="35"/>
       <c r="Z12" s="35"/>
@@ -7387,29 +7539,29 @@
       <c r="CV12" s="35"/>
       <c r="CW12" s="35"/>
       <c r="CX12" s="36"/>
-      <c r="CY12" s="72"/>
+      <c r="CY12" s="70"/>
       <c r="CZ12" s="36"/>
-      <c r="DA12" s="72"/>
+      <c r="DA12" s="70"/>
       <c r="DB12" s="36"/>
-      <c r="DC12" s="72"/>
+      <c r="DC12" s="70"/>
       <c r="DD12" s="36"/>
-      <c r="DE12" s="72"/>
+      <c r="DE12" s="70"/>
       <c r="DF12" s="36"/>
-      <c r="DG12" s="72"/>
+      <c r="DG12" s="70"/>
       <c r="DH12" s="36"/>
-      <c r="DI12" s="72"/>
+      <c r="DI12" s="70"/>
       <c r="DJ12" s="36"/>
-      <c r="DK12" s="72"/>
+      <c r="DK12" s="70"/>
       <c r="DL12" s="36"/>
-      <c r="DM12" s="72"/>
+      <c r="DM12" s="70"/>
       <c r="DN12" s="36"/>
-      <c r="DO12" s="72"/>
+      <c r="DO12" s="70"/>
       <c r="DP12" s="36"/>
-      <c r="DQ12" s="72"/>
+      <c r="DQ12" s="70"/>
       <c r="DR12" s="36"/>
-      <c r="DS12" s="72"/>
+      <c r="DS12" s="70"/>
       <c r="DT12" s="36"/>
-      <c r="DU12" s="72"/>
+      <c r="DU12" s="70"/>
       <c r="DV12" s="37">
         <f t="shared" ref="DV12:DW12" si="16">CX12+CZ12+DB12+DD12+DF12+DH12+DJ12+DL12+DN12+DP12+DR12+DT12</f>
         <v>0</v>
@@ -7444,7 +7596,7 @@
       </c>
       <c r="F13" s="30" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G13" s="40">
         <f t="shared" si="3"/>
@@ -7456,7 +7608,7 @@
       </c>
       <c r="I13" s="41">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="41">
         <f t="shared" si="6"/>
@@ -7480,7 +7632,7 @@
       </c>
       <c r="O13" s="42">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P13" s="35" t="s">
         <v>40</v>
@@ -7497,7 +7649,9 @@
         <v>40</v>
       </c>
       <c r="V13" s="35"/>
-      <c r="W13" s="35"/>
+      <c r="W13" s="35" t="s">
+        <v>13</v>
+      </c>
       <c r="X13" s="35"/>
       <c r="Y13" s="35"/>
       <c r="Z13" s="35"/>
@@ -7577,29 +7731,29 @@
       <c r="CV13" s="35"/>
       <c r="CW13" s="35"/>
       <c r="CX13" s="36"/>
-      <c r="CY13" s="72"/>
+      <c r="CY13" s="70"/>
       <c r="CZ13" s="36"/>
-      <c r="DA13" s="72"/>
+      <c r="DA13" s="70"/>
       <c r="DB13" s="36"/>
-      <c r="DC13" s="72"/>
+      <c r="DC13" s="70"/>
       <c r="DD13" s="36"/>
-      <c r="DE13" s="72"/>
+      <c r="DE13" s="70"/>
       <c r="DF13" s="36"/>
-      <c r="DG13" s="72"/>
+      <c r="DG13" s="70"/>
       <c r="DH13" s="36"/>
-      <c r="DI13" s="72"/>
+      <c r="DI13" s="70"/>
       <c r="DJ13" s="36"/>
-      <c r="DK13" s="72"/>
+      <c r="DK13" s="70"/>
       <c r="DL13" s="36"/>
-      <c r="DM13" s="72"/>
+      <c r="DM13" s="70"/>
       <c r="DN13" s="36"/>
-      <c r="DO13" s="72"/>
+      <c r="DO13" s="70"/>
       <c r="DP13" s="36"/>
-      <c r="DQ13" s="72"/>
+      <c r="DQ13" s="70"/>
       <c r="DR13" s="36"/>
-      <c r="DS13" s="72"/>
+      <c r="DS13" s="70"/>
       <c r="DT13" s="36"/>
-      <c r="DU13" s="72"/>
+      <c r="DU13" s="70"/>
       <c r="DV13" s="37">
         <f t="shared" ref="DV13:DW13" si="17">CX13+CZ13+DB13+DD13+DF13+DH13+DJ13+DL13+DN13+DP13+DR13+DT13</f>
         <v>0</v>
@@ -7638,7 +7792,7 @@
       </c>
       <c r="G14" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" s="41">
         <f t="shared" si="4"/>
@@ -7687,7 +7841,9 @@
         <v>40</v>
       </c>
       <c r="V14" s="35"/>
-      <c r="W14" s="35"/>
+      <c r="W14" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X14" s="35"/>
       <c r="Y14" s="35"/>
       <c r="Z14" s="35"/>
@@ -7767,29 +7923,29 @@
       <c r="CV14" s="35"/>
       <c r="CW14" s="35"/>
       <c r="CX14" s="36"/>
-      <c r="CY14" s="72"/>
+      <c r="CY14" s="70"/>
       <c r="CZ14" s="36"/>
-      <c r="DA14" s="72"/>
+      <c r="DA14" s="70"/>
       <c r="DB14" s="36"/>
-      <c r="DC14" s="72"/>
+      <c r="DC14" s="70"/>
       <c r="DD14" s="36"/>
-      <c r="DE14" s="72"/>
+      <c r="DE14" s="70"/>
       <c r="DF14" s="36"/>
-      <c r="DG14" s="72"/>
+      <c r="DG14" s="70"/>
       <c r="DH14" s="36"/>
-      <c r="DI14" s="72"/>
+      <c r="DI14" s="70"/>
       <c r="DJ14" s="36"/>
-      <c r="DK14" s="72"/>
+      <c r="DK14" s="70"/>
       <c r="DL14" s="36"/>
-      <c r="DM14" s="72"/>
+      <c r="DM14" s="70"/>
       <c r="DN14" s="36"/>
-      <c r="DO14" s="72"/>
+      <c r="DO14" s="70"/>
       <c r="DP14" s="36"/>
-      <c r="DQ14" s="72"/>
+      <c r="DQ14" s="70"/>
       <c r="DR14" s="36"/>
-      <c r="DS14" s="72"/>
+      <c r="DS14" s="70"/>
       <c r="DT14" s="36"/>
-      <c r="DU14" s="72"/>
+      <c r="DU14" s="70"/>
       <c r="DV14" s="37">
         <f t="shared" ref="DV14:DW14" si="18">CX14+CZ14+DB14+DD14+DF14+DH14+DJ14+DL14+DN14+DP14+DR14+DT14</f>
         <v>0</v>
@@ -7828,7 +7984,7 @@
       </c>
       <c r="G15" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" s="41">
         <f t="shared" si="4"/>
@@ -7877,7 +8033,9 @@
         <v>40</v>
       </c>
       <c r="V15" s="35"/>
-      <c r="W15" s="35"/>
+      <c r="W15" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X15" s="35"/>
       <c r="Y15" s="35"/>
       <c r="Z15" s="35"/>
@@ -7957,29 +8115,29 @@
       <c r="CV15" s="35"/>
       <c r="CW15" s="35"/>
       <c r="CX15" s="36"/>
-      <c r="CY15" s="72"/>
+      <c r="CY15" s="70"/>
       <c r="CZ15" s="36"/>
-      <c r="DA15" s="72"/>
+      <c r="DA15" s="70"/>
       <c r="DB15" s="36"/>
-      <c r="DC15" s="72"/>
+      <c r="DC15" s="70"/>
       <c r="DD15" s="36"/>
-      <c r="DE15" s="72"/>
+      <c r="DE15" s="70"/>
       <c r="DF15" s="36"/>
-      <c r="DG15" s="72"/>
+      <c r="DG15" s="70"/>
       <c r="DH15" s="36"/>
-      <c r="DI15" s="72"/>
+      <c r="DI15" s="70"/>
       <c r="DJ15" s="36"/>
-      <c r="DK15" s="72"/>
+      <c r="DK15" s="70"/>
       <c r="DL15" s="36"/>
-      <c r="DM15" s="72"/>
+      <c r="DM15" s="70"/>
       <c r="DN15" s="36"/>
-      <c r="DO15" s="72"/>
+      <c r="DO15" s="70"/>
       <c r="DP15" s="36"/>
-      <c r="DQ15" s="72"/>
+      <c r="DQ15" s="70"/>
       <c r="DR15" s="36"/>
-      <c r="DS15" s="72"/>
+      <c r="DS15" s="70"/>
       <c r="DT15" s="36"/>
-      <c r="DU15" s="72"/>
+      <c r="DU15" s="70"/>
       <c r="DV15" s="37">
         <f t="shared" ref="DV15:DW15" si="19">CX15+CZ15+DB15+DD15+DF15+DH15+DJ15+DL15+DN15+DP15+DR15+DT15</f>
         <v>0</v>
@@ -8018,7 +8176,7 @@
       </c>
       <c r="G16" s="40">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="41">
         <f t="shared" si="4"/>
@@ -8050,7 +8208,7 @@
       </c>
       <c r="O16" s="42">
         <f t="shared" si="11"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="P16" s="35" t="s">
         <v>40</v>
@@ -8067,7 +8225,9 @@
         <v>13</v>
       </c>
       <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
+      <c r="W16" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X16" s="35"/>
       <c r="Y16" s="35"/>
       <c r="Z16" s="35"/>
@@ -8147,29 +8307,29 @@
       <c r="CV16" s="35"/>
       <c r="CW16" s="35"/>
       <c r="CX16" s="36"/>
-      <c r="CY16" s="72"/>
+      <c r="CY16" s="70"/>
       <c r="CZ16" s="36"/>
-      <c r="DA16" s="72"/>
+      <c r="DA16" s="70"/>
       <c r="DB16" s="36"/>
-      <c r="DC16" s="72"/>
+      <c r="DC16" s="70"/>
       <c r="DD16" s="36"/>
-      <c r="DE16" s="72"/>
+      <c r="DE16" s="70"/>
       <c r="DF16" s="36"/>
-      <c r="DG16" s="72"/>
+      <c r="DG16" s="70"/>
       <c r="DH16" s="36"/>
-      <c r="DI16" s="72"/>
+      <c r="DI16" s="70"/>
       <c r="DJ16" s="36"/>
-      <c r="DK16" s="72"/>
+      <c r="DK16" s="70"/>
       <c r="DL16" s="36"/>
-      <c r="DM16" s="72"/>
+      <c r="DM16" s="70"/>
       <c r="DN16" s="36"/>
-      <c r="DO16" s="72"/>
+      <c r="DO16" s="70"/>
       <c r="DP16" s="36"/>
-      <c r="DQ16" s="72"/>
+      <c r="DQ16" s="70"/>
       <c r="DR16" s="36"/>
-      <c r="DS16" s="72"/>
+      <c r="DS16" s="70"/>
       <c r="DT16" s="36"/>
-      <c r="DU16" s="72"/>
+      <c r="DU16" s="70"/>
       <c r="DV16" s="37">
         <f t="shared" ref="DV16:DW16" si="20">CX16+CZ16+DB16+DD16+DF16+DH16+DJ16+DL16+DN16+DP16+DR16+DT16</f>
         <v>0</v>
@@ -8208,7 +8368,7 @@
       </c>
       <c r="G17" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="41">
         <f t="shared" si="4"/>
@@ -8257,7 +8417,9 @@
         <v>40</v>
       </c>
       <c r="V17" s="35"/>
-      <c r="W17" s="35"/>
+      <c r="W17" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X17" s="35"/>
       <c r="Y17" s="35"/>
       <c r="Z17" s="35"/>
@@ -8337,29 +8499,29 @@
       <c r="CV17" s="35"/>
       <c r="CW17" s="35"/>
       <c r="CX17" s="36"/>
-      <c r="CY17" s="72"/>
+      <c r="CY17" s="70"/>
       <c r="CZ17" s="36"/>
-      <c r="DA17" s="72"/>
+      <c r="DA17" s="70"/>
       <c r="DB17" s="36"/>
-      <c r="DC17" s="72"/>
+      <c r="DC17" s="70"/>
       <c r="DD17" s="36"/>
-      <c r="DE17" s="72"/>
+      <c r="DE17" s="70"/>
       <c r="DF17" s="36"/>
-      <c r="DG17" s="72"/>
+      <c r="DG17" s="70"/>
       <c r="DH17" s="36"/>
-      <c r="DI17" s="72"/>
+      <c r="DI17" s="70"/>
       <c r="DJ17" s="36"/>
-      <c r="DK17" s="72"/>
+      <c r="DK17" s="70"/>
       <c r="DL17" s="36"/>
-      <c r="DM17" s="72"/>
+      <c r="DM17" s="70"/>
       <c r="DN17" s="36"/>
-      <c r="DO17" s="72"/>
+      <c r="DO17" s="70"/>
       <c r="DP17" s="36"/>
-      <c r="DQ17" s="72"/>
+      <c r="DQ17" s="70"/>
       <c r="DR17" s="36"/>
-      <c r="DS17" s="72"/>
+      <c r="DS17" s="70"/>
       <c r="DT17" s="36"/>
-      <c r="DU17" s="72"/>
+      <c r="DU17" s="70"/>
       <c r="DV17" s="37">
         <f t="shared" ref="DV17:DW17" si="21">CX17+CZ17+DB17+DD17+DF17+DH17+DJ17+DL17+DN17+DP17+DR17+DT17</f>
         <v>0</v>
@@ -8398,7 +8560,7 @@
       </c>
       <c r="G18" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="41">
         <f t="shared" si="4"/>
@@ -8447,7 +8609,9 @@
         <v>40</v>
       </c>
       <c r="V18" s="35"/>
-      <c r="W18" s="35"/>
+      <c r="W18" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X18" s="35"/>
       <c r="Y18" s="35"/>
       <c r="Z18" s="35"/>
@@ -8527,29 +8691,29 @@
       <c r="CV18" s="35"/>
       <c r="CW18" s="35"/>
       <c r="CX18" s="36"/>
-      <c r="CY18" s="72"/>
+      <c r="CY18" s="70"/>
       <c r="CZ18" s="36"/>
-      <c r="DA18" s="72"/>
+      <c r="DA18" s="70"/>
       <c r="DB18" s="36"/>
-      <c r="DC18" s="72"/>
+      <c r="DC18" s="70"/>
       <c r="DD18" s="36"/>
-      <c r="DE18" s="72"/>
+      <c r="DE18" s="70"/>
       <c r="DF18" s="36"/>
-      <c r="DG18" s="72"/>
+      <c r="DG18" s="70"/>
       <c r="DH18" s="36"/>
-      <c r="DI18" s="72"/>
+      <c r="DI18" s="70"/>
       <c r="DJ18" s="36"/>
-      <c r="DK18" s="72"/>
+      <c r="DK18" s="70"/>
       <c r="DL18" s="36"/>
-      <c r="DM18" s="72"/>
+      <c r="DM18" s="70"/>
       <c r="DN18" s="36"/>
-      <c r="DO18" s="72"/>
+      <c r="DO18" s="70"/>
       <c r="DP18" s="36"/>
-      <c r="DQ18" s="72"/>
+      <c r="DQ18" s="70"/>
       <c r="DR18" s="36"/>
-      <c r="DS18" s="72"/>
+      <c r="DS18" s="70"/>
       <c r="DT18" s="36"/>
-      <c r="DU18" s="72"/>
+      <c r="DU18" s="70"/>
       <c r="DV18" s="37">
         <f t="shared" ref="DV18:DW18" si="22">CX18+CZ18+DB18+DD18+DF18+DH18+DJ18+DL18+DN18+DP18+DR18+DT18</f>
         <v>0</v>
@@ -8588,7 +8752,7 @@
       </c>
       <c r="G19" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" s="41">
         <f t="shared" si="4"/>
@@ -8637,7 +8801,9 @@
         <v>40</v>
       </c>
       <c r="V19" s="35"/>
-      <c r="W19" s="35"/>
+      <c r="W19" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X19" s="35"/>
       <c r="Y19" s="35"/>
       <c r="Z19" s="35"/>
@@ -8717,29 +8883,29 @@
       <c r="CV19" s="35"/>
       <c r="CW19" s="35"/>
       <c r="CX19" s="36"/>
-      <c r="CY19" s="72"/>
+      <c r="CY19" s="70"/>
       <c r="CZ19" s="36"/>
-      <c r="DA19" s="72"/>
+      <c r="DA19" s="70"/>
       <c r="DB19" s="36"/>
-      <c r="DC19" s="72"/>
+      <c r="DC19" s="70"/>
       <c r="DD19" s="36"/>
-      <c r="DE19" s="72"/>
+      <c r="DE19" s="70"/>
       <c r="DF19" s="36"/>
-      <c r="DG19" s="72"/>
+      <c r="DG19" s="70"/>
       <c r="DH19" s="36"/>
-      <c r="DI19" s="72"/>
+      <c r="DI19" s="70"/>
       <c r="DJ19" s="36"/>
-      <c r="DK19" s="72"/>
+      <c r="DK19" s="70"/>
       <c r="DL19" s="36"/>
-      <c r="DM19" s="72"/>
+      <c r="DM19" s="70"/>
       <c r="DN19" s="36"/>
-      <c r="DO19" s="72"/>
+      <c r="DO19" s="70"/>
       <c r="DP19" s="36"/>
-      <c r="DQ19" s="72"/>
+      <c r="DQ19" s="70"/>
       <c r="DR19" s="36"/>
-      <c r="DS19" s="72"/>
+      <c r="DS19" s="70"/>
       <c r="DT19" s="36"/>
-      <c r="DU19" s="72"/>
+      <c r="DU19" s="70"/>
       <c r="DV19" s="37">
         <f t="shared" ref="DV19:DW19" si="23">CX19+CZ19+DB19+DD19+DF19+DH19+DJ19+DL19+DN19+DP19+DR19+DT19</f>
         <v>0</v>
@@ -8778,7 +8944,7 @@
       </c>
       <c r="G20" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="41">
         <f t="shared" si="4"/>
@@ -8827,7 +8993,9 @@
         <v>40</v>
       </c>
       <c r="V20" s="35"/>
-      <c r="W20" s="35"/>
+      <c r="W20" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X20" s="35"/>
       <c r="Y20" s="35"/>
       <c r="Z20" s="35"/>
@@ -8907,29 +9075,29 @@
       <c r="CV20" s="35"/>
       <c r="CW20" s="35"/>
       <c r="CX20" s="36"/>
-      <c r="CY20" s="72"/>
+      <c r="CY20" s="70"/>
       <c r="CZ20" s="36"/>
-      <c r="DA20" s="72"/>
+      <c r="DA20" s="70"/>
       <c r="DB20" s="36"/>
-      <c r="DC20" s="72"/>
+      <c r="DC20" s="70"/>
       <c r="DD20" s="36"/>
-      <c r="DE20" s="72"/>
+      <c r="DE20" s="70"/>
       <c r="DF20" s="36"/>
-      <c r="DG20" s="72"/>
+      <c r="DG20" s="70"/>
       <c r="DH20" s="36"/>
-      <c r="DI20" s="72"/>
+      <c r="DI20" s="70"/>
       <c r="DJ20" s="36"/>
-      <c r="DK20" s="72"/>
+      <c r="DK20" s="70"/>
       <c r="DL20" s="36"/>
-      <c r="DM20" s="72"/>
+      <c r="DM20" s="70"/>
       <c r="DN20" s="36"/>
-      <c r="DO20" s="72"/>
+      <c r="DO20" s="70"/>
       <c r="DP20" s="36"/>
-      <c r="DQ20" s="72"/>
+      <c r="DQ20" s="70"/>
       <c r="DR20" s="36"/>
-      <c r="DS20" s="72"/>
+      <c r="DS20" s="70"/>
       <c r="DT20" s="36"/>
-      <c r="DU20" s="72"/>
+      <c r="DU20" s="70"/>
       <c r="DV20" s="37">
         <f t="shared" ref="DV20:DW20" si="24">CX20+CZ20+DB20+DD20+DF20+DH20+DJ20+DL20+DN20+DP20+DR20+DT20</f>
         <v>0</v>
@@ -8966,7 +9134,7 @@
       </c>
       <c r="G21" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H21" s="41">
         <f t="shared" si="4"/>
@@ -9015,7 +9183,9 @@
         <v>40</v>
       </c>
       <c r="V21" s="35"/>
-      <c r="W21" s="35"/>
+      <c r="W21" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X21" s="35"/>
       <c r="Y21" s="35"/>
       <c r="Z21" s="35"/>
@@ -9095,29 +9265,29 @@
       <c r="CV21" s="35"/>
       <c r="CW21" s="35"/>
       <c r="CX21" s="36"/>
-      <c r="CY21" s="72"/>
+      <c r="CY21" s="70"/>
       <c r="CZ21" s="36"/>
-      <c r="DA21" s="72"/>
+      <c r="DA21" s="70"/>
       <c r="DB21" s="36"/>
-      <c r="DC21" s="72"/>
+      <c r="DC21" s="70"/>
       <c r="DD21" s="36"/>
-      <c r="DE21" s="72"/>
+      <c r="DE21" s="70"/>
       <c r="DF21" s="36"/>
-      <c r="DG21" s="72"/>
+      <c r="DG21" s="70"/>
       <c r="DH21" s="36"/>
-      <c r="DI21" s="72"/>
+      <c r="DI21" s="70"/>
       <c r="DJ21" s="36"/>
-      <c r="DK21" s="72"/>
+      <c r="DK21" s="70"/>
       <c r="DL21" s="36"/>
-      <c r="DM21" s="72"/>
+      <c r="DM21" s="70"/>
       <c r="DN21" s="36"/>
-      <c r="DO21" s="72"/>
+      <c r="DO21" s="70"/>
       <c r="DP21" s="36"/>
-      <c r="DQ21" s="72"/>
+      <c r="DQ21" s="70"/>
       <c r="DR21" s="36"/>
-      <c r="DS21" s="72"/>
+      <c r="DS21" s="70"/>
       <c r="DT21" s="36"/>
-      <c r="DU21" s="72"/>
+      <c r="DU21" s="70"/>
       <c r="DV21" s="37">
         <f t="shared" ref="DV21:DW21" si="25">CX21+CZ21+DB21+DD21+DF21+DH21+DJ21+DL21+DN21+DP21+DR21+DT21</f>
         <v>0</v>
@@ -9154,7 +9324,7 @@
       </c>
       <c r="G22" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="41">
         <f t="shared" si="4"/>
@@ -9203,7 +9373,9 @@
         <v>40</v>
       </c>
       <c r="V22" s="35"/>
-      <c r="W22" s="35"/>
+      <c r="W22" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X22" s="35"/>
       <c r="Y22" s="35"/>
       <c r="Z22" s="35"/>
@@ -9283,29 +9455,29 @@
       <c r="CV22" s="35"/>
       <c r="CW22" s="35"/>
       <c r="CX22" s="36"/>
-      <c r="CY22" s="72"/>
+      <c r="CY22" s="70"/>
       <c r="CZ22" s="36"/>
-      <c r="DA22" s="72"/>
+      <c r="DA22" s="70"/>
       <c r="DB22" s="36"/>
-      <c r="DC22" s="72"/>
+      <c r="DC22" s="70"/>
       <c r="DD22" s="36"/>
-      <c r="DE22" s="72"/>
+      <c r="DE22" s="70"/>
       <c r="DF22" s="36"/>
-      <c r="DG22" s="72"/>
+      <c r="DG22" s="70"/>
       <c r="DH22" s="36"/>
-      <c r="DI22" s="72"/>
+      <c r="DI22" s="70"/>
       <c r="DJ22" s="36"/>
-      <c r="DK22" s="72"/>
+      <c r="DK22" s="70"/>
       <c r="DL22" s="36"/>
-      <c r="DM22" s="72"/>
+      <c r="DM22" s="70"/>
       <c r="DN22" s="36"/>
-      <c r="DO22" s="72"/>
+      <c r="DO22" s="70"/>
       <c r="DP22" s="36"/>
-      <c r="DQ22" s="72"/>
+      <c r="DQ22" s="70"/>
       <c r="DR22" s="36"/>
-      <c r="DS22" s="72"/>
+      <c r="DS22" s="70"/>
       <c r="DT22" s="36"/>
-      <c r="DU22" s="72"/>
+      <c r="DU22" s="70"/>
       <c r="DV22" s="37">
         <f t="shared" ref="DV22:DW22" si="26">CX22+CZ22+DB22+DD22+DF22+DH22+DJ22+DL22+DN22+DP22+DR22+DT22</f>
         <v>0</v>
@@ -9342,7 +9514,7 @@
       </c>
       <c r="G23" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="41">
         <f t="shared" si="4"/>
@@ -9391,7 +9563,9 @@
         <v>40</v>
       </c>
       <c r="V23" s="35"/>
-      <c r="W23" s="35"/>
+      <c r="W23" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X23" s="35"/>
       <c r="Y23" s="35"/>
       <c r="Z23" s="35"/>
@@ -9471,29 +9645,29 @@
       <c r="CV23" s="35"/>
       <c r="CW23" s="35"/>
       <c r="CX23" s="36"/>
-      <c r="CY23" s="72"/>
+      <c r="CY23" s="70"/>
       <c r="CZ23" s="36"/>
-      <c r="DA23" s="72"/>
+      <c r="DA23" s="70"/>
       <c r="DB23" s="36"/>
-      <c r="DC23" s="72"/>
+      <c r="DC23" s="70"/>
       <c r="DD23" s="36"/>
-      <c r="DE23" s="72"/>
+      <c r="DE23" s="70"/>
       <c r="DF23" s="36"/>
-      <c r="DG23" s="72"/>
+      <c r="DG23" s="70"/>
       <c r="DH23" s="36"/>
-      <c r="DI23" s="72"/>
+      <c r="DI23" s="70"/>
       <c r="DJ23" s="36"/>
-      <c r="DK23" s="72"/>
+      <c r="DK23" s="70"/>
       <c r="DL23" s="36"/>
-      <c r="DM23" s="72"/>
+      <c r="DM23" s="70"/>
       <c r="DN23" s="36"/>
-      <c r="DO23" s="72"/>
+      <c r="DO23" s="70"/>
       <c r="DP23" s="36"/>
-      <c r="DQ23" s="72"/>
+      <c r="DQ23" s="70"/>
       <c r="DR23" s="36"/>
-      <c r="DS23" s="72"/>
+      <c r="DS23" s="70"/>
       <c r="DT23" s="36"/>
-      <c r="DU23" s="72"/>
+      <c r="DU23" s="70"/>
       <c r="DV23" s="37">
         <f t="shared" ref="DV23:DW23" si="27">CX23+CZ23+DB23+DD23+DF23+DH23+DJ23+DL23+DN23+DP23+DR23+DT23</f>
         <v>0</v>
@@ -9530,7 +9704,7 @@
       </c>
       <c r="G24" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H24" s="41">
         <f t="shared" si="4"/>
@@ -9579,7 +9753,9 @@
         <v>40</v>
       </c>
       <c r="V24" s="35"/>
-      <c r="W24" s="35"/>
+      <c r="W24" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X24" s="35"/>
       <c r="Y24" s="35"/>
       <c r="Z24" s="35"/>
@@ -9659,29 +9835,29 @@
       <c r="CV24" s="35"/>
       <c r="CW24" s="35"/>
       <c r="CX24" s="36"/>
-      <c r="CY24" s="72"/>
+      <c r="CY24" s="70"/>
       <c r="CZ24" s="36"/>
-      <c r="DA24" s="72"/>
+      <c r="DA24" s="70"/>
       <c r="DB24" s="36"/>
-      <c r="DC24" s="72"/>
+      <c r="DC24" s="70"/>
       <c r="DD24" s="36"/>
-      <c r="DE24" s="72"/>
+      <c r="DE24" s="70"/>
       <c r="DF24" s="36"/>
-      <c r="DG24" s="72"/>
+      <c r="DG24" s="70"/>
       <c r="DH24" s="36"/>
-      <c r="DI24" s="72"/>
+      <c r="DI24" s="70"/>
       <c r="DJ24" s="36"/>
-      <c r="DK24" s="72"/>
+      <c r="DK24" s="70"/>
       <c r="DL24" s="36"/>
-      <c r="DM24" s="72"/>
+      <c r="DM24" s="70"/>
       <c r="DN24" s="36"/>
-      <c r="DO24" s="72"/>
+      <c r="DO24" s="70"/>
       <c r="DP24" s="36"/>
-      <c r="DQ24" s="72"/>
+      <c r="DQ24" s="70"/>
       <c r="DR24" s="36"/>
-      <c r="DS24" s="72"/>
+      <c r="DS24" s="70"/>
       <c r="DT24" s="36"/>
-      <c r="DU24" s="72"/>
+      <c r="DU24" s="70"/>
       <c r="DV24" s="37">
         <f t="shared" ref="DV24:DW24" si="28">CX24+CZ24+DB24+DD24+DF24+DH24+DJ24+DL24+DN24+DP24+DR24+DT24</f>
         <v>0</v>
@@ -9718,7 +9894,7 @@
       </c>
       <c r="G25" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H25" s="41">
         <f t="shared" si="4"/>
@@ -9767,7 +9943,9 @@
         <v>40</v>
       </c>
       <c r="V25" s="35"/>
-      <c r="W25" s="35"/>
+      <c r="W25" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X25" s="35"/>
       <c r="Y25" s="35"/>
       <c r="Z25" s="35"/>
@@ -9847,29 +10025,29 @@
       <c r="CV25" s="35"/>
       <c r="CW25" s="35"/>
       <c r="CX25" s="36"/>
-      <c r="CY25" s="72"/>
+      <c r="CY25" s="70"/>
       <c r="CZ25" s="36"/>
-      <c r="DA25" s="72"/>
+      <c r="DA25" s="70"/>
       <c r="DB25" s="36"/>
-      <c r="DC25" s="72"/>
+      <c r="DC25" s="70"/>
       <c r="DD25" s="36"/>
-      <c r="DE25" s="72"/>
+      <c r="DE25" s="70"/>
       <c r="DF25" s="36"/>
-      <c r="DG25" s="72"/>
+      <c r="DG25" s="70"/>
       <c r="DH25" s="36"/>
-      <c r="DI25" s="72"/>
+      <c r="DI25" s="70"/>
       <c r="DJ25" s="36"/>
-      <c r="DK25" s="72"/>
+      <c r="DK25" s="70"/>
       <c r="DL25" s="36"/>
-      <c r="DM25" s="72"/>
+      <c r="DM25" s="70"/>
       <c r="DN25" s="36"/>
-      <c r="DO25" s="72"/>
+      <c r="DO25" s="70"/>
       <c r="DP25" s="36"/>
-      <c r="DQ25" s="72"/>
+      <c r="DQ25" s="70"/>
       <c r="DR25" s="36"/>
-      <c r="DS25" s="72"/>
+      <c r="DS25" s="70"/>
       <c r="DT25" s="36"/>
-      <c r="DU25" s="72"/>
+      <c r="DU25" s="70"/>
       <c r="DV25" s="37">
         <f t="shared" ref="DV25:DW25" si="29">CX25+CZ25+DB25+DD25+DF25+DH25+DJ25+DL25+DN25+DP25+DR25+DT25</f>
         <v>0</v>
@@ -9906,7 +10084,7 @@
       </c>
       <c r="G26" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H26" s="41">
         <f t="shared" si="4"/>
@@ -9955,7 +10133,9 @@
         <v>40</v>
       </c>
       <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
+      <c r="W26" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X26" s="35"/>
       <c r="Y26" s="35"/>
       <c r="Z26" s="35"/>
@@ -10035,29 +10215,29 @@
       <c r="CV26" s="35"/>
       <c r="CW26" s="35"/>
       <c r="CX26" s="36"/>
-      <c r="CY26" s="72"/>
+      <c r="CY26" s="70"/>
       <c r="CZ26" s="36"/>
-      <c r="DA26" s="72"/>
+      <c r="DA26" s="70"/>
       <c r="DB26" s="36"/>
-      <c r="DC26" s="72"/>
+      <c r="DC26" s="70"/>
       <c r="DD26" s="36"/>
-      <c r="DE26" s="72"/>
+      <c r="DE26" s="70"/>
       <c r="DF26" s="36"/>
-      <c r="DG26" s="72"/>
+      <c r="DG26" s="70"/>
       <c r="DH26" s="36"/>
-      <c r="DI26" s="72"/>
+      <c r="DI26" s="70"/>
       <c r="DJ26" s="36"/>
-      <c r="DK26" s="72"/>
+      <c r="DK26" s="70"/>
       <c r="DL26" s="36"/>
-      <c r="DM26" s="72"/>
+      <c r="DM26" s="70"/>
       <c r="DN26" s="36"/>
-      <c r="DO26" s="72"/>
+      <c r="DO26" s="70"/>
       <c r="DP26" s="36"/>
-      <c r="DQ26" s="72"/>
+      <c r="DQ26" s="70"/>
       <c r="DR26" s="36"/>
-      <c r="DS26" s="72"/>
+      <c r="DS26" s="70"/>
       <c r="DT26" s="36"/>
-      <c r="DU26" s="72"/>
+      <c r="DU26" s="70"/>
       <c r="DV26" s="37">
         <f t="shared" ref="DV26:DW26" si="30">CX26+CZ26+DB26+DD26+DF26+DH26+DJ26+DL26+DN26+DP26+DR26+DT26</f>
         <v>0</v>
@@ -10094,7 +10274,7 @@
       </c>
       <c r="G27" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="41">
         <f t="shared" si="4"/>
@@ -10143,7 +10323,9 @@
         <v>40</v>
       </c>
       <c r="V27" s="35"/>
-      <c r="W27" s="35"/>
+      <c r="W27" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X27" s="35"/>
       <c r="Y27" s="35"/>
       <c r="Z27" s="35"/>
@@ -10223,29 +10405,29 @@
       <c r="CV27" s="35"/>
       <c r="CW27" s="35"/>
       <c r="CX27" s="36"/>
-      <c r="CY27" s="72"/>
+      <c r="CY27" s="70"/>
       <c r="CZ27" s="36"/>
-      <c r="DA27" s="72"/>
+      <c r="DA27" s="70"/>
       <c r="DB27" s="36"/>
-      <c r="DC27" s="72"/>
+      <c r="DC27" s="70"/>
       <c r="DD27" s="36"/>
-      <c r="DE27" s="72"/>
+      <c r="DE27" s="70"/>
       <c r="DF27" s="36"/>
-      <c r="DG27" s="72"/>
+      <c r="DG27" s="70"/>
       <c r="DH27" s="36"/>
-      <c r="DI27" s="72"/>
+      <c r="DI27" s="70"/>
       <c r="DJ27" s="36"/>
-      <c r="DK27" s="72"/>
+      <c r="DK27" s="70"/>
       <c r="DL27" s="36"/>
-      <c r="DM27" s="72"/>
+      <c r="DM27" s="70"/>
       <c r="DN27" s="36"/>
-      <c r="DO27" s="72"/>
+      <c r="DO27" s="70"/>
       <c r="DP27" s="36"/>
-      <c r="DQ27" s="72"/>
+      <c r="DQ27" s="70"/>
       <c r="DR27" s="36"/>
-      <c r="DS27" s="72"/>
+      <c r="DS27" s="70"/>
       <c r="DT27" s="36"/>
-      <c r="DU27" s="72"/>
+      <c r="DU27" s="70"/>
       <c r="DV27" s="37">
         <f t="shared" ref="DV27:DW27" si="31">CX27+CZ27+DB27+DD27+DF27+DH27+DJ27+DL27+DN27+DP27+DR27+DT27</f>
         <v>0</v>
@@ -10282,7 +10464,7 @@
       </c>
       <c r="G28" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="41">
         <f t="shared" si="4"/>
@@ -10331,7 +10513,9 @@
         <v>40</v>
       </c>
       <c r="V28" s="35"/>
-      <c r="W28" s="35"/>
+      <c r="W28" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X28" s="35"/>
       <c r="Y28" s="35"/>
       <c r="Z28" s="35"/>
@@ -10411,29 +10595,29 @@
       <c r="CV28" s="35"/>
       <c r="CW28" s="35"/>
       <c r="CX28" s="36"/>
-      <c r="CY28" s="72"/>
+      <c r="CY28" s="70"/>
       <c r="CZ28" s="36"/>
-      <c r="DA28" s="72"/>
+      <c r="DA28" s="70"/>
       <c r="DB28" s="36"/>
-      <c r="DC28" s="72"/>
+      <c r="DC28" s="70"/>
       <c r="DD28" s="36"/>
-      <c r="DE28" s="72"/>
+      <c r="DE28" s="70"/>
       <c r="DF28" s="36"/>
-      <c r="DG28" s="72"/>
+      <c r="DG28" s="70"/>
       <c r="DH28" s="36"/>
-      <c r="DI28" s="72"/>
+      <c r="DI28" s="70"/>
       <c r="DJ28" s="36"/>
-      <c r="DK28" s="72"/>
+      <c r="DK28" s="70"/>
       <c r="DL28" s="36"/>
-      <c r="DM28" s="72"/>
+      <c r="DM28" s="70"/>
       <c r="DN28" s="36"/>
-      <c r="DO28" s="72"/>
+      <c r="DO28" s="70"/>
       <c r="DP28" s="36"/>
-      <c r="DQ28" s="72"/>
+      <c r="DQ28" s="70"/>
       <c r="DR28" s="36"/>
-      <c r="DS28" s="72"/>
+      <c r="DS28" s="70"/>
       <c r="DT28" s="36"/>
-      <c r="DU28" s="72"/>
+      <c r="DU28" s="70"/>
       <c r="DV28" s="37">
         <f t="shared" ref="DV28:DW28" si="32">CX28+CZ28+DB28+DD28+DF28+DH28+DJ28+DL28+DN28+DP28+DR28+DT28</f>
         <v>0</v>
@@ -10470,7 +10654,7 @@
       </c>
       <c r="G29" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H29" s="41">
         <f t="shared" si="4"/>
@@ -10519,7 +10703,9 @@
         <v>40</v>
       </c>
       <c r="V29" s="35"/>
-      <c r="W29" s="35"/>
+      <c r="W29" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X29" s="35"/>
       <c r="Y29" s="35"/>
       <c r="Z29" s="35"/>
@@ -10599,29 +10785,29 @@
       <c r="CV29" s="35"/>
       <c r="CW29" s="35"/>
       <c r="CX29" s="36"/>
-      <c r="CY29" s="72"/>
+      <c r="CY29" s="70"/>
       <c r="CZ29" s="36"/>
-      <c r="DA29" s="72"/>
+      <c r="DA29" s="70"/>
       <c r="DB29" s="36"/>
-      <c r="DC29" s="72"/>
+      <c r="DC29" s="70"/>
       <c r="DD29" s="36"/>
-      <c r="DE29" s="72"/>
+      <c r="DE29" s="70"/>
       <c r="DF29" s="36"/>
-      <c r="DG29" s="72"/>
+      <c r="DG29" s="70"/>
       <c r="DH29" s="36"/>
-      <c r="DI29" s="72"/>
+      <c r="DI29" s="70"/>
       <c r="DJ29" s="36"/>
-      <c r="DK29" s="72"/>
+      <c r="DK29" s="70"/>
       <c r="DL29" s="36"/>
-      <c r="DM29" s="72"/>
+      <c r="DM29" s="70"/>
       <c r="DN29" s="36"/>
-      <c r="DO29" s="72"/>
+      <c r="DO29" s="70"/>
       <c r="DP29" s="36"/>
-      <c r="DQ29" s="72"/>
+      <c r="DQ29" s="70"/>
       <c r="DR29" s="36"/>
-      <c r="DS29" s="72"/>
+      <c r="DS29" s="70"/>
       <c r="DT29" s="36"/>
-      <c r="DU29" s="72"/>
+      <c r="DU29" s="70"/>
       <c r="DV29" s="37">
         <f t="shared" ref="DV29:DW29" si="33">CX29+CZ29+DB29+DD29+DF29+DH29+DJ29+DL29+DN29+DP29+DR29+DT29</f>
         <v>0</v>
@@ -10658,7 +10844,7 @@
       </c>
       <c r="G30" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30" s="41">
         <f t="shared" si="4"/>
@@ -10707,7 +10893,9 @@
         <v>40</v>
       </c>
       <c r="V30" s="35"/>
-      <c r="W30" s="35"/>
+      <c r="W30" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X30" s="35"/>
       <c r="Y30" s="35"/>
       <c r="Z30" s="35"/>
@@ -10787,29 +10975,29 @@
       <c r="CV30" s="35"/>
       <c r="CW30" s="35"/>
       <c r="CX30" s="36"/>
-      <c r="CY30" s="72"/>
+      <c r="CY30" s="70"/>
       <c r="CZ30" s="36"/>
-      <c r="DA30" s="72"/>
+      <c r="DA30" s="70"/>
       <c r="DB30" s="36"/>
-      <c r="DC30" s="72"/>
+      <c r="DC30" s="70"/>
       <c r="DD30" s="36"/>
-      <c r="DE30" s="72"/>
+      <c r="DE30" s="70"/>
       <c r="DF30" s="36"/>
-      <c r="DG30" s="72"/>
+      <c r="DG30" s="70"/>
       <c r="DH30" s="36"/>
-      <c r="DI30" s="72"/>
+      <c r="DI30" s="70"/>
       <c r="DJ30" s="36"/>
-      <c r="DK30" s="72"/>
+      <c r="DK30" s="70"/>
       <c r="DL30" s="36"/>
-      <c r="DM30" s="72"/>
+      <c r="DM30" s="70"/>
       <c r="DN30" s="36"/>
-      <c r="DO30" s="72"/>
+      <c r="DO30" s="70"/>
       <c r="DP30" s="36"/>
-      <c r="DQ30" s="72"/>
+      <c r="DQ30" s="70"/>
       <c r="DR30" s="36"/>
-      <c r="DS30" s="72"/>
+      <c r="DS30" s="70"/>
       <c r="DT30" s="36"/>
-      <c r="DU30" s="72"/>
+      <c r="DU30" s="70"/>
       <c r="DV30" s="37">
         <f t="shared" ref="DV30:DW30" si="34">CX30+CZ30+DB30+DD30+DF30+DH30+DJ30+DL30+DN30+DP30+DR30+DT30</f>
         <v>0</v>
@@ -10845,7 +11033,7 @@
       </c>
       <c r="G31" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" s="41">
         <f t="shared" si="4"/>
@@ -10894,7 +11082,9 @@
         <v>40</v>
       </c>
       <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
+      <c r="W31" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X31" s="35"/>
       <c r="Y31" s="35"/>
       <c r="Z31" s="35"/>
@@ -10974,29 +11164,29 @@
       <c r="CV31" s="35"/>
       <c r="CW31" s="35"/>
       <c r="CX31" s="36"/>
-      <c r="CY31" s="72"/>
+      <c r="CY31" s="70"/>
       <c r="CZ31" s="36"/>
-      <c r="DA31" s="72"/>
+      <c r="DA31" s="70"/>
       <c r="DB31" s="36"/>
-      <c r="DC31" s="72"/>
+      <c r="DC31" s="70"/>
       <c r="DD31" s="36"/>
-      <c r="DE31" s="72"/>
+      <c r="DE31" s="70"/>
       <c r="DF31" s="36"/>
-      <c r="DG31" s="72"/>
+      <c r="DG31" s="70"/>
       <c r="DH31" s="36"/>
-      <c r="DI31" s="72"/>
+      <c r="DI31" s="70"/>
       <c r="DJ31" s="36"/>
-      <c r="DK31" s="72"/>
+      <c r="DK31" s="70"/>
       <c r="DL31" s="36"/>
-      <c r="DM31" s="72"/>
+      <c r="DM31" s="70"/>
       <c r="DN31" s="36"/>
-      <c r="DO31" s="72"/>
+      <c r="DO31" s="70"/>
       <c r="DP31" s="36"/>
-      <c r="DQ31" s="72"/>
+      <c r="DQ31" s="70"/>
       <c r="DR31" s="36"/>
-      <c r="DS31" s="72"/>
+      <c r="DS31" s="70"/>
       <c r="DT31" s="36"/>
-      <c r="DU31" s="72"/>
+      <c r="DU31" s="70"/>
       <c r="DV31" s="37">
         <f t="shared" ref="DV31:DW31" si="35">CX31+CZ31+DB31+DD31+DF31+DH31+DJ31+DL31+DN31+DP31+DR31+DT31</f>
         <v>0</v>
@@ -11032,7 +11222,7 @@
       </c>
       <c r="G32" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H32" s="41">
         <f t="shared" si="4"/>
@@ -11081,7 +11271,9 @@
         <v>40</v>
       </c>
       <c r="V32" s="35"/>
-      <c r="W32" s="35"/>
+      <c r="W32" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X32" s="35"/>
       <c r="Y32" s="35"/>
       <c r="Z32" s="35"/>
@@ -11161,29 +11353,29 @@
       <c r="CV32" s="35"/>
       <c r="CW32" s="35"/>
       <c r="CX32" s="36"/>
-      <c r="CY32" s="72"/>
+      <c r="CY32" s="70"/>
       <c r="CZ32" s="36"/>
-      <c r="DA32" s="72"/>
+      <c r="DA32" s="70"/>
       <c r="DB32" s="36"/>
-      <c r="DC32" s="72"/>
+      <c r="DC32" s="70"/>
       <c r="DD32" s="36"/>
-      <c r="DE32" s="72"/>
+      <c r="DE32" s="70"/>
       <c r="DF32" s="36"/>
-      <c r="DG32" s="72"/>
+      <c r="DG32" s="70"/>
       <c r="DH32" s="36"/>
-      <c r="DI32" s="72"/>
+      <c r="DI32" s="70"/>
       <c r="DJ32" s="36"/>
-      <c r="DK32" s="72"/>
+      <c r="DK32" s="70"/>
       <c r="DL32" s="36"/>
-      <c r="DM32" s="72"/>
+      <c r="DM32" s="70"/>
       <c r="DN32" s="36"/>
-      <c r="DO32" s="72"/>
+      <c r="DO32" s="70"/>
       <c r="DP32" s="36"/>
-      <c r="DQ32" s="72"/>
+      <c r="DQ32" s="70"/>
       <c r="DR32" s="36"/>
-      <c r="DS32" s="72"/>
+      <c r="DS32" s="70"/>
       <c r="DT32" s="36"/>
-      <c r="DU32" s="72"/>
+      <c r="DU32" s="70"/>
       <c r="DV32" s="37">
         <f t="shared" ref="DV32:DW32" si="36">CX32+CZ32+DB32+DD32+DF32+DH32+DJ32+DL32+DN32+DP32+DR32+DT32</f>
         <v>0</v>
@@ -11219,7 +11411,7 @@
       </c>
       <c r="G33" s="40">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H33" s="41">
         <f t="shared" si="4"/>
@@ -11251,7 +11443,7 @@
       </c>
       <c r="O33" s="42">
         <f t="shared" si="11"/>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="P33" s="35" t="s">
         <v>40</v>
@@ -11268,7 +11460,9 @@
         <v>40</v>
       </c>
       <c r="V33" s="35"/>
-      <c r="W33" s="35"/>
+      <c r="W33" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X33" s="35"/>
       <c r="Y33" s="35"/>
       <c r="Z33" s="35"/>
@@ -11348,29 +11542,29 @@
       <c r="CV33" s="35"/>
       <c r="CW33" s="35"/>
       <c r="CX33" s="36"/>
-      <c r="CY33" s="72"/>
+      <c r="CY33" s="70"/>
       <c r="CZ33" s="36"/>
-      <c r="DA33" s="72"/>
+      <c r="DA33" s="70"/>
       <c r="DB33" s="36"/>
-      <c r="DC33" s="72"/>
+      <c r="DC33" s="70"/>
       <c r="DD33" s="36"/>
-      <c r="DE33" s="72"/>
+      <c r="DE33" s="70"/>
       <c r="DF33" s="36"/>
-      <c r="DG33" s="72"/>
+      <c r="DG33" s="70"/>
       <c r="DH33" s="36"/>
-      <c r="DI33" s="72"/>
+      <c r="DI33" s="70"/>
       <c r="DJ33" s="36"/>
-      <c r="DK33" s="72"/>
+      <c r="DK33" s="70"/>
       <c r="DL33" s="36"/>
-      <c r="DM33" s="72"/>
+      <c r="DM33" s="70"/>
       <c r="DN33" s="36"/>
-      <c r="DO33" s="72"/>
+      <c r="DO33" s="70"/>
       <c r="DP33" s="36"/>
-      <c r="DQ33" s="72"/>
+      <c r="DQ33" s="70"/>
       <c r="DR33" s="36"/>
-      <c r="DS33" s="72"/>
+      <c r="DS33" s="70"/>
       <c r="DT33" s="36"/>
-      <c r="DU33" s="72"/>
+      <c r="DU33" s="70"/>
       <c r="DV33" s="37">
         <f t="shared" ref="DV33:DW33" si="37">CX33+CZ33+DB33+DD33+DF33+DH33+DJ33+DL33+DN33+DP33+DR33+DT33</f>
         <v>0</v>
@@ -11398,7 +11592,7 @@
         <v>Pedraza Páez Juan Felipe</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F34" s="30" t="str">
         <f t="shared" si="2"/>
@@ -11406,7 +11600,7 @@
       </c>
       <c r="G34" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H34" s="41">
         <f t="shared" si="4"/>
@@ -11455,7 +11649,9 @@
         <v>40</v>
       </c>
       <c r="V34" s="35"/>
-      <c r="W34" s="35"/>
+      <c r="W34" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X34" s="35"/>
       <c r="Y34" s="35"/>
       <c r="Z34" s="35"/>
@@ -11535,29 +11731,29 @@
       <c r="CV34" s="35"/>
       <c r="CW34" s="35"/>
       <c r="CX34" s="36"/>
-      <c r="CY34" s="72"/>
+      <c r="CY34" s="70"/>
       <c r="CZ34" s="36"/>
-      <c r="DA34" s="72"/>
+      <c r="DA34" s="70"/>
       <c r="DB34" s="36"/>
-      <c r="DC34" s="72"/>
+      <c r="DC34" s="70"/>
       <c r="DD34" s="36"/>
-      <c r="DE34" s="72"/>
+      <c r="DE34" s="70"/>
       <c r="DF34" s="36"/>
-      <c r="DG34" s="72"/>
+      <c r="DG34" s="70"/>
       <c r="DH34" s="36"/>
-      <c r="DI34" s="72"/>
+      <c r="DI34" s="70"/>
       <c r="DJ34" s="36"/>
-      <c r="DK34" s="72"/>
+      <c r="DK34" s="70"/>
       <c r="DL34" s="36"/>
-      <c r="DM34" s="72"/>
+      <c r="DM34" s="70"/>
       <c r="DN34" s="36"/>
-      <c r="DO34" s="72"/>
+      <c r="DO34" s="70"/>
       <c r="DP34" s="36"/>
-      <c r="DQ34" s="72"/>
+      <c r="DQ34" s="70"/>
       <c r="DR34" s="36"/>
-      <c r="DS34" s="72"/>
+      <c r="DS34" s="70"/>
       <c r="DT34" s="36"/>
-      <c r="DU34" s="72"/>
+      <c r="DU34" s="70"/>
       <c r="DV34" s="37">
         <f t="shared" ref="DV34:DW34" si="38">CX34+CZ34+DB34+DD34+DF34+DH34+DJ34+DL34+DN34+DP34+DR34+DT34</f>
         <v>0</v>
@@ -11593,7 +11789,7 @@
       </c>
       <c r="G35" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H35" s="41">
         <f t="shared" si="4"/>
@@ -11642,7 +11838,9 @@
         <v>40</v>
       </c>
       <c r="V35" s="35"/>
-      <c r="W35" s="35"/>
+      <c r="W35" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X35" s="35"/>
       <c r="Y35" s="35"/>
       <c r="Z35" s="35"/>
@@ -11722,29 +11920,29 @@
       <c r="CV35" s="35"/>
       <c r="CW35" s="35"/>
       <c r="CX35" s="36"/>
-      <c r="CY35" s="72"/>
+      <c r="CY35" s="70"/>
       <c r="CZ35" s="36"/>
-      <c r="DA35" s="72"/>
+      <c r="DA35" s="70"/>
       <c r="DB35" s="36"/>
-      <c r="DC35" s="72"/>
+      <c r="DC35" s="70"/>
       <c r="DD35" s="36"/>
-      <c r="DE35" s="72"/>
+      <c r="DE35" s="70"/>
       <c r="DF35" s="36"/>
-      <c r="DG35" s="72"/>
+      <c r="DG35" s="70"/>
       <c r="DH35" s="36"/>
-      <c r="DI35" s="72"/>
+      <c r="DI35" s="70"/>
       <c r="DJ35" s="36"/>
-      <c r="DK35" s="72"/>
+      <c r="DK35" s="70"/>
       <c r="DL35" s="36"/>
-      <c r="DM35" s="72"/>
+      <c r="DM35" s="70"/>
       <c r="DN35" s="36"/>
-      <c r="DO35" s="72"/>
+      <c r="DO35" s="70"/>
       <c r="DP35" s="36"/>
-      <c r="DQ35" s="72"/>
+      <c r="DQ35" s="70"/>
       <c r="DR35" s="36"/>
-      <c r="DS35" s="72"/>
+      <c r="DS35" s="70"/>
       <c r="DT35" s="36"/>
-      <c r="DU35" s="72"/>
+      <c r="DU35" s="70"/>
       <c r="DV35" s="37">
         <f t="shared" ref="DV35:DW35" si="39">CX35+CZ35+DB35+DD35+DF35+DH35+DJ35+DL35+DN35+DP35+DR35+DT35</f>
         <v>0</v>
@@ -11779,7 +11977,7 @@
       </c>
       <c r="G36" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H36" s="41">
         <f t="shared" si="4"/>
@@ -11828,7 +12026,9 @@
         <v>40</v>
       </c>
       <c r="V36" s="35"/>
-      <c r="W36" s="35"/>
+      <c r="W36" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X36" s="35"/>
       <c r="Y36" s="35"/>
       <c r="Z36" s="35"/>
@@ -11908,29 +12108,29 @@
       <c r="CV36" s="35"/>
       <c r="CW36" s="35"/>
       <c r="CX36" s="36"/>
-      <c r="CY36" s="72"/>
+      <c r="CY36" s="70"/>
       <c r="CZ36" s="36"/>
-      <c r="DA36" s="72"/>
+      <c r="DA36" s="70"/>
       <c r="DB36" s="36"/>
-      <c r="DC36" s="72"/>
+      <c r="DC36" s="70"/>
       <c r="DD36" s="36"/>
-      <c r="DE36" s="72"/>
+      <c r="DE36" s="70"/>
       <c r="DF36" s="36"/>
-      <c r="DG36" s="72"/>
+      <c r="DG36" s="70"/>
       <c r="DH36" s="36"/>
-      <c r="DI36" s="72"/>
+      <c r="DI36" s="70"/>
       <c r="DJ36" s="36"/>
-      <c r="DK36" s="72"/>
+      <c r="DK36" s="70"/>
       <c r="DL36" s="36"/>
-      <c r="DM36" s="72"/>
+      <c r="DM36" s="70"/>
       <c r="DN36" s="36"/>
-      <c r="DO36" s="72"/>
+      <c r="DO36" s="70"/>
       <c r="DP36" s="36"/>
-      <c r="DQ36" s="72"/>
+      <c r="DQ36" s="70"/>
       <c r="DR36" s="36"/>
-      <c r="DS36" s="72"/>
+      <c r="DS36" s="70"/>
       <c r="DT36" s="36"/>
-      <c r="DU36" s="72"/>
+      <c r="DU36" s="70"/>
       <c r="DV36" s="37">
         <f t="shared" ref="DV36:DW36" si="40">CX36+CZ36+DB36+DD36+DF36+DH36+DJ36+DL36+DN36+DP36+DR36+DT36</f>
         <v>0</v>
@@ -11966,7 +12166,7 @@
       </c>
       <c r="G37" s="40">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H37" s="41">
         <f t="shared" si="4"/>
@@ -12015,7 +12215,9 @@
         <v>40</v>
       </c>
       <c r="V37" s="35"/>
-      <c r="W37" s="35"/>
+      <c r="W37" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X37" s="35"/>
       <c r="Y37" s="35"/>
       <c r="Z37" s="35"/>
@@ -12095,29 +12297,29 @@
       <c r="CV37" s="35"/>
       <c r="CW37" s="35"/>
       <c r="CX37" s="36"/>
-      <c r="CY37" s="72"/>
+      <c r="CY37" s="70"/>
       <c r="CZ37" s="36"/>
-      <c r="DA37" s="72"/>
+      <c r="DA37" s="70"/>
       <c r="DB37" s="36"/>
-      <c r="DC37" s="72"/>
+      <c r="DC37" s="70"/>
       <c r="DD37" s="36"/>
-      <c r="DE37" s="72"/>
+      <c r="DE37" s="70"/>
       <c r="DF37" s="36"/>
-      <c r="DG37" s="72"/>
+      <c r="DG37" s="70"/>
       <c r="DH37" s="36"/>
-      <c r="DI37" s="72"/>
+      <c r="DI37" s="70"/>
       <c r="DJ37" s="36"/>
-      <c r="DK37" s="72"/>
+      <c r="DK37" s="70"/>
       <c r="DL37" s="36"/>
-      <c r="DM37" s="72"/>
+      <c r="DM37" s="70"/>
       <c r="DN37" s="36"/>
-      <c r="DO37" s="72"/>
+      <c r="DO37" s="70"/>
       <c r="DP37" s="36"/>
-      <c r="DQ37" s="72"/>
+      <c r="DQ37" s="70"/>
       <c r="DR37" s="36"/>
-      <c r="DS37" s="72"/>
+      <c r="DS37" s="70"/>
       <c r="DT37" s="36"/>
-      <c r="DU37" s="72"/>
+      <c r="DU37" s="70"/>
       <c r="DV37" s="37">
         <f t="shared" ref="DV37:DW37" si="41">CX37+CZ37+DB37+DD37+DF37+DH37+DJ37+DL37+DN37+DP37+DR37+DT37</f>
         <v>0</v>
@@ -12153,7 +12355,7 @@
       </c>
       <c r="G38" s="40">
         <f t="shared" ref="G38:G43" si="43">COUNTIF(P38:CR38,"A")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" s="41">
         <f t="shared" ref="H38:H43" si="44">COUNTIF(P38:CR38,"CE")</f>
@@ -12198,7 +12400,9 @@
         <v>40</v>
       </c>
       <c r="V38" s="35"/>
-      <c r="W38" s="35"/>
+      <c r="W38" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X38" s="35"/>
       <c r="Y38" s="35"/>
       <c r="Z38" s="35"/>
@@ -12278,29 +12482,29 @@
       <c r="CV38" s="35"/>
       <c r="CW38" s="35"/>
       <c r="CX38" s="36"/>
-      <c r="CY38" s="72"/>
+      <c r="CY38" s="70"/>
       <c r="CZ38" s="36"/>
-      <c r="DA38" s="72"/>
+      <c r="DA38" s="70"/>
       <c r="DB38" s="36"/>
-      <c r="DC38" s="72"/>
+      <c r="DC38" s="70"/>
       <c r="DD38" s="36"/>
-      <c r="DE38" s="72"/>
+      <c r="DE38" s="70"/>
       <c r="DF38" s="36"/>
-      <c r="DG38" s="72"/>
+      <c r="DG38" s="70"/>
       <c r="DH38" s="36"/>
-      <c r="DI38" s="72"/>
+      <c r="DI38" s="70"/>
       <c r="DJ38" s="36"/>
-      <c r="DK38" s="72"/>
+      <c r="DK38" s="70"/>
       <c r="DL38" s="36"/>
-      <c r="DM38" s="72"/>
+      <c r="DM38" s="70"/>
       <c r="DN38" s="36"/>
-      <c r="DO38" s="72"/>
+      <c r="DO38" s="70"/>
       <c r="DP38" s="36"/>
-      <c r="DQ38" s="72"/>
+      <c r="DQ38" s="70"/>
       <c r="DR38" s="36"/>
-      <c r="DS38" s="72"/>
+      <c r="DS38" s="70"/>
       <c r="DT38" s="36"/>
-      <c r="DU38" s="72"/>
+      <c r="DU38" s="70"/>
       <c r="DV38" s="37"/>
       <c r="DW38" s="38"/>
     </row>
@@ -12330,7 +12534,7 @@
       </c>
       <c r="G39" s="40">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="41">
         <f t="shared" si="44"/>
@@ -12362,7 +12566,7 @@
       </c>
       <c r="O39" s="42">
         <f t="shared" si="51"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="P39" s="35"/>
       <c r="Q39" s="35"/>
@@ -12375,7 +12579,9 @@
         <v>13</v>
       </c>
       <c r="V39" s="35"/>
-      <c r="W39" s="35"/>
+      <c r="W39" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X39" s="35"/>
       <c r="Y39" s="35"/>
       <c r="Z39" s="35"/>
@@ -12455,29 +12661,29 @@
       <c r="CV39" s="35"/>
       <c r="CW39" s="35"/>
       <c r="CX39" s="36"/>
-      <c r="CY39" s="72"/>
+      <c r="CY39" s="70"/>
       <c r="CZ39" s="36"/>
-      <c r="DA39" s="72"/>
+      <c r="DA39" s="70"/>
       <c r="DB39" s="36"/>
-      <c r="DC39" s="72"/>
+      <c r="DC39" s="70"/>
       <c r="DD39" s="36"/>
-      <c r="DE39" s="72"/>
+      <c r="DE39" s="70"/>
       <c r="DF39" s="36"/>
-      <c r="DG39" s="72"/>
+      <c r="DG39" s="70"/>
       <c r="DH39" s="36"/>
-      <c r="DI39" s="72"/>
+      <c r="DI39" s="70"/>
       <c r="DJ39" s="36"/>
-      <c r="DK39" s="72"/>
+      <c r="DK39" s="70"/>
       <c r="DL39" s="36"/>
-      <c r="DM39" s="72"/>
+      <c r="DM39" s="70"/>
       <c r="DN39" s="36"/>
-      <c r="DO39" s="72"/>
+      <c r="DO39" s="70"/>
       <c r="DP39" s="36"/>
-      <c r="DQ39" s="72"/>
+      <c r="DQ39" s="70"/>
       <c r="DR39" s="36"/>
-      <c r="DS39" s="72"/>
+      <c r="DS39" s="70"/>
       <c r="DT39" s="36"/>
-      <c r="DU39" s="72"/>
+      <c r="DU39" s="70"/>
       <c r="DV39" s="37"/>
       <c r="DW39" s="38"/>
     </row>
@@ -12503,7 +12709,7 @@
       </c>
       <c r="F40" s="30" t="str">
         <f t="shared" si="42"/>
-        <v/>
+        <v>CON FALTAS</v>
       </c>
       <c r="G40" s="40">
         <f t="shared" si="43"/>
@@ -12515,7 +12721,7 @@
       </c>
       <c r="I40" s="41">
         <f t="shared" si="45"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="41">
         <f t="shared" si="46"/>
@@ -12539,7 +12745,7 @@
       </c>
       <c r="O40" s="42">
         <f t="shared" si="51"/>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="P40" s="35"/>
       <c r="Q40" s="35"/>
@@ -12552,7 +12758,9 @@
         <v>40</v>
       </c>
       <c r="V40" s="35"/>
-      <c r="W40" s="35"/>
+      <c r="W40" s="35" t="s">
+        <v>13</v>
+      </c>
       <c r="X40" s="35"/>
       <c r="Y40" s="35"/>
       <c r="Z40" s="35"/>
@@ -12632,29 +12840,29 @@
       <c r="CV40" s="35"/>
       <c r="CW40" s="35"/>
       <c r="CX40" s="36"/>
-      <c r="CY40" s="72"/>
+      <c r="CY40" s="70"/>
       <c r="CZ40" s="36"/>
-      <c r="DA40" s="72"/>
+      <c r="DA40" s="70"/>
       <c r="DB40" s="36"/>
-      <c r="DC40" s="72"/>
+      <c r="DC40" s="70"/>
       <c r="DD40" s="36"/>
-      <c r="DE40" s="72"/>
+      <c r="DE40" s="70"/>
       <c r="DF40" s="36"/>
-      <c r="DG40" s="72"/>
+      <c r="DG40" s="70"/>
       <c r="DH40" s="36"/>
-      <c r="DI40" s="72"/>
+      <c r="DI40" s="70"/>
       <c r="DJ40" s="36"/>
-      <c r="DK40" s="72"/>
+      <c r="DK40" s="70"/>
       <c r="DL40" s="36"/>
-      <c r="DM40" s="72"/>
+      <c r="DM40" s="70"/>
       <c r="DN40" s="36"/>
-      <c r="DO40" s="72"/>
+      <c r="DO40" s="70"/>
       <c r="DP40" s="36"/>
-      <c r="DQ40" s="72"/>
+      <c r="DQ40" s="70"/>
       <c r="DR40" s="36"/>
-      <c r="DS40" s="72"/>
+      <c r="DS40" s="70"/>
       <c r="DT40" s="36"/>
-      <c r="DU40" s="72"/>
+      <c r="DU40" s="70"/>
       <c r="DV40" s="37"/>
       <c r="DW40" s="38"/>
     </row>
@@ -12684,7 +12892,7 @@
       </c>
       <c r="G41" s="40">
         <f t="shared" si="43"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H41" s="41">
         <f t="shared" si="44"/>
@@ -12729,7 +12937,9 @@
         <v>40</v>
       </c>
       <c r="V41" s="35"/>
-      <c r="W41" s="35"/>
+      <c r="W41" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X41" s="35"/>
       <c r="Y41" s="35"/>
       <c r="Z41" s="35"/>
@@ -12809,29 +13019,29 @@
       <c r="CV41" s="35"/>
       <c r="CW41" s="35"/>
       <c r="CX41" s="36"/>
-      <c r="CY41" s="72"/>
+      <c r="CY41" s="70"/>
       <c r="CZ41" s="36"/>
-      <c r="DA41" s="72"/>
+      <c r="DA41" s="70"/>
       <c r="DB41" s="36"/>
-      <c r="DC41" s="72"/>
+      <c r="DC41" s="70"/>
       <c r="DD41" s="36"/>
-      <c r="DE41" s="72"/>
+      <c r="DE41" s="70"/>
       <c r="DF41" s="36"/>
-      <c r="DG41" s="72"/>
+      <c r="DG41" s="70"/>
       <c r="DH41" s="36"/>
-      <c r="DI41" s="72"/>
+      <c r="DI41" s="70"/>
       <c r="DJ41" s="36"/>
-      <c r="DK41" s="72"/>
+      <c r="DK41" s="70"/>
       <c r="DL41" s="36"/>
-      <c r="DM41" s="72"/>
+      <c r="DM41" s="70"/>
       <c r="DN41" s="36"/>
-      <c r="DO41" s="72"/>
+      <c r="DO41" s="70"/>
       <c r="DP41" s="36"/>
-      <c r="DQ41" s="72"/>
+      <c r="DQ41" s="70"/>
       <c r="DR41" s="36"/>
-      <c r="DS41" s="72"/>
+      <c r="DS41" s="70"/>
       <c r="DT41" s="36"/>
-      <c r="DU41" s="72"/>
+      <c r="DU41" s="70"/>
       <c r="DV41" s="37"/>
       <c r="DW41" s="38"/>
     </row>
@@ -12861,7 +13071,7 @@
       </c>
       <c r="G42" s="40">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="41">
         <f t="shared" si="44"/>
@@ -12893,7 +13103,7 @@
       </c>
       <c r="O42" s="42">
         <f t="shared" si="51"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="P42" s="35"/>
       <c r="Q42" s="35"/>
@@ -12906,7 +13116,9 @@
         <v>13</v>
       </c>
       <c r="V42" s="35"/>
-      <c r="W42" s="35"/>
+      <c r="W42" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X42" s="35"/>
       <c r="Y42" s="35"/>
       <c r="Z42" s="35"/>
@@ -12986,29 +13198,29 @@
       <c r="CV42" s="35"/>
       <c r="CW42" s="35"/>
       <c r="CX42" s="36"/>
-      <c r="CY42" s="72"/>
+      <c r="CY42" s="70"/>
       <c r="CZ42" s="36"/>
-      <c r="DA42" s="72"/>
+      <c r="DA42" s="70"/>
       <c r="DB42" s="36"/>
-      <c r="DC42" s="72"/>
+      <c r="DC42" s="70"/>
       <c r="DD42" s="36"/>
-      <c r="DE42" s="72"/>
+      <c r="DE42" s="70"/>
       <c r="DF42" s="36"/>
-      <c r="DG42" s="72"/>
+      <c r="DG42" s="70"/>
       <c r="DH42" s="36"/>
-      <c r="DI42" s="72"/>
+      <c r="DI42" s="70"/>
       <c r="DJ42" s="36"/>
-      <c r="DK42" s="72"/>
+      <c r="DK42" s="70"/>
       <c r="DL42" s="36"/>
-      <c r="DM42" s="72"/>
+      <c r="DM42" s="70"/>
       <c r="DN42" s="36"/>
-      <c r="DO42" s="72"/>
+      <c r="DO42" s="70"/>
       <c r="DP42" s="36"/>
-      <c r="DQ42" s="72"/>
+      <c r="DQ42" s="70"/>
       <c r="DR42" s="36"/>
-      <c r="DS42" s="72"/>
+      <c r="DS42" s="70"/>
       <c r="DT42" s="36"/>
-      <c r="DU42" s="72"/>
+      <c r="DU42" s="70"/>
       <c r="DV42" s="37"/>
       <c r="DW42" s="38"/>
     </row>
@@ -13038,7 +13250,7 @@
       </c>
       <c r="G43" s="40">
         <f t="shared" si="43"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" s="41">
         <f t="shared" si="44"/>
@@ -13083,7 +13295,9 @@
         <v>40</v>
       </c>
       <c r="V43" s="35"/>
-      <c r="W43" s="35"/>
+      <c r="W43" s="35" t="s">
+        <v>40</v>
+      </c>
       <c r="X43" s="35"/>
       <c r="Y43" s="35"/>
       <c r="Z43" s="35"/>
@@ -13163,53 +13377,53 @@
       <c r="CV43" s="35"/>
       <c r="CW43" s="35"/>
       <c r="CX43" s="36"/>
-      <c r="CY43" s="72"/>
+      <c r="CY43" s="70"/>
       <c r="CZ43" s="36"/>
-      <c r="DA43" s="72"/>
+      <c r="DA43" s="70"/>
       <c r="DB43" s="36"/>
-      <c r="DC43" s="72"/>
+      <c r="DC43" s="70"/>
       <c r="DD43" s="36"/>
-      <c r="DE43" s="72"/>
+      <c r="DE43" s="70"/>
       <c r="DF43" s="36"/>
-      <c r="DG43" s="72"/>
+      <c r="DG43" s="70"/>
       <c r="DH43" s="36"/>
-      <c r="DI43" s="72"/>
+      <c r="DI43" s="70"/>
       <c r="DJ43" s="36"/>
-      <c r="DK43" s="72"/>
+      <c r="DK43" s="70"/>
       <c r="DL43" s="36"/>
-      <c r="DM43" s="72"/>
+      <c r="DM43" s="70"/>
       <c r="DN43" s="36"/>
-      <c r="DO43" s="72"/>
+      <c r="DO43" s="70"/>
       <c r="DP43" s="36"/>
-      <c r="DQ43" s="72"/>
+      <c r="DQ43" s="70"/>
       <c r="DR43" s="36"/>
-      <c r="DS43" s="72"/>
+      <c r="DS43" s="70"/>
       <c r="DT43" s="36"/>
-      <c r="DU43" s="72"/>
+      <c r="DU43" s="70"/>
       <c r="DV43" s="37"/>
       <c r="DW43" s="38"/>
     </row>
     <row r="44" spans="1:127" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A44" s="73"/>
-      <c r="B44" s="74"/>
-      <c r="C44" s="75"/>
-      <c r="D44" s="75"/>
-      <c r="E44" s="75"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="108" t="s">
-        <v>61</v>
-      </c>
-      <c r="H44" s="109"/>
-      <c r="I44" s="109"/>
-      <c r="J44" s="109"/>
-      <c r="K44" s="109"/>
-      <c r="L44" s="109"/>
-      <c r="M44" s="110"/>
-      <c r="N44" s="111" t="str">
+      <c r="A44" s="71"/>
+      <c r="B44" s="72"/>
+      <c r="C44" s="73"/>
+      <c r="D44" s="73"/>
+      <c r="E44" s="73"/>
+      <c r="F44" s="72"/>
+      <c r="G44" s="121" t="s">
+        <v>60</v>
+      </c>
+      <c r="H44" s="122"/>
+      <c r="I44" s="122"/>
+      <c r="J44" s="122"/>
+      <c r="K44" s="122"/>
+      <c r="L44" s="122"/>
+      <c r="M44" s="123"/>
+      <c r="N44" s="124" t="str">
         <f>G8</f>
         <v>A</v>
       </c>
-      <c r="O44" s="112"/>
+      <c r="O44" s="125"/>
       <c r="P44" s="43">
         <f t="shared" ref="P44:AU44" si="52">COUNTIF(P9:P37,"A")</f>
         <v>29</v>
@@ -13240,7 +13454,7 @@
       </c>
       <c r="W44" s="43">
         <f t="shared" si="52"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="X44" s="43">
         <f t="shared" si="52"/>
@@ -13555,29 +13769,29 @@
         <v>0</v>
       </c>
       <c r="CX44" s="36"/>
-      <c r="CY44" s="72"/>
+      <c r="CY44" s="70"/>
       <c r="CZ44" s="36"/>
-      <c r="DA44" s="72"/>
+      <c r="DA44" s="70"/>
       <c r="DB44" s="36"/>
-      <c r="DC44" s="72"/>
+      <c r="DC44" s="70"/>
       <c r="DD44" s="36"/>
-      <c r="DE44" s="72"/>
+      <c r="DE44" s="70"/>
       <c r="DF44" s="36"/>
-      <c r="DG44" s="72"/>
+      <c r="DG44" s="70"/>
       <c r="DH44" s="36"/>
-      <c r="DI44" s="72"/>
+      <c r="DI44" s="70"/>
       <c r="DJ44" s="36"/>
-      <c r="DK44" s="72"/>
+      <c r="DK44" s="70"/>
       <c r="DL44" s="36"/>
-      <c r="DM44" s="72"/>
+      <c r="DM44" s="70"/>
       <c r="DN44" s="36"/>
-      <c r="DO44" s="72"/>
+      <c r="DO44" s="70"/>
       <c r="DP44" s="36"/>
-      <c r="DQ44" s="72"/>
+      <c r="DQ44" s="70"/>
       <c r="DR44" s="36"/>
-      <c r="DS44" s="72"/>
+      <c r="DS44" s="70"/>
       <c r="DT44" s="36"/>
-      <c r="DU44" s="72"/>
+      <c r="DU44" s="70"/>
       <c r="DV44" s="37">
         <f t="shared" ref="DV44:DW44" si="55">CX44+CZ44+DB44+DD44+DF44+DH44+DJ44+DL44+DN44+DP44+DR44+DT44</f>
         <v>0</v>
@@ -13588,26 +13802,26 @@
       </c>
     </row>
     <row r="45" spans="1:127" ht="15.75" customHeight="1">
-      <c r="A45" s="73"/>
-      <c r="B45" s="74"/>
-      <c r="C45" s="75"/>
-      <c r="D45" s="75"/>
-      <c r="E45" s="75"/>
-      <c r="F45" s="74"/>
-      <c r="G45" s="144" t="s">
+      <c r="A45" s="71"/>
+      <c r="B45" s="72"/>
+      <c r="C45" s="73"/>
+      <c r="D45" s="73"/>
+      <c r="E45" s="73"/>
+      <c r="F45" s="72"/>
+      <c r="G45" s="157" t="s">
         <v>12</v>
       </c>
-      <c r="H45" s="109"/>
-      <c r="I45" s="109"/>
-      <c r="J45" s="109"/>
-      <c r="K45" s="109"/>
-      <c r="L45" s="109"/>
-      <c r="M45" s="110"/>
-      <c r="N45" s="111" t="str">
+      <c r="H45" s="122"/>
+      <c r="I45" s="122"/>
+      <c r="J45" s="122"/>
+      <c r="K45" s="122"/>
+      <c r="L45" s="122"/>
+      <c r="M45" s="123"/>
+      <c r="N45" s="124" t="str">
         <f>H8</f>
         <v>CE</v>
       </c>
-      <c r="O45" s="112"/>
+      <c r="O45" s="125"/>
       <c r="P45" s="43">
         <f t="shared" ref="P45:AU45" si="56">COUNTIF(P9:P37,"CE")</f>
         <v>0</v>
@@ -13953,29 +14167,29 @@
         <v>0</v>
       </c>
       <c r="CX45" s="36"/>
-      <c r="CY45" s="72"/>
+      <c r="CY45" s="70"/>
       <c r="CZ45" s="36"/>
-      <c r="DA45" s="72"/>
+      <c r="DA45" s="70"/>
       <c r="DB45" s="36"/>
-      <c r="DC45" s="72"/>
+      <c r="DC45" s="70"/>
       <c r="DD45" s="36"/>
-      <c r="DE45" s="72"/>
+      <c r="DE45" s="70"/>
       <c r="DF45" s="36"/>
-      <c r="DG45" s="72"/>
+      <c r="DG45" s="70"/>
       <c r="DH45" s="36"/>
-      <c r="DI45" s="72"/>
+      <c r="DI45" s="70"/>
       <c r="DJ45" s="36"/>
-      <c r="DK45" s="72"/>
+      <c r="DK45" s="70"/>
       <c r="DL45" s="36"/>
-      <c r="DM45" s="72"/>
+      <c r="DM45" s="70"/>
       <c r="DN45" s="36"/>
-      <c r="DO45" s="72"/>
+      <c r="DO45" s="70"/>
       <c r="DP45" s="36"/>
-      <c r="DQ45" s="72"/>
+      <c r="DQ45" s="70"/>
       <c r="DR45" s="36"/>
-      <c r="DS45" s="72"/>
+      <c r="DS45" s="70"/>
       <c r="DT45" s="36"/>
-      <c r="DU45" s="72"/>
+      <c r="DU45" s="70"/>
       <c r="DV45" s="37">
         <f t="shared" ref="DV45:DW45" si="59">CX45+CZ45+DB45+DD45+DF45+DH45+DJ45+DL45+DN45+DP45+DR45+DT45</f>
         <v>0</v>
@@ -13986,26 +14200,26 @@
       </c>
     </row>
     <row r="46" spans="1:127" ht="15.75" customHeight="1">
-      <c r="A46" s="73"/>
-      <c r="B46" s="74"/>
-      <c r="C46" s="75"/>
-      <c r="D46" s="75"/>
-      <c r="E46" s="75"/>
-      <c r="F46" s="74"/>
-      <c r="G46" s="145" t="s">
+      <c r="A46" s="71"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="73"/>
+      <c r="F46" s="72"/>
+      <c r="G46" s="158" t="s">
         <v>14</v>
       </c>
-      <c r="H46" s="109"/>
-      <c r="I46" s="109"/>
-      <c r="J46" s="109"/>
-      <c r="K46" s="109"/>
-      <c r="L46" s="109"/>
-      <c r="M46" s="110"/>
-      <c r="N46" s="111" t="str">
+      <c r="H46" s="122"/>
+      <c r="I46" s="122"/>
+      <c r="J46" s="122"/>
+      <c r="K46" s="122"/>
+      <c r="L46" s="122"/>
+      <c r="M46" s="123"/>
+      <c r="N46" s="124" t="str">
         <f>I8</f>
         <v>SE</v>
       </c>
-      <c r="O46" s="112"/>
+      <c r="O46" s="125"/>
       <c r="P46" s="43">
         <f t="shared" ref="P46:AU46" si="60">COUNTIF(P9:P37,"SE")</f>
         <v>0</v>
@@ -14036,7 +14250,7 @@
       </c>
       <c r="W46" s="43">
         <f t="shared" si="60"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" s="43">
         <f t="shared" si="60"/>
@@ -14351,29 +14565,29 @@
         <v>0</v>
       </c>
       <c r="CX46" s="36"/>
-      <c r="CY46" s="72"/>
+      <c r="CY46" s="70"/>
       <c r="CZ46" s="36"/>
-      <c r="DA46" s="72"/>
+      <c r="DA46" s="70"/>
       <c r="DB46" s="36"/>
-      <c r="DC46" s="72"/>
+      <c r="DC46" s="70"/>
       <c r="DD46" s="36"/>
-      <c r="DE46" s="72"/>
+      <c r="DE46" s="70"/>
       <c r="DF46" s="36"/>
-      <c r="DG46" s="72"/>
+      <c r="DG46" s="70"/>
       <c r="DH46" s="36"/>
-      <c r="DI46" s="72"/>
+      <c r="DI46" s="70"/>
       <c r="DJ46" s="36"/>
-      <c r="DK46" s="72"/>
+      <c r="DK46" s="70"/>
       <c r="DL46" s="36"/>
-      <c r="DM46" s="72"/>
+      <c r="DM46" s="70"/>
       <c r="DN46" s="36"/>
-      <c r="DO46" s="72"/>
+      <c r="DO46" s="70"/>
       <c r="DP46" s="36"/>
-      <c r="DQ46" s="72"/>
+      <c r="DQ46" s="70"/>
       <c r="DR46" s="36"/>
-      <c r="DS46" s="72"/>
+      <c r="DS46" s="70"/>
       <c r="DT46" s="36"/>
-      <c r="DU46" s="72"/>
+      <c r="DU46" s="70"/>
       <c r="DV46" s="37">
         <f t="shared" ref="DV46:DW46" si="63">CX46+CZ46+DB46+DD46+DF46+DH46+DJ46+DL46+DN46+DP46+DR46+DT46</f>
         <v>0</v>
@@ -14384,26 +14598,26 @@
       </c>
     </row>
     <row r="47" spans="1:127" ht="15.75" customHeight="1">
-      <c r="A47" s="73"/>
-      <c r="B47" s="74"/>
-      <c r="C47" s="75"/>
-      <c r="D47" s="75"/>
-      <c r="E47" s="75"/>
+      <c r="A47" s="71"/>
+      <c r="B47" s="72"/>
+      <c r="C47" s="73"/>
+      <c r="D47" s="73"/>
+      <c r="E47" s="73"/>
       <c r="F47" s="44"/>
-      <c r="G47" s="146" t="s">
-        <v>62</v>
-      </c>
-      <c r="H47" s="109"/>
-      <c r="I47" s="109"/>
-      <c r="J47" s="109"/>
-      <c r="K47" s="109"/>
-      <c r="L47" s="109"/>
-      <c r="M47" s="110"/>
-      <c r="N47" s="111" t="str">
+      <c r="G47" s="159" t="s">
+        <v>61</v>
+      </c>
+      <c r="H47" s="122"/>
+      <c r="I47" s="122"/>
+      <c r="J47" s="122"/>
+      <c r="K47" s="122"/>
+      <c r="L47" s="122"/>
+      <c r="M47" s="123"/>
+      <c r="N47" s="124" t="str">
         <f>J8</f>
         <v>INC</v>
       </c>
-      <c r="O47" s="112"/>
+      <c r="O47" s="125"/>
       <c r="P47" s="43">
         <f t="shared" ref="P47:AU47" si="64">COUNTIF(P9:P37,"INC")</f>
         <v>0</v>
@@ -14749,29 +14963,29 @@
         <v>0</v>
       </c>
       <c r="CX47" s="36"/>
-      <c r="CY47" s="72"/>
+      <c r="CY47" s="70"/>
       <c r="CZ47" s="36"/>
-      <c r="DA47" s="72"/>
+      <c r="DA47" s="70"/>
       <c r="DB47" s="36"/>
-      <c r="DC47" s="72"/>
+      <c r="DC47" s="70"/>
       <c r="DD47" s="36"/>
-      <c r="DE47" s="72"/>
+      <c r="DE47" s="70"/>
       <c r="DF47" s="36"/>
-      <c r="DG47" s="72"/>
+      <c r="DG47" s="70"/>
       <c r="DH47" s="36"/>
-      <c r="DI47" s="72"/>
+      <c r="DI47" s="70"/>
       <c r="DJ47" s="36"/>
-      <c r="DK47" s="72"/>
+      <c r="DK47" s="70"/>
       <c r="DL47" s="36"/>
-      <c r="DM47" s="72"/>
+      <c r="DM47" s="70"/>
       <c r="DN47" s="36"/>
-      <c r="DO47" s="72"/>
+      <c r="DO47" s="70"/>
       <c r="DP47" s="36"/>
-      <c r="DQ47" s="72"/>
+      <c r="DQ47" s="70"/>
       <c r="DR47" s="36"/>
-      <c r="DS47" s="72"/>
+      <c r="DS47" s="70"/>
       <c r="DT47" s="36"/>
-      <c r="DU47" s="72"/>
+      <c r="DU47" s="70"/>
       <c r="DV47" s="37">
         <f t="shared" ref="DV47:DW47" si="67">CX47+CZ47+DB47+DD47+DF47+DH47+DJ47+DL47+DN47+DP47+DR47+DT47</f>
         <v>0</v>
@@ -14782,26 +14996,26 @@
       </c>
     </row>
     <row r="48" spans="1:127" ht="15.75" customHeight="1">
-      <c r="A48" s="73"/>
-      <c r="B48" s="74"/>
-      <c r="C48" s="75"/>
-      <c r="D48" s="75"/>
-      <c r="E48" s="75"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="140" t="s">
-        <v>63</v>
-      </c>
-      <c r="H48" s="109"/>
-      <c r="I48" s="109"/>
-      <c r="J48" s="109"/>
-      <c r="K48" s="109"/>
-      <c r="L48" s="109"/>
-      <c r="M48" s="110"/>
-      <c r="N48" s="111" t="str">
+      <c r="A48" s="71"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="73"/>
+      <c r="D48" s="73"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="72"/>
+      <c r="G48" s="153" t="s">
+        <v>62</v>
+      </c>
+      <c r="H48" s="122"/>
+      <c r="I48" s="122"/>
+      <c r="J48" s="122"/>
+      <c r="K48" s="122"/>
+      <c r="L48" s="122"/>
+      <c r="M48" s="123"/>
+      <c r="N48" s="124" t="str">
         <f>K8</f>
         <v>LIC</v>
       </c>
-      <c r="O48" s="112"/>
+      <c r="O48" s="125"/>
       <c r="P48" s="43">
         <f t="shared" ref="P48:AU48" si="68">COUNTIF(P9:P37,"LIC")</f>
         <v>0</v>
@@ -15147,29 +15361,29 @@
         <v>0</v>
       </c>
       <c r="CX48" s="36"/>
-      <c r="CY48" s="72"/>
+      <c r="CY48" s="70"/>
       <c r="CZ48" s="36"/>
-      <c r="DA48" s="72"/>
+      <c r="DA48" s="70"/>
       <c r="DB48" s="36"/>
-      <c r="DC48" s="72"/>
+      <c r="DC48" s="70"/>
       <c r="DD48" s="36"/>
-      <c r="DE48" s="72"/>
+      <c r="DE48" s="70"/>
       <c r="DF48" s="36"/>
-      <c r="DG48" s="72"/>
+      <c r="DG48" s="70"/>
       <c r="DH48" s="36"/>
-      <c r="DI48" s="72"/>
+      <c r="DI48" s="70"/>
       <c r="DJ48" s="36"/>
-      <c r="DK48" s="72"/>
+      <c r="DK48" s="70"/>
       <c r="DL48" s="36"/>
-      <c r="DM48" s="72"/>
+      <c r="DM48" s="70"/>
       <c r="DN48" s="36"/>
-      <c r="DO48" s="72"/>
+      <c r="DO48" s="70"/>
       <c r="DP48" s="36"/>
-      <c r="DQ48" s="72"/>
+      <c r="DQ48" s="70"/>
       <c r="DR48" s="36"/>
-      <c r="DS48" s="72"/>
+      <c r="DS48" s="70"/>
       <c r="DT48" s="36"/>
-      <c r="DU48" s="72"/>
+      <c r="DU48" s="70"/>
       <c r="DV48" s="37">
         <f t="shared" ref="DV48:DW48" si="71">CX48+CZ48+DB48+DD48+DF48+DH48+DJ48+DL48+DN48+DP48+DR48+DT48</f>
         <v>0</v>
@@ -15180,26 +15394,26 @@
       </c>
     </row>
     <row r="49" spans="1:127" ht="15.75" customHeight="1">
-      <c r="A49" s="73"/>
-      <c r="B49" s="74"/>
-      <c r="C49" s="75"/>
-      <c r="D49" s="75"/>
-      <c r="E49" s="75"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="148" t="s">
-        <v>64</v>
-      </c>
-      <c r="H49" s="109"/>
-      <c r="I49" s="109"/>
-      <c r="J49" s="109"/>
-      <c r="K49" s="109"/>
-      <c r="L49" s="109"/>
-      <c r="M49" s="110"/>
-      <c r="N49" s="111" t="str">
+      <c r="A49" s="71"/>
+      <c r="B49" s="72"/>
+      <c r="C49" s="73"/>
+      <c r="D49" s="73"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="72"/>
+      <c r="G49" s="161" t="s">
+        <v>63</v>
+      </c>
+      <c r="H49" s="122"/>
+      <c r="I49" s="122"/>
+      <c r="J49" s="122"/>
+      <c r="K49" s="122"/>
+      <c r="L49" s="122"/>
+      <c r="M49" s="123"/>
+      <c r="N49" s="124" t="str">
         <f>L8</f>
         <v>CLM</v>
       </c>
-      <c r="O49" s="112"/>
+      <c r="O49" s="125"/>
       <c r="P49" s="43">
         <f t="shared" ref="P49:AU49" si="72">COUNTIF(P9:P37,"CLM")</f>
         <v>0</v>
@@ -15545,29 +15759,29 @@
         <v>0</v>
       </c>
       <c r="CX49" s="36"/>
-      <c r="CY49" s="72"/>
+      <c r="CY49" s="70"/>
       <c r="CZ49" s="36"/>
-      <c r="DA49" s="72"/>
+      <c r="DA49" s="70"/>
       <c r="DB49" s="36"/>
-      <c r="DC49" s="72"/>
+      <c r="DC49" s="70"/>
       <c r="DD49" s="36"/>
-      <c r="DE49" s="72"/>
+      <c r="DE49" s="70"/>
       <c r="DF49" s="36"/>
-      <c r="DG49" s="72"/>
+      <c r="DG49" s="70"/>
       <c r="DH49" s="36"/>
-      <c r="DI49" s="72"/>
+      <c r="DI49" s="70"/>
       <c r="DJ49" s="36"/>
-      <c r="DK49" s="72"/>
+      <c r="DK49" s="70"/>
       <c r="DL49" s="36"/>
-      <c r="DM49" s="72"/>
+      <c r="DM49" s="70"/>
       <c r="DN49" s="36"/>
-      <c r="DO49" s="72"/>
+      <c r="DO49" s="70"/>
       <c r="DP49" s="36"/>
-      <c r="DQ49" s="72"/>
+      <c r="DQ49" s="70"/>
       <c r="DR49" s="36"/>
-      <c r="DS49" s="72"/>
+      <c r="DS49" s="70"/>
       <c r="DT49" s="36"/>
-      <c r="DU49" s="72"/>
+      <c r="DU49" s="70"/>
       <c r="DV49" s="37">
         <f t="shared" ref="DV49:DW49" si="75">CX49+CZ49+DB49+DD49+DF49+DH49+DJ49+DL49+DN49+DP49+DR49+DT49</f>
         <v>0</v>
@@ -15578,26 +15792,26 @@
       </c>
     </row>
     <row r="50" spans="1:127" ht="15.75" customHeight="1">
-      <c r="A50" s="73"/>
-      <c r="B50" s="74"/>
-      <c r="C50" s="75"/>
-      <c r="D50" s="75"/>
-      <c r="E50" s="75"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="149" t="s">
-        <v>65</v>
-      </c>
-      <c r="H50" s="109"/>
-      <c r="I50" s="109"/>
-      <c r="J50" s="109"/>
-      <c r="K50" s="109"/>
-      <c r="L50" s="109"/>
-      <c r="M50" s="110"/>
-      <c r="N50" s="111" t="str">
+      <c r="A50" s="71"/>
+      <c r="B50" s="72"/>
+      <c r="C50" s="73"/>
+      <c r="D50" s="73"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="72"/>
+      <c r="G50" s="162" t="s">
+        <v>64</v>
+      </c>
+      <c r="H50" s="122"/>
+      <c r="I50" s="122"/>
+      <c r="J50" s="122"/>
+      <c r="K50" s="122"/>
+      <c r="L50" s="122"/>
+      <c r="M50" s="123"/>
+      <c r="N50" s="124" t="str">
         <f>M8</f>
         <v>SFF</v>
       </c>
-      <c r="O50" s="112"/>
+      <c r="O50" s="125"/>
       <c r="P50" s="43">
         <f t="shared" ref="P50:AU50" si="76">COUNTIF(P9:P37,"SFF")</f>
         <v>0</v>
@@ -15943,29 +16157,29 @@
         <v>0</v>
       </c>
       <c r="CX50" s="36"/>
-      <c r="CY50" s="72"/>
+      <c r="CY50" s="70"/>
       <c r="CZ50" s="36"/>
-      <c r="DA50" s="72"/>
+      <c r="DA50" s="70"/>
       <c r="DB50" s="36"/>
-      <c r="DC50" s="72"/>
+      <c r="DC50" s="70"/>
       <c r="DD50" s="36"/>
-      <c r="DE50" s="72"/>
+      <c r="DE50" s="70"/>
       <c r="DF50" s="36"/>
-      <c r="DG50" s="72"/>
+      <c r="DG50" s="70"/>
       <c r="DH50" s="36"/>
-      <c r="DI50" s="72"/>
+      <c r="DI50" s="70"/>
       <c r="DJ50" s="36"/>
-      <c r="DK50" s="72"/>
+      <c r="DK50" s="70"/>
       <c r="DL50" s="36"/>
-      <c r="DM50" s="72"/>
+      <c r="DM50" s="70"/>
       <c r="DN50" s="36"/>
-      <c r="DO50" s="72"/>
+      <c r="DO50" s="70"/>
       <c r="DP50" s="36"/>
-      <c r="DQ50" s="72"/>
+      <c r="DQ50" s="70"/>
       <c r="DR50" s="36"/>
-      <c r="DS50" s="72"/>
+      <c r="DS50" s="70"/>
       <c r="DT50" s="36"/>
-      <c r="DU50" s="72"/>
+      <c r="DU50" s="70"/>
       <c r="DV50" s="37">
         <f t="shared" ref="DV50:DW50" si="79">CX50+CZ50+DB50+DD50+DF50+DH50+DJ50+DL50+DN50+DP50+DR50+DT50</f>
         <v>0</v>
@@ -15976,26 +16190,26 @@
       </c>
     </row>
     <row r="51" spans="1:127" ht="15.75" customHeight="1">
-      <c r="A51" s="73"/>
-      <c r="B51" s="74"/>
-      <c r="C51" s="75"/>
-      <c r="D51" s="75"/>
-      <c r="E51" s="75"/>
-      <c r="F51" s="74"/>
-      <c r="G51" s="150" t="s">
-        <v>66</v>
-      </c>
-      <c r="H51" s="109"/>
-      <c r="I51" s="109"/>
-      <c r="J51" s="109"/>
-      <c r="K51" s="109"/>
-      <c r="L51" s="109"/>
-      <c r="M51" s="110"/>
-      <c r="N51" s="111" t="str">
+      <c r="A51" s="71"/>
+      <c r="B51" s="72"/>
+      <c r="C51" s="73"/>
+      <c r="D51" s="73"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="72"/>
+      <c r="G51" s="163" t="s">
+        <v>65</v>
+      </c>
+      <c r="H51" s="122"/>
+      <c r="I51" s="122"/>
+      <c r="J51" s="122"/>
+      <c r="K51" s="122"/>
+      <c r="L51" s="122"/>
+      <c r="M51" s="123"/>
+      <c r="N51" s="124" t="str">
         <f>N8</f>
         <v>RET</v>
       </c>
-      <c r="O51" s="112"/>
+      <c r="O51" s="125"/>
       <c r="P51" s="43">
         <f t="shared" ref="P51:AU51" si="80">COUNTIF(P9:P37,"RET")</f>
         <v>0</v>
@@ -16341,29 +16555,29 @@
         <v>0</v>
       </c>
       <c r="CX51" s="36"/>
-      <c r="CY51" s="72"/>
+      <c r="CY51" s="70"/>
       <c r="CZ51" s="36"/>
-      <c r="DA51" s="72"/>
+      <c r="DA51" s="70"/>
       <c r="DB51" s="36"/>
-      <c r="DC51" s="72"/>
+      <c r="DC51" s="70"/>
       <c r="DD51" s="36"/>
-      <c r="DE51" s="72"/>
+      <c r="DE51" s="70"/>
       <c r="DF51" s="36"/>
-      <c r="DG51" s="72"/>
+      <c r="DG51" s="70"/>
       <c r="DH51" s="36"/>
-      <c r="DI51" s="72"/>
+      <c r="DI51" s="70"/>
       <c r="DJ51" s="36"/>
-      <c r="DK51" s="72"/>
+      <c r="DK51" s="70"/>
       <c r="DL51" s="36"/>
-      <c r="DM51" s="72"/>
+      <c r="DM51" s="70"/>
       <c r="DN51" s="36"/>
-      <c r="DO51" s="72"/>
+      <c r="DO51" s="70"/>
       <c r="DP51" s="36"/>
-      <c r="DQ51" s="72"/>
+      <c r="DQ51" s="70"/>
       <c r="DR51" s="36"/>
-      <c r="DS51" s="72"/>
+      <c r="DS51" s="70"/>
       <c r="DT51" s="36"/>
-      <c r="DU51" s="72"/>
+      <c r="DU51" s="70"/>
       <c r="DV51" s="37">
         <f t="shared" ref="DV51:DW51" si="83">CX51+CZ51+DB51+DD51+DF51+DH51+DJ51+DL51+DN51+DP51+DR51+DT51</f>
         <v>0</v>
@@ -16374,399 +16588,399 @@
       </c>
     </row>
     <row r="52" spans="1:127" ht="15.75" customHeight="1">
-      <c r="A52" s="73"/>
-      <c r="B52" s="74"/>
-      <c r="C52" s="75"/>
-      <c r="D52" s="75"/>
-      <c r="E52" s="75"/>
-      <c r="F52" s="74"/>
-      <c r="G52" s="75"/>
-      <c r="H52" s="75"/>
-      <c r="I52" s="75"/>
-      <c r="J52" s="75"/>
-      <c r="K52" s="75"/>
-      <c r="L52" s="75"/>
-      <c r="M52" s="75"/>
-      <c r="N52" s="75"/>
-      <c r="O52" s="75"/>
-      <c r="P52" s="75"/>
-      <c r="Q52" s="75"/>
-      <c r="R52" s="75"/>
-      <c r="S52" s="75"/>
-      <c r="T52" s="75"/>
-      <c r="U52" s="75"/>
-      <c r="V52" s="75"/>
-      <c r="W52" s="75"/>
-      <c r="X52" s="75"/>
-      <c r="Y52" s="75"/>
-      <c r="Z52" s="75"/>
-      <c r="AA52" s="75"/>
-      <c r="AB52" s="75"/>
-      <c r="AC52" s="75"/>
-      <c r="AD52" s="75"/>
-      <c r="AE52" s="75"/>
-      <c r="AF52" s="75"/>
-      <c r="AG52" s="75"/>
-      <c r="AH52" s="75"/>
-      <c r="AI52" s="75"/>
-      <c r="AJ52" s="75"/>
-      <c r="AK52" s="75"/>
-      <c r="AL52" s="75"/>
-      <c r="AM52" s="75"/>
-      <c r="AN52" s="75"/>
-      <c r="AO52" s="75"/>
-      <c r="AP52" s="75"/>
-      <c r="AQ52" s="75"/>
-      <c r="AR52" s="75"/>
-      <c r="AS52" s="75"/>
-      <c r="AT52" s="75"/>
-      <c r="AU52" s="75"/>
-      <c r="AV52" s="75"/>
-      <c r="AW52" s="75"/>
-      <c r="AX52" s="75"/>
-      <c r="AY52" s="75"/>
-      <c r="AZ52" s="75"/>
-      <c r="BA52" s="75"/>
-      <c r="BB52" s="75"/>
-      <c r="BC52" s="75"/>
-      <c r="BD52" s="75"/>
-      <c r="BE52" s="75"/>
-      <c r="BF52" s="75"/>
-      <c r="BG52" s="75"/>
-      <c r="BH52" s="75"/>
-      <c r="BI52" s="75"/>
-      <c r="BJ52" s="75"/>
-      <c r="BK52" s="75"/>
-      <c r="BL52" s="75"/>
-      <c r="BM52" s="75"/>
-      <c r="BN52" s="75"/>
-      <c r="BO52" s="75"/>
-      <c r="BP52" s="75"/>
-      <c r="BQ52" s="75"/>
-      <c r="BR52" s="75"/>
-      <c r="BS52" s="75"/>
-      <c r="BT52" s="75"/>
-      <c r="BU52" s="75"/>
-      <c r="BV52" s="75"/>
-      <c r="BW52" s="75"/>
-      <c r="BX52" s="75"/>
-      <c r="BY52" s="75"/>
-      <c r="BZ52" s="75"/>
-      <c r="CA52" s="75"/>
-      <c r="CB52" s="75"/>
-      <c r="CC52" s="75"/>
-      <c r="CD52" s="75"/>
-      <c r="CE52" s="75"/>
-      <c r="CF52" s="75"/>
-      <c r="CG52" s="75"/>
-      <c r="CH52" s="75"/>
-      <c r="CI52" s="75"/>
-      <c r="CJ52" s="75"/>
-      <c r="CK52" s="75"/>
-      <c r="CL52" s="75"/>
-      <c r="CM52" s="75"/>
-      <c r="CN52" s="75"/>
-      <c r="CO52" s="75"/>
-      <c r="CP52" s="75"/>
-      <c r="CQ52" s="75"/>
-      <c r="CR52" s="75"/>
-      <c r="CS52" s="75"/>
-      <c r="CT52" s="75"/>
-      <c r="CU52" s="75"/>
-      <c r="CV52" s="75"/>
-      <c r="CW52" s="75"/>
-      <c r="CX52" s="75"/>
-      <c r="CY52" s="75"/>
-      <c r="CZ52" s="75"/>
-      <c r="DA52" s="75"/>
-      <c r="DB52" s="75"/>
-      <c r="DC52" s="75"/>
-      <c r="DD52" s="75"/>
-      <c r="DE52" s="75"/>
-      <c r="DF52" s="75"/>
-      <c r="DG52" s="75"/>
-      <c r="DH52" s="75"/>
-      <c r="DI52" s="75"/>
-      <c r="DJ52" s="75"/>
-      <c r="DK52" s="75"/>
-      <c r="DL52" s="75"/>
-      <c r="DM52" s="75"/>
-      <c r="DN52" s="75"/>
-      <c r="DO52" s="75"/>
-      <c r="DP52" s="75"/>
-      <c r="DQ52" s="75"/>
-      <c r="DR52" s="75"/>
-      <c r="DS52" s="75"/>
-      <c r="DT52" s="75"/>
-      <c r="DU52" s="75"/>
-      <c r="DV52" s="75"/>
-      <c r="DW52" s="75"/>
+      <c r="A52" s="71"/>
+      <c r="B52" s="72"/>
+      <c r="C52" s="73"/>
+      <c r="D52" s="73"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="72"/>
+      <c r="G52" s="73"/>
+      <c r="H52" s="73"/>
+      <c r="I52" s="73"/>
+      <c r="J52" s="73"/>
+      <c r="K52" s="73"/>
+      <c r="L52" s="73"/>
+      <c r="M52" s="73"/>
+      <c r="N52" s="73"/>
+      <c r="O52" s="73"/>
+      <c r="P52" s="73"/>
+      <c r="Q52" s="73"/>
+      <c r="R52" s="73"/>
+      <c r="S52" s="73"/>
+      <c r="T52" s="73"/>
+      <c r="U52" s="73"/>
+      <c r="V52" s="73"/>
+      <c r="W52" s="73"/>
+      <c r="X52" s="73"/>
+      <c r="Y52" s="73"/>
+      <c r="Z52" s="73"/>
+      <c r="AA52" s="73"/>
+      <c r="AB52" s="73"/>
+      <c r="AC52" s="73"/>
+      <c r="AD52" s="73"/>
+      <c r="AE52" s="73"/>
+      <c r="AF52" s="73"/>
+      <c r="AG52" s="73"/>
+      <c r="AH52" s="73"/>
+      <c r="AI52" s="73"/>
+      <c r="AJ52" s="73"/>
+      <c r="AK52" s="73"/>
+      <c r="AL52" s="73"/>
+      <c r="AM52" s="73"/>
+      <c r="AN52" s="73"/>
+      <c r="AO52" s="73"/>
+      <c r="AP52" s="73"/>
+      <c r="AQ52" s="73"/>
+      <c r="AR52" s="73"/>
+      <c r="AS52" s="73"/>
+      <c r="AT52" s="73"/>
+      <c r="AU52" s="73"/>
+      <c r="AV52" s="73"/>
+      <c r="AW52" s="73"/>
+      <c r="AX52" s="73"/>
+      <c r="AY52" s="73"/>
+      <c r="AZ52" s="73"/>
+      <c r="BA52" s="73"/>
+      <c r="BB52" s="73"/>
+      <c r="BC52" s="73"/>
+      <c r="BD52" s="73"/>
+      <c r="BE52" s="73"/>
+      <c r="BF52" s="73"/>
+      <c r="BG52" s="73"/>
+      <c r="BH52" s="73"/>
+      <c r="BI52" s="73"/>
+      <c r="BJ52" s="73"/>
+      <c r="BK52" s="73"/>
+      <c r="BL52" s="73"/>
+      <c r="BM52" s="73"/>
+      <c r="BN52" s="73"/>
+      <c r="BO52" s="73"/>
+      <c r="BP52" s="73"/>
+      <c r="BQ52" s="73"/>
+      <c r="BR52" s="73"/>
+      <c r="BS52" s="73"/>
+      <c r="BT52" s="73"/>
+      <c r="BU52" s="73"/>
+      <c r="BV52" s="73"/>
+      <c r="BW52" s="73"/>
+      <c r="BX52" s="73"/>
+      <c r="BY52" s="73"/>
+      <c r="BZ52" s="73"/>
+      <c r="CA52" s="73"/>
+      <c r="CB52" s="73"/>
+      <c r="CC52" s="73"/>
+      <c r="CD52" s="73"/>
+      <c r="CE52" s="73"/>
+      <c r="CF52" s="73"/>
+      <c r="CG52" s="73"/>
+      <c r="CH52" s="73"/>
+      <c r="CI52" s="73"/>
+      <c r="CJ52" s="73"/>
+      <c r="CK52" s="73"/>
+      <c r="CL52" s="73"/>
+      <c r="CM52" s="73"/>
+      <c r="CN52" s="73"/>
+      <c r="CO52" s="73"/>
+      <c r="CP52" s="73"/>
+      <c r="CQ52" s="73"/>
+      <c r="CR52" s="73"/>
+      <c r="CS52" s="73"/>
+      <c r="CT52" s="73"/>
+      <c r="CU52" s="73"/>
+      <c r="CV52" s="73"/>
+      <c r="CW52" s="73"/>
+      <c r="CX52" s="73"/>
+      <c r="CY52" s="73"/>
+      <c r="CZ52" s="73"/>
+      <c r="DA52" s="73"/>
+      <c r="DB52" s="73"/>
+      <c r="DC52" s="73"/>
+      <c r="DD52" s="73"/>
+      <c r="DE52" s="73"/>
+      <c r="DF52" s="73"/>
+      <c r="DG52" s="73"/>
+      <c r="DH52" s="73"/>
+      <c r="DI52" s="73"/>
+      <c r="DJ52" s="73"/>
+      <c r="DK52" s="73"/>
+      <c r="DL52" s="73"/>
+      <c r="DM52" s="73"/>
+      <c r="DN52" s="73"/>
+      <c r="DO52" s="73"/>
+      <c r="DP52" s="73"/>
+      <c r="DQ52" s="73"/>
+      <c r="DR52" s="73"/>
+      <c r="DS52" s="73"/>
+      <c r="DT52" s="73"/>
+      <c r="DU52" s="73"/>
+      <c r="DV52" s="73"/>
+      <c r="DW52" s="73"/>
     </row>
     <row r="53" spans="1:127" ht="15.75" customHeight="1">
-      <c r="A53" s="73"/>
-      <c r="B53" s="74"/>
-      <c r="C53" s="75"/>
-      <c r="D53" s="75"/>
-      <c r="E53" s="75"/>
-      <c r="F53" s="74"/>
-      <c r="G53" s="75"/>
-      <c r="H53" s="75"/>
-      <c r="I53" s="75"/>
-      <c r="J53" s="75"/>
-      <c r="K53" s="75"/>
-      <c r="L53" s="75"/>
-      <c r="M53" s="75"/>
-      <c r="N53" s="75"/>
-      <c r="O53" s="75"/>
-      <c r="P53" s="75"/>
-      <c r="Q53" s="75"/>
-      <c r="R53" s="75"/>
-      <c r="S53" s="75"/>
-      <c r="T53" s="75"/>
-      <c r="U53" s="75"/>
-      <c r="V53" s="75"/>
-      <c r="W53" s="75"/>
-      <c r="X53" s="75"/>
-      <c r="Y53" s="75"/>
-      <c r="Z53" s="75"/>
-      <c r="AA53" s="75"/>
-      <c r="AB53" s="75"/>
-      <c r="AC53" s="75"/>
-      <c r="AD53" s="75"/>
-      <c r="AE53" s="75"/>
-      <c r="AF53" s="75"/>
-      <c r="AG53" s="75"/>
-      <c r="AH53" s="75"/>
-      <c r="AI53" s="75"/>
-      <c r="AJ53" s="75"/>
-      <c r="AK53" s="75"/>
-      <c r="AL53" s="75"/>
-      <c r="AM53" s="75"/>
-      <c r="AN53" s="75"/>
-      <c r="AO53" s="75"/>
-      <c r="AP53" s="75"/>
-      <c r="AQ53" s="75"/>
-      <c r="AR53" s="75"/>
-      <c r="AS53" s="75"/>
-      <c r="AT53" s="75"/>
-      <c r="AU53" s="75"/>
-      <c r="AV53" s="75"/>
-      <c r="AW53" s="75"/>
-      <c r="AX53" s="75"/>
-      <c r="AY53" s="75"/>
-      <c r="AZ53" s="75"/>
-      <c r="BA53" s="75"/>
-      <c r="BB53" s="75"/>
-      <c r="BC53" s="75"/>
-      <c r="BD53" s="75"/>
-      <c r="BE53" s="75"/>
-      <c r="BF53" s="75"/>
-      <c r="BG53" s="75"/>
-      <c r="BH53" s="75"/>
-      <c r="BI53" s="75"/>
-      <c r="BJ53" s="75"/>
-      <c r="BK53" s="75"/>
-      <c r="BL53" s="75"/>
-      <c r="BM53" s="75"/>
-      <c r="BN53" s="75"/>
-      <c r="BO53" s="75"/>
-      <c r="BP53" s="75"/>
-      <c r="BQ53" s="75"/>
-      <c r="BR53" s="75"/>
-      <c r="BS53" s="75"/>
-      <c r="BT53" s="75"/>
-      <c r="BU53" s="75"/>
-      <c r="BV53" s="75"/>
-      <c r="BW53" s="75"/>
-      <c r="BX53" s="75"/>
-      <c r="BY53" s="75"/>
-      <c r="BZ53" s="75"/>
-      <c r="CA53" s="75"/>
-      <c r="CB53" s="75"/>
-      <c r="CC53" s="75"/>
-      <c r="CD53" s="75"/>
-      <c r="CE53" s="75"/>
-      <c r="CF53" s="75"/>
-      <c r="CG53" s="75"/>
-      <c r="CH53" s="75"/>
-      <c r="CI53" s="75"/>
-      <c r="CJ53" s="75"/>
-      <c r="CK53" s="75"/>
-      <c r="CL53" s="75"/>
-      <c r="CM53" s="75"/>
-      <c r="CN53" s="75"/>
-      <c r="CO53" s="75"/>
-      <c r="CP53" s="75"/>
-      <c r="CQ53" s="75"/>
-      <c r="CR53" s="75"/>
-      <c r="CS53" s="75"/>
-      <c r="CT53" s="75"/>
-      <c r="CU53" s="75"/>
-      <c r="CV53" s="75"/>
-      <c r="CW53" s="75"/>
-      <c r="CX53" s="75"/>
-      <c r="CY53" s="75"/>
-      <c r="CZ53" s="75"/>
-      <c r="DA53" s="75"/>
-      <c r="DB53" s="75"/>
-      <c r="DC53" s="75"/>
-      <c r="DD53" s="75"/>
-      <c r="DE53" s="75"/>
-      <c r="DF53" s="75"/>
-      <c r="DG53" s="75"/>
-      <c r="DH53" s="75"/>
-      <c r="DI53" s="75"/>
-      <c r="DJ53" s="75"/>
-      <c r="DK53" s="75"/>
-      <c r="DL53" s="75"/>
-      <c r="DM53" s="75"/>
-      <c r="DN53" s="75"/>
-      <c r="DO53" s="75"/>
-      <c r="DP53" s="75"/>
-      <c r="DQ53" s="75"/>
-      <c r="DR53" s="75"/>
-      <c r="DS53" s="75"/>
-      <c r="DT53" s="75"/>
-      <c r="DU53" s="75"/>
-      <c r="DV53" s="75"/>
-      <c r="DW53" s="75"/>
+      <c r="A53" s="71"/>
+      <c r="B53" s="72"/>
+      <c r="C53" s="73"/>
+      <c r="D53" s="73"/>
+      <c r="E53" s="73"/>
+      <c r="F53" s="72"/>
+      <c r="G53" s="73"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73"/>
+      <c r="J53" s="73"/>
+      <c r="K53" s="73"/>
+      <c r="L53" s="73"/>
+      <c r="M53" s="73"/>
+      <c r="N53" s="73"/>
+      <c r="O53" s="73"/>
+      <c r="P53" s="73"/>
+      <c r="Q53" s="73"/>
+      <c r="R53" s="73"/>
+      <c r="S53" s="73"/>
+      <c r="T53" s="73"/>
+      <c r="U53" s="73"/>
+      <c r="V53" s="73"/>
+      <c r="W53" s="73"/>
+      <c r="X53" s="73"/>
+      <c r="Y53" s="73"/>
+      <c r="Z53" s="73"/>
+      <c r="AA53" s="73"/>
+      <c r="AB53" s="73"/>
+      <c r="AC53" s="73"/>
+      <c r="AD53" s="73"/>
+      <c r="AE53" s="73"/>
+      <c r="AF53" s="73"/>
+      <c r="AG53" s="73"/>
+      <c r="AH53" s="73"/>
+      <c r="AI53" s="73"/>
+      <c r="AJ53" s="73"/>
+      <c r="AK53" s="73"/>
+      <c r="AL53" s="73"/>
+      <c r="AM53" s="73"/>
+      <c r="AN53" s="73"/>
+      <c r="AO53" s="73"/>
+      <c r="AP53" s="73"/>
+      <c r="AQ53" s="73"/>
+      <c r="AR53" s="73"/>
+      <c r="AS53" s="73"/>
+      <c r="AT53" s="73"/>
+      <c r="AU53" s="73"/>
+      <c r="AV53" s="73"/>
+      <c r="AW53" s="73"/>
+      <c r="AX53" s="73"/>
+      <c r="AY53" s="73"/>
+      <c r="AZ53" s="73"/>
+      <c r="BA53" s="73"/>
+      <c r="BB53" s="73"/>
+      <c r="BC53" s="73"/>
+      <c r="BD53" s="73"/>
+      <c r="BE53" s="73"/>
+      <c r="BF53" s="73"/>
+      <c r="BG53" s="73"/>
+      <c r="BH53" s="73"/>
+      <c r="BI53" s="73"/>
+      <c r="BJ53" s="73"/>
+      <c r="BK53" s="73"/>
+      <c r="BL53" s="73"/>
+      <c r="BM53" s="73"/>
+      <c r="BN53" s="73"/>
+      <c r="BO53" s="73"/>
+      <c r="BP53" s="73"/>
+      <c r="BQ53" s="73"/>
+      <c r="BR53" s="73"/>
+      <c r="BS53" s="73"/>
+      <c r="BT53" s="73"/>
+      <c r="BU53" s="73"/>
+      <c r="BV53" s="73"/>
+      <c r="BW53" s="73"/>
+      <c r="BX53" s="73"/>
+      <c r="BY53" s="73"/>
+      <c r="BZ53" s="73"/>
+      <c r="CA53" s="73"/>
+      <c r="CB53" s="73"/>
+      <c r="CC53" s="73"/>
+      <c r="CD53" s="73"/>
+      <c r="CE53" s="73"/>
+      <c r="CF53" s="73"/>
+      <c r="CG53" s="73"/>
+      <c r="CH53" s="73"/>
+      <c r="CI53" s="73"/>
+      <c r="CJ53" s="73"/>
+      <c r="CK53" s="73"/>
+      <c r="CL53" s="73"/>
+      <c r="CM53" s="73"/>
+      <c r="CN53" s="73"/>
+      <c r="CO53" s="73"/>
+      <c r="CP53" s="73"/>
+      <c r="CQ53" s="73"/>
+      <c r="CR53" s="73"/>
+      <c r="CS53" s="73"/>
+      <c r="CT53" s="73"/>
+      <c r="CU53" s="73"/>
+      <c r="CV53" s="73"/>
+      <c r="CW53" s="73"/>
+      <c r="CX53" s="73"/>
+      <c r="CY53" s="73"/>
+      <c r="CZ53" s="73"/>
+      <c r="DA53" s="73"/>
+      <c r="DB53" s="73"/>
+      <c r="DC53" s="73"/>
+      <c r="DD53" s="73"/>
+      <c r="DE53" s="73"/>
+      <c r="DF53" s="73"/>
+      <c r="DG53" s="73"/>
+      <c r="DH53" s="73"/>
+      <c r="DI53" s="73"/>
+      <c r="DJ53" s="73"/>
+      <c r="DK53" s="73"/>
+      <c r="DL53" s="73"/>
+      <c r="DM53" s="73"/>
+      <c r="DN53" s="73"/>
+      <c r="DO53" s="73"/>
+      <c r="DP53" s="73"/>
+      <c r="DQ53" s="73"/>
+      <c r="DR53" s="73"/>
+      <c r="DS53" s="73"/>
+      <c r="DT53" s="73"/>
+      <c r="DU53" s="73"/>
+      <c r="DV53" s="73"/>
+      <c r="DW53" s="73"/>
     </row>
     <row r="54" spans="1:127" ht="15.75" customHeight="1">
-      <c r="A54" s="73"/>
-      <c r="B54" s="74"/>
-      <c r="C54" s="75"/>
-      <c r="D54" s="75"/>
-      <c r="E54" s="75"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="75"/>
-      <c r="H54" s="75"/>
-      <c r="I54" s="75"/>
-      <c r="J54" s="75"/>
-      <c r="K54" s="75"/>
-      <c r="L54" s="75"/>
-      <c r="M54" s="75"/>
-      <c r="N54" s="75"/>
-      <c r="O54" s="75"/>
-      <c r="P54" s="75"/>
-      <c r="Q54" s="75"/>
-      <c r="R54" s="75"/>
-      <c r="S54" s="75"/>
-      <c r="T54" s="75"/>
-      <c r="U54" s="75"/>
-      <c r="V54" s="75"/>
-      <c r="W54" s="75"/>
-      <c r="X54" s="75"/>
-      <c r="Y54" s="75"/>
-      <c r="Z54" s="75"/>
-      <c r="AA54" s="75"/>
-      <c r="AB54" s="75"/>
-      <c r="AC54" s="75"/>
-      <c r="AD54" s="75"/>
-      <c r="AE54" s="75"/>
-      <c r="AF54" s="75"/>
-      <c r="AG54" s="75"/>
-      <c r="AH54" s="75"/>
-      <c r="AI54" s="75"/>
-      <c r="AJ54" s="75"/>
-      <c r="AK54" s="75"/>
-      <c r="AL54" s="75"/>
-      <c r="AM54" s="75"/>
-      <c r="AN54" s="75"/>
-      <c r="AO54" s="75"/>
-      <c r="AP54" s="75"/>
-      <c r="AQ54" s="75"/>
-      <c r="AR54" s="75"/>
-      <c r="AS54" s="75"/>
-      <c r="AT54" s="75"/>
-      <c r="AU54" s="75"/>
-      <c r="AV54" s="75"/>
-      <c r="AW54" s="75"/>
-      <c r="AX54" s="75"/>
-      <c r="AY54" s="75"/>
-      <c r="AZ54" s="75"/>
-      <c r="BA54" s="75"/>
-      <c r="BB54" s="75"/>
-      <c r="BC54" s="75"/>
-      <c r="BD54" s="75"/>
-      <c r="BE54" s="75"/>
-      <c r="BF54" s="75"/>
-      <c r="BG54" s="75"/>
-      <c r="BH54" s="75"/>
-      <c r="BI54" s="75"/>
-      <c r="BJ54" s="75"/>
-      <c r="BK54" s="75"/>
-      <c r="BL54" s="75"/>
-      <c r="BM54" s="75"/>
-      <c r="BN54" s="75"/>
-      <c r="BO54" s="75"/>
-      <c r="BP54" s="75"/>
-      <c r="BQ54" s="75"/>
-      <c r="BR54" s="75"/>
-      <c r="BS54" s="75"/>
-      <c r="BT54" s="75"/>
-      <c r="BU54" s="75"/>
-      <c r="BV54" s="75"/>
-      <c r="BW54" s="75"/>
-      <c r="BX54" s="75"/>
-      <c r="BY54" s="75"/>
-      <c r="BZ54" s="75"/>
-      <c r="CA54" s="75"/>
-      <c r="CB54" s="75"/>
-      <c r="CC54" s="75"/>
-      <c r="CD54" s="75"/>
-      <c r="CE54" s="75"/>
-      <c r="CF54" s="75"/>
-      <c r="CG54" s="75"/>
-      <c r="CH54" s="75"/>
-      <c r="CI54" s="75"/>
-      <c r="CJ54" s="75"/>
-      <c r="CK54" s="75"/>
-      <c r="CL54" s="75"/>
-      <c r="CM54" s="75"/>
-      <c r="CN54" s="75"/>
-      <c r="CO54" s="75"/>
-      <c r="CP54" s="75"/>
-      <c r="CQ54" s="75"/>
-      <c r="CR54" s="75"/>
-      <c r="CS54" s="75"/>
-      <c r="CT54" s="75"/>
-      <c r="CU54" s="75"/>
-      <c r="CV54" s="75"/>
-      <c r="CW54" s="75"/>
-      <c r="CX54" s="75"/>
-      <c r="CY54" s="75"/>
-      <c r="CZ54" s="75"/>
-      <c r="DA54" s="75"/>
-      <c r="DB54" s="75"/>
-      <c r="DC54" s="75"/>
-      <c r="DD54" s="75"/>
-      <c r="DE54" s="75"/>
-      <c r="DF54" s="75"/>
-      <c r="DG54" s="75"/>
-      <c r="DH54" s="75"/>
-      <c r="DI54" s="75"/>
-      <c r="DJ54" s="75"/>
-      <c r="DK54" s="75"/>
-      <c r="DL54" s="75"/>
-      <c r="DM54" s="75"/>
-      <c r="DN54" s="75"/>
-      <c r="DO54" s="75"/>
-      <c r="DP54" s="75"/>
-      <c r="DQ54" s="75"/>
-      <c r="DR54" s="75"/>
-      <c r="DS54" s="75"/>
-      <c r="DT54" s="75"/>
-      <c r="DU54" s="75"/>
-      <c r="DV54" s="75"/>
-      <c r="DW54" s="75"/>
+      <c r="A54" s="71"/>
+      <c r="B54" s="72"/>
+      <c r="C54" s="73"/>
+      <c r="D54" s="73"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="72"/>
+      <c r="G54" s="73"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73"/>
+      <c r="J54" s="73"/>
+      <c r="K54" s="73"/>
+      <c r="L54" s="73"/>
+      <c r="M54" s="73"/>
+      <c r="N54" s="73"/>
+      <c r="O54" s="73"/>
+      <c r="P54" s="73"/>
+      <c r="Q54" s="73"/>
+      <c r="R54" s="73"/>
+      <c r="S54" s="73"/>
+      <c r="T54" s="73"/>
+      <c r="U54" s="73"/>
+      <c r="V54" s="73"/>
+      <c r="W54" s="73"/>
+      <c r="X54" s="73"/>
+      <c r="Y54" s="73"/>
+      <c r="Z54" s="73"/>
+      <c r="AA54" s="73"/>
+      <c r="AB54" s="73"/>
+      <c r="AC54" s="73"/>
+      <c r="AD54" s="73"/>
+      <c r="AE54" s="73"/>
+      <c r="AF54" s="73"/>
+      <c r="AG54" s="73"/>
+      <c r="AH54" s="73"/>
+      <c r="AI54" s="73"/>
+      <c r="AJ54" s="73"/>
+      <c r="AK54" s="73"/>
+      <c r="AL54" s="73"/>
+      <c r="AM54" s="73"/>
+      <c r="AN54" s="73"/>
+      <c r="AO54" s="73"/>
+      <c r="AP54" s="73"/>
+      <c r="AQ54" s="73"/>
+      <c r="AR54" s="73"/>
+      <c r="AS54" s="73"/>
+      <c r="AT54" s="73"/>
+      <c r="AU54" s="73"/>
+      <c r="AV54" s="73"/>
+      <c r="AW54" s="73"/>
+      <c r="AX54" s="73"/>
+      <c r="AY54" s="73"/>
+      <c r="AZ54" s="73"/>
+      <c r="BA54" s="73"/>
+      <c r="BB54" s="73"/>
+      <c r="BC54" s="73"/>
+      <c r="BD54" s="73"/>
+      <c r="BE54" s="73"/>
+      <c r="BF54" s="73"/>
+      <c r="BG54" s="73"/>
+      <c r="BH54" s="73"/>
+      <c r="BI54" s="73"/>
+      <c r="BJ54" s="73"/>
+      <c r="BK54" s="73"/>
+      <c r="BL54" s="73"/>
+      <c r="BM54" s="73"/>
+      <c r="BN54" s="73"/>
+      <c r="BO54" s="73"/>
+      <c r="BP54" s="73"/>
+      <c r="BQ54" s="73"/>
+      <c r="BR54" s="73"/>
+      <c r="BS54" s="73"/>
+      <c r="BT54" s="73"/>
+      <c r="BU54" s="73"/>
+      <c r="BV54" s="73"/>
+      <c r="BW54" s="73"/>
+      <c r="BX54" s="73"/>
+      <c r="BY54" s="73"/>
+      <c r="BZ54" s="73"/>
+      <c r="CA54" s="73"/>
+      <c r="CB54" s="73"/>
+      <c r="CC54" s="73"/>
+      <c r="CD54" s="73"/>
+      <c r="CE54" s="73"/>
+      <c r="CF54" s="73"/>
+      <c r="CG54" s="73"/>
+      <c r="CH54" s="73"/>
+      <c r="CI54" s="73"/>
+      <c r="CJ54" s="73"/>
+      <c r="CK54" s="73"/>
+      <c r="CL54" s="73"/>
+      <c r="CM54" s="73"/>
+      <c r="CN54" s="73"/>
+      <c r="CO54" s="73"/>
+      <c r="CP54" s="73"/>
+      <c r="CQ54" s="73"/>
+      <c r="CR54" s="73"/>
+      <c r="CS54" s="73"/>
+      <c r="CT54" s="73"/>
+      <c r="CU54" s="73"/>
+      <c r="CV54" s="73"/>
+      <c r="CW54" s="73"/>
+      <c r="CX54" s="73"/>
+      <c r="CY54" s="73"/>
+      <c r="CZ54" s="73"/>
+      <c r="DA54" s="73"/>
+      <c r="DB54" s="73"/>
+      <c r="DC54" s="73"/>
+      <c r="DD54" s="73"/>
+      <c r="DE54" s="73"/>
+      <c r="DF54" s="73"/>
+      <c r="DG54" s="73"/>
+      <c r="DH54" s="73"/>
+      <c r="DI54" s="73"/>
+      <c r="DJ54" s="73"/>
+      <c r="DK54" s="73"/>
+      <c r="DL54" s="73"/>
+      <c r="DM54" s="73"/>
+      <c r="DN54" s="73"/>
+      <c r="DO54" s="73"/>
+      <c r="DP54" s="73"/>
+      <c r="DQ54" s="73"/>
+      <c r="DR54" s="73"/>
+      <c r="DS54" s="73"/>
+      <c r="DT54" s="73"/>
+      <c r="DU54" s="73"/>
+      <c r="DV54" s="73"/>
+      <c r="DW54" s="73"/>
     </row>
     <row r="55" spans="1:127" ht="15.75" customHeight="1">
-      <c r="A55" s="73"/>
-      <c r="B55" s="74"/>
-      <c r="C55" s="76"/>
-      <c r="D55" s="75"/>
-      <c r="E55" s="75"/>
-      <c r="F55" s="74"/>
+      <c r="A55" s="71"/>
+      <c r="B55" s="72"/>
+      <c r="C55" s="74"/>
+      <c r="D55" s="73"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="72"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -16890,12 +17104,12 @@
       <c r="DW55" s="1"/>
     </row>
     <row r="56" spans="1:127" ht="15.75" customHeight="1">
-      <c r="A56" s="73"/>
-      <c r="B56" s="74"/>
-      <c r="C56" s="75"/>
-      <c r="D56" s="75"/>
-      <c r="E56" s="75"/>
-      <c r="F56" s="74"/>
+      <c r="A56" s="71"/>
+      <c r="B56" s="72"/>
+      <c r="C56" s="73"/>
+      <c r="D56" s="73"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="72"/>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -41781,18 +41995,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A1" s="180">
-        <v>0</v>
-      </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="174"/>
+      <c r="A1" s="193">
+        <v>0</v>
+      </c>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="187"/>
       <c r="L1" s="48"/>
       <c r="M1" s="48"/>
       <c r="N1" s="48"/>
@@ -41810,16 +42024,16 @@
       <c r="Z1" s="48"/>
     </row>
     <row r="2" spans="1:26" ht="15.75">
-      <c r="A2" s="123"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="174"/>
+      <c r="A2" s="136"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="136"/>
+      <c r="F2" s="136"/>
+      <c r="G2" s="136"/>
+      <c r="H2" s="136"/>
+      <c r="I2" s="136"/>
+      <c r="J2" s="187"/>
       <c r="L2" s="48"/>
       <c r="M2" s="48"/>
       <c r="N2" s="48"/>
@@ -41837,15 +42051,15 @@
       <c r="Z2" s="48"/>
     </row>
     <row r="3" spans="1:26" ht="15.75">
-      <c r="A3" s="178" t="s">
+      <c r="A3" s="191" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="100"/>
-      <c r="C3" s="181" t="s">
+      <c r="B3" s="113"/>
+      <c r="C3" s="194" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="99"/>
-      <c r="E3" s="100"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="113"/>
       <c r="F3" s="49"/>
       <c r="G3" s="49"/>
       <c r="H3" s="50"/>
@@ -41869,23 +42083,23 @@
       <c r="Z3" s="48"/>
     </row>
     <row r="4" spans="1:26" ht="15.75">
-      <c r="A4" s="178" t="s">
+      <c r="A4" s="191" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="100"/>
-      <c r="C4" s="182">
-        <v>3151042</v>
-      </c>
-      <c r="D4" s="99"/>
-      <c r="E4" s="100"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="195">
+        <v>3415087</v>
+      </c>
+      <c r="D4" s="112"/>
+      <c r="E4" s="113"/>
       <c r="F4" s="51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4" s="52">
         <v>2</v>
       </c>
       <c r="H4" s="50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I4" s="50"/>
       <c r="J4" s="48"/>
@@ -41907,17 +42121,17 @@
       <c r="Z4" s="48"/>
     </row>
     <row r="5" spans="1:26" ht="15.75">
-      <c r="A5" s="178" t="s">
+      <c r="A5" s="191" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="179" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5" s="99"/>
-      <c r="E5" s="100"/>
+      <c r="B5" s="113"/>
+      <c r="C5" s="192" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="112"/>
+      <c r="E5" s="113"/>
       <c r="F5" s="51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5" s="53">
         <v>46084</v>
@@ -41943,17 +42157,17 @@
       <c r="Z5" s="48"/>
     </row>
     <row r="6" spans="1:26" ht="15.75">
-      <c r="A6" s="178" t="s">
+      <c r="A6" s="191" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="113"/>
+      <c r="C6" s="196" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="112"/>
+      <c r="E6" s="113"/>
+      <c r="F6" s="51" t="s">
         <v>70</v>
-      </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="183" t="s">
-        <v>178</v>
-      </c>
-      <c r="D6" s="99"/>
-      <c r="E6" s="100"/>
-      <c r="F6" s="51" t="s">
-        <v>71</v>
       </c>
       <c r="G6" s="54">
         <v>46087</v>
@@ -41979,17 +42193,17 @@
       <c r="Z6" s="48"/>
     </row>
     <row r="7" spans="1:26" ht="15.75">
-      <c r="A7" s="178" t="s">
+      <c r="A7" s="191" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="100"/>
-      <c r="C7" s="184" t="s">
+      <c r="B7" s="113"/>
+      <c r="C7" s="197" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="112"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="55" t="s">
         <v>72</v>
-      </c>
-      <c r="D7" s="99"/>
-      <c r="E7" s="100"/>
-      <c r="F7" s="55" t="s">
-        <v>73</v>
       </c>
       <c r="G7" s="56">
         <v>10</v>
@@ -42015,17 +42229,17 @@
       <c r="Z7" s="48"/>
     </row>
     <row r="8" spans="1:26" ht="15.75">
-      <c r="A8" s="185" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" s="100"/>
-      <c r="C8" s="186" t="s">
-        <v>362</v>
-      </c>
-      <c r="D8" s="99"/>
-      <c r="E8" s="99"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="100"/>
+      <c r="A8" s="198" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="113"/>
+      <c r="C8" s="199" t="s">
+        <v>276</v>
+      </c>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="113"/>
       <c r="H8" s="50"/>
       <c r="I8" s="50"/>
       <c r="J8" s="48"/>
@@ -42051,34 +42265,34 @@
         <v>34</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>363</v>
+        <v>277</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>366</v>
+        <v>280</v>
       </c>
       <c r="D9" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="58" t="s">
+      <c r="F9" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="58" t="s">
+      <c r="G9" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="58" t="s">
+      <c r="H9" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="58" t="s">
+      <c r="I9" s="58" t="s">
+        <v>278</v>
+      </c>
+      <c r="J9" s="58" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="58" t="s">
-        <v>364</v>
-      </c>
-      <c r="J9" s="58" t="s">
-        <v>80</v>
-      </c>
       <c r="K9" s="58" t="s">
-        <v>365</v>
+        <v>279</v>
       </c>
       <c r="L9" s="48"/>
       <c r="M9" s="48"/>
@@ -42097,33 +42311,35 @@
       <c r="Z9" s="48"/>
     </row>
     <row r="10" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A10" s="77">
+      <c r="A10" s="75">
         <v>1</v>
       </c>
-      <c r="B10" s="79" t="s">
-        <v>179</v>
-      </c>
-      <c r="C10" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D10" s="85">
+      <c r="B10" s="77" t="s">
+        <v>293</v>
+      </c>
+      <c r="C10" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="83">
         <v>1022968139</v>
       </c>
-      <c r="E10" s="88"/>
-      <c r="F10" s="95" t="s">
-        <v>216</v>
-      </c>
-      <c r="G10" s="97">
+      <c r="E10" s="86"/>
+      <c r="F10" s="98" t="s">
+        <v>130</v>
+      </c>
+      <c r="G10" s="95">
         <v>3241896763</v>
       </c>
-      <c r="H10" s="85" t="s">
-        <v>251</v>
-      </c>
-      <c r="I10" s="85" t="s">
-        <v>252</v>
-      </c>
-      <c r="J10" s="85"/>
-      <c r="K10" s="96"/>
+      <c r="H10" s="83" t="s">
+        <v>165</v>
+      </c>
+      <c r="I10" s="83" t="s">
+        <v>166</v>
+      </c>
+      <c r="J10" s="83"/>
+      <c r="K10" s="96" t="s">
+        <v>354</v>
+      </c>
       <c r="L10" s="48"/>
       <c r="M10" s="48"/>
       <c r="N10" s="48"/>
@@ -42141,37 +42357,37 @@
       <c r="Z10" s="48"/>
     </row>
     <row r="11" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A11" s="77">
+      <c r="A11" s="75">
         <f t="shared" ref="A11:A45" si="0">A10+1</f>
         <v>2</v>
       </c>
-      <c r="B11" s="79" t="s">
-        <v>180</v>
-      </c>
-      <c r="C11" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D11" s="85">
+      <c r="B11" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="83">
         <v>1141330545</v>
       </c>
-      <c r="E11" s="88"/>
-      <c r="F11" s="94" t="s">
-        <v>217</v>
-      </c>
-      <c r="G11" s="97">
+      <c r="E11" s="86"/>
+      <c r="F11" s="100" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="95">
         <v>3168860412</v>
       </c>
-      <c r="H11" s="85" t="s">
-        <v>254</v>
-      </c>
-      <c r="I11" s="85" t="s">
-        <v>255</v>
-      </c>
-      <c r="J11" s="85">
+      <c r="H11" s="83" t="s">
+        <v>168</v>
+      </c>
+      <c r="I11" s="83" t="s">
+        <v>169</v>
+      </c>
+      <c r="J11" s="83">
         <v>3241896776</v>
       </c>
-      <c r="K11" s="96" t="s">
-        <v>253</v>
+      <c r="K11" s="94" t="s">
+        <v>167</v>
       </c>
       <c r="L11" s="48"/>
       <c r="M11" s="48"/>
@@ -42190,37 +42406,37 @@
       <c r="Z11" s="48"/>
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A12" s="77">
+      <c r="A12" s="75">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B12" s="79" t="s">
-        <v>181</v>
-      </c>
-      <c r="C12" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D12" s="85">
+      <c r="B12" s="77" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D12" s="83">
         <v>1141123272</v>
       </c>
-      <c r="E12" s="87"/>
-      <c r="F12" s="95" t="s">
-        <v>218</v>
-      </c>
-      <c r="G12" s="97">
+      <c r="E12" s="85"/>
+      <c r="F12" s="98" t="s">
+        <v>132</v>
+      </c>
+      <c r="G12" s="95">
         <v>3229157385</v>
       </c>
-      <c r="H12" s="85" t="s">
-        <v>257</v>
-      </c>
-      <c r="I12" s="85" t="s">
-        <v>258</v>
-      </c>
-      <c r="J12" s="85">
+      <c r="H12" s="83" t="s">
+        <v>171</v>
+      </c>
+      <c r="I12" s="83" t="s">
+        <v>172</v>
+      </c>
+      <c r="J12" s="83">
         <v>3057153970</v>
       </c>
-      <c r="K12" s="96" t="s">
-        <v>256</v>
+      <c r="K12" s="94" t="s">
+        <v>170</v>
       </c>
       <c r="L12" s="48"/>
       <c r="M12" s="48"/>
@@ -42239,37 +42455,37 @@
       <c r="Z12" s="48"/>
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A13" s="77">
+      <c r="A13" s="75">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B13" s="79" t="s">
-        <v>182</v>
-      </c>
-      <c r="C13" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D13" s="85">
+      <c r="B13" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D13" s="83">
         <v>1013008314</v>
       </c>
-      <c r="E13" s="88"/>
-      <c r="F13" s="94" t="s">
-        <v>219</v>
-      </c>
-      <c r="G13" s="97">
+      <c r="E13" s="86"/>
+      <c r="F13" s="100" t="s">
+        <v>133</v>
+      </c>
+      <c r="G13" s="95">
         <v>323280803</v>
       </c>
-      <c r="H13" s="85" t="s">
-        <v>260</v>
-      </c>
-      <c r="I13" s="85" t="s">
-        <v>261</v>
-      </c>
-      <c r="J13" s="85">
+      <c r="H13" s="83" t="s">
+        <v>174</v>
+      </c>
+      <c r="I13" s="83" t="s">
+        <v>175</v>
+      </c>
+      <c r="J13" s="83">
         <v>3226783624</v>
       </c>
-      <c r="K13" s="96" t="s">
-        <v>259</v>
+      <c r="K13" s="94" t="s">
+        <v>173</v>
       </c>
       <c r="L13" s="48"/>
       <c r="M13" s="48"/>
@@ -42288,37 +42504,37 @@
       <c r="Z13" s="48"/>
     </row>
     <row r="14" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A14" s="77">
+      <c r="A14" s="75">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B14" s="79" t="s">
-        <v>183</v>
-      </c>
-      <c r="C14" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D14" s="85">
+      <c r="B14" s="77" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D14" s="83">
         <v>1016956354</v>
       </c>
-      <c r="E14" s="88"/>
-      <c r="F14" s="95" t="s">
-        <v>220</v>
-      </c>
-      <c r="G14" s="97">
+      <c r="E14" s="86"/>
+      <c r="F14" s="98" t="s">
+        <v>134</v>
+      </c>
+      <c r="G14" s="95">
         <v>3151261923</v>
       </c>
-      <c r="H14" s="85" t="s">
-        <v>263</v>
-      </c>
-      <c r="I14" s="85" t="s">
-        <v>264</v>
-      </c>
-      <c r="J14" s="85">
+      <c r="H14" s="83" t="s">
+        <v>177</v>
+      </c>
+      <c r="I14" s="83" t="s">
+        <v>178</v>
+      </c>
+      <c r="J14" s="83">
         <v>3232808083</v>
       </c>
-      <c r="K14" s="96" t="s">
-        <v>262</v>
+      <c r="K14" s="94" t="s">
+        <v>176</v>
       </c>
       <c r="L14" s="48"/>
       <c r="M14" s="48"/>
@@ -42337,37 +42553,37 @@
       <c r="Z14" s="48"/>
     </row>
     <row r="15" spans="1:26" ht="22.5" customHeight="1">
-      <c r="A15" s="77">
+      <c r="A15" s="75">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B15" s="79" t="s">
-        <v>184</v>
-      </c>
-      <c r="C15" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D15" s="85">
+      <c r="B15" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="83">
         <v>1022363595</v>
       </c>
-      <c r="E15" s="88"/>
-      <c r="F15" s="94" t="s">
-        <v>221</v>
-      </c>
-      <c r="G15" s="97">
+      <c r="E15" s="86"/>
+      <c r="F15" s="100" t="s">
+        <v>135</v>
+      </c>
+      <c r="G15" s="95">
         <v>3502771892</v>
       </c>
-      <c r="H15" s="85" t="s">
-        <v>266</v>
-      </c>
-      <c r="I15" s="85" t="s">
-        <v>267</v>
-      </c>
-      <c r="J15" s="85">
+      <c r="H15" s="83" t="s">
+        <v>180</v>
+      </c>
+      <c r="I15" s="83" t="s">
+        <v>181</v>
+      </c>
+      <c r="J15" s="83">
         <v>3208027889</v>
       </c>
-      <c r="K15" s="96" t="s">
-        <v>265</v>
+      <c r="K15" s="94" t="s">
+        <v>179</v>
       </c>
       <c r="L15" s="48"/>
       <c r="M15" s="48"/>
@@ -42386,37 +42602,37 @@
       <c r="Z15" s="48"/>
     </row>
     <row r="16" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A16" s="77">
+      <c r="A16" s="75">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B16" s="79" t="s">
-        <v>185</v>
-      </c>
-      <c r="C16" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D16" s="85">
+      <c r="B16" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="83">
         <v>1071839754</v>
       </c>
-      <c r="E16" s="88"/>
-      <c r="F16" s="95" t="s">
-        <v>222</v>
-      </c>
-      <c r="G16" s="97">
+      <c r="E16" s="86"/>
+      <c r="F16" s="98" t="s">
+        <v>136</v>
+      </c>
+      <c r="G16" s="95">
         <v>3028453994</v>
       </c>
-      <c r="H16" s="85" t="s">
-        <v>269</v>
-      </c>
-      <c r="I16" s="85" t="s">
-        <v>270</v>
-      </c>
-      <c r="J16" s="85">
+      <c r="H16" s="83" t="s">
+        <v>183</v>
+      </c>
+      <c r="I16" s="83" t="s">
+        <v>184</v>
+      </c>
+      <c r="J16" s="83">
         <v>3007767197</v>
       </c>
-      <c r="K16" s="96" t="s">
-        <v>268</v>
+      <c r="K16" s="94" t="s">
+        <v>182</v>
       </c>
       <c r="L16" s="48"/>
       <c r="M16" s="48"/>
@@ -42435,37 +42651,37 @@
       <c r="Z16" s="48"/>
     </row>
     <row r="17" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A17" s="77">
+      <c r="A17" s="75">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B17" s="79" t="s">
+      <c r="B17" s="77" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="83">
+        <v>1010761790</v>
+      </c>
+      <c r="E17" s="86"/>
+      <c r="F17" s="100" t="s">
+        <v>137</v>
+      </c>
+      <c r="G17" s="95">
+        <v>3118752681</v>
+      </c>
+      <c r="H17" s="83" t="s">
         <v>186</v>
       </c>
-      <c r="C17" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D17" s="85">
-        <v>1010761790</v>
-      </c>
-      <c r="E17" s="88"/>
-      <c r="F17" s="94" t="s">
-        <v>223</v>
-      </c>
-      <c r="G17" s="97">
-        <v>3118752681</v>
-      </c>
-      <c r="H17" s="85" t="s">
-        <v>272</v>
-      </c>
-      <c r="I17" s="85" t="s">
-        <v>273</v>
-      </c>
-      <c r="J17" s="85">
+      <c r="I17" s="83" t="s">
+        <v>187</v>
+      </c>
+      <c r="J17" s="83">
         <v>3213732898</v>
       </c>
-      <c r="K17" s="96" t="s">
-        <v>271</v>
+      <c r="K17" s="94" t="s">
+        <v>185</v>
       </c>
       <c r="L17" s="48"/>
       <c r="M17" s="48"/>
@@ -42484,37 +42700,37 @@
       <c r="Z17" s="48"/>
     </row>
     <row r="18" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A18" s="77">
+      <c r="A18" s="75">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B18" s="79" t="s">
-        <v>187</v>
-      </c>
-      <c r="C18" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D18" s="85">
+      <c r="B18" s="77" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="83">
         <v>1145224966</v>
       </c>
-      <c r="E18" s="88"/>
-      <c r="F18" s="95" t="s">
-        <v>224</v>
-      </c>
-      <c r="G18" s="97">
+      <c r="E18" s="86"/>
+      <c r="F18" s="98" t="s">
+        <v>138</v>
+      </c>
+      <c r="G18" s="95">
         <v>3027386279</v>
       </c>
-      <c r="H18" s="85" t="s">
-        <v>275</v>
-      </c>
-      <c r="I18" s="85" t="s">
-        <v>276</v>
-      </c>
-      <c r="J18" s="85">
+      <c r="H18" s="83" t="s">
+        <v>189</v>
+      </c>
+      <c r="I18" s="83" t="s">
+        <v>190</v>
+      </c>
+      <c r="J18" s="83">
         <v>3165272332</v>
       </c>
-      <c r="K18" s="96" t="s">
-        <v>274</v>
+      <c r="K18" s="94" t="s">
+        <v>188</v>
       </c>
       <c r="L18" s="48"/>
       <c r="M18" s="48"/>
@@ -42533,37 +42749,37 @@
       <c r="Z18" s="48"/>
     </row>
     <row r="19" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A19" s="77">
+      <c r="A19" s="75">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B19" s="79" t="s">
-        <v>188</v>
-      </c>
-      <c r="C19" s="86" t="s">
-        <v>215</v>
-      </c>
-      <c r="D19" s="85">
+      <c r="B19" s="77" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="84" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" s="83">
         <v>5435931</v>
       </c>
-      <c r="E19" s="89"/>
-      <c r="F19" s="94" t="s">
-        <v>225</v>
-      </c>
-      <c r="G19" s="97">
+      <c r="E19" s="87"/>
+      <c r="F19" s="100" t="s">
+        <v>139</v>
+      </c>
+      <c r="G19" s="95">
         <v>3204761364</v>
       </c>
-      <c r="H19" s="85" t="s">
-        <v>278</v>
-      </c>
-      <c r="I19" s="85" t="s">
-        <v>279</v>
-      </c>
-      <c r="J19" s="85">
+      <c r="H19" s="83" t="s">
+        <v>192</v>
+      </c>
+      <c r="I19" s="83" t="s">
+        <v>193</v>
+      </c>
+      <c r="J19" s="83">
         <v>3144091358</v>
       </c>
-      <c r="K19" s="96" t="s">
-        <v>277</v>
+      <c r="K19" s="94" t="s">
+        <v>191</v>
       </c>
       <c r="L19" s="48"/>
       <c r="M19" s="48"/>
@@ -42582,37 +42798,37 @@
       <c r="Z19" s="48"/>
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A20" s="77">
+      <c r="A20" s="75">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B20" s="79" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D20" s="85">
+      <c r="B20" s="77" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D20" s="83">
         <v>1014870600</v>
       </c>
-      <c r="E20" s="89"/>
-      <c r="F20" s="95" t="s">
-        <v>226</v>
-      </c>
-      <c r="G20" s="97">
+      <c r="E20" s="87"/>
+      <c r="F20" s="98" t="s">
+        <v>140</v>
+      </c>
+      <c r="G20" s="95">
         <v>3196387219</v>
       </c>
-      <c r="H20" s="85" t="s">
-        <v>281</v>
-      </c>
-      <c r="I20" s="85" t="s">
-        <v>282</v>
-      </c>
-      <c r="J20" s="85">
+      <c r="H20" s="83" t="s">
+        <v>195</v>
+      </c>
+      <c r="I20" s="83" t="s">
+        <v>196</v>
+      </c>
+      <c r="J20" s="83">
         <v>3161569075</v>
       </c>
-      <c r="K20" s="96" t="s">
-        <v>280</v>
+      <c r="K20" s="94" t="s">
+        <v>194</v>
       </c>
       <c r="L20" s="48"/>
       <c r="M20" s="48"/>
@@ -42631,37 +42847,37 @@
       <c r="Z20" s="48"/>
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A21" s="77">
+      <c r="A21" s="75">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B21" s="79" t="s">
-        <v>190</v>
-      </c>
-      <c r="C21" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D21" s="85">
+      <c r="B21" s="77" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" s="83">
         <v>1145226101</v>
       </c>
-      <c r="E21" s="89"/>
-      <c r="F21" s="94" t="s">
-        <v>227</v>
-      </c>
-      <c r="G21" s="97">
+      <c r="E21" s="87"/>
+      <c r="F21" s="100" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" s="95">
         <v>3112007862</v>
       </c>
-      <c r="H21" s="85" t="s">
-        <v>284</v>
-      </c>
-      <c r="I21" s="85" t="s">
-        <v>285</v>
-      </c>
-      <c r="J21" s="85">
+      <c r="H21" s="83" t="s">
+        <v>198</v>
+      </c>
+      <c r="I21" s="83" t="s">
+        <v>199</v>
+      </c>
+      <c r="J21" s="83">
         <v>3044426775</v>
       </c>
-      <c r="K21" s="96" t="s">
-        <v>283</v>
+      <c r="K21" s="94" t="s">
+        <v>197</v>
       </c>
       <c r="L21" s="48"/>
       <c r="M21" s="48"/>
@@ -42680,35 +42896,35 @@
       <c r="Z21" s="48"/>
     </row>
     <row r="22" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A22" s="77">
+      <c r="A22" s="75">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B22" s="79" t="s">
-        <v>191</v>
-      </c>
-      <c r="C22" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D22" s="85">
+      <c r="B22" s="77" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="83">
         <v>1150185896</v>
       </c>
-      <c r="E22" s="88"/>
-      <c r="F22" s="95" t="s">
-        <v>228</v>
-      </c>
-      <c r="G22" s="97">
+      <c r="E22" s="86"/>
+      <c r="F22" s="98" t="s">
+        <v>142</v>
+      </c>
+      <c r="G22" s="95">
         <v>3236964252</v>
       </c>
-      <c r="H22" s="85"/>
-      <c r="I22" s="85" t="s">
-        <v>287</v>
-      </c>
-      <c r="J22" s="85">
+      <c r="H22" s="83"/>
+      <c r="I22" s="83" t="s">
+        <v>201</v>
+      </c>
+      <c r="J22" s="83">
         <v>3142400388</v>
       </c>
-      <c r="K22" s="96" t="s">
-        <v>286</v>
+      <c r="K22" s="94" t="s">
+        <v>200</v>
       </c>
       <c r="L22" s="48"/>
       <c r="M22" s="48"/>
@@ -42727,37 +42943,37 @@
       <c r="Z22" s="48"/>
     </row>
     <row r="23" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A23" s="77">
+      <c r="A23" s="75">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B23" s="79" t="s">
-        <v>192</v>
-      </c>
-      <c r="C23" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D23" s="85">
+      <c r="B23" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="83">
         <v>1022973396</v>
       </c>
-      <c r="E23" s="87"/>
-      <c r="F23" s="94" t="s">
-        <v>229</v>
-      </c>
-      <c r="G23" s="97">
+      <c r="E23" s="85"/>
+      <c r="F23" s="100" t="s">
+        <v>143</v>
+      </c>
+      <c r="G23" s="95">
         <v>3114707804</v>
       </c>
-      <c r="H23" s="85" t="s">
-        <v>289</v>
-      </c>
-      <c r="I23" s="85" t="s">
-        <v>290</v>
-      </c>
-      <c r="J23" s="85">
+      <c r="H23" s="83" t="s">
+        <v>203</v>
+      </c>
+      <c r="I23" s="83" t="s">
+        <v>204</v>
+      </c>
+      <c r="J23" s="83">
         <v>3006162042</v>
       </c>
-      <c r="K23" s="96" t="s">
-        <v>288</v>
+      <c r="K23" s="94" t="s">
+        <v>202</v>
       </c>
       <c r="L23" s="48"/>
       <c r="M23" s="48"/>
@@ -42776,37 +42992,37 @@
       <c r="Z23" s="48"/>
     </row>
     <row r="24" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A24" s="77">
+      <c r="A24" s="75">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B24" s="79" t="s">
-        <v>193</v>
-      </c>
-      <c r="C24" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D24" s="85">
+      <c r="B24" s="77" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="83">
         <v>1043985607</v>
       </c>
-      <c r="E24" s="88"/>
-      <c r="F24" s="95" t="s">
-        <v>230</v>
-      </c>
-      <c r="G24" s="97">
+      <c r="E24" s="86"/>
+      <c r="F24" s="98" t="s">
+        <v>144</v>
+      </c>
+      <c r="G24" s="95">
         <v>3170179434</v>
       </c>
-      <c r="H24" s="85" t="s">
-        <v>292</v>
-      </c>
-      <c r="I24" s="85" t="s">
-        <v>293</v>
-      </c>
-      <c r="J24" s="85">
+      <c r="H24" s="83" t="s">
+        <v>206</v>
+      </c>
+      <c r="I24" s="83" t="s">
+        <v>207</v>
+      </c>
+      <c r="J24" s="83">
         <v>3135111551</v>
       </c>
-      <c r="K24" s="96" t="s">
-        <v>291</v>
+      <c r="K24" s="94" t="s">
+        <v>205</v>
       </c>
       <c r="L24" s="48"/>
       <c r="M24" s="48"/>
@@ -42825,37 +43041,37 @@
       <c r="Z24" s="48"/>
     </row>
     <row r="25" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A25" s="77">
+      <c r="A25" s="75">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B25" s="79" t="s">
-        <v>194</v>
-      </c>
-      <c r="C25" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D25" s="85">
+      <c r="B25" s="77" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="83">
         <v>1033740235</v>
       </c>
-      <c r="E25" s="88"/>
-      <c r="F25" s="94" t="s">
-        <v>231</v>
-      </c>
-      <c r="G25" s="97">
+      <c r="E25" s="86"/>
+      <c r="F25" s="100" t="s">
+        <v>145</v>
+      </c>
+      <c r="G25" s="95">
         <v>3144815739</v>
       </c>
-      <c r="H25" s="85" t="s">
-        <v>295</v>
-      </c>
-      <c r="I25" s="85" t="s">
-        <v>296</v>
-      </c>
-      <c r="J25" s="85">
+      <c r="H25" s="83" t="s">
+        <v>209</v>
+      </c>
+      <c r="I25" s="83" t="s">
+        <v>210</v>
+      </c>
+      <c r="J25" s="83">
         <v>3147031098</v>
       </c>
-      <c r="K25" s="96" t="s">
-        <v>294</v>
+      <c r="K25" s="94" t="s">
+        <v>208</v>
       </c>
       <c r="L25" s="59"/>
       <c r="M25" s="59"/>
@@ -42874,37 +43090,37 @@
       <c r="Z25" s="59"/>
     </row>
     <row r="26" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A26" s="77">
+      <c r="A26" s="75">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B26" s="79" t="s">
-        <v>195</v>
-      </c>
-      <c r="C26" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D26" s="85">
+      <c r="B26" s="77" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D26" s="83">
         <v>1019999361</v>
       </c>
-      <c r="E26" s="89"/>
-      <c r="F26" s="95" t="s">
-        <v>232</v>
-      </c>
-      <c r="G26" s="97">
+      <c r="E26" s="87"/>
+      <c r="F26" s="98" t="s">
+        <v>146</v>
+      </c>
+      <c r="G26" s="95">
         <v>3232326197</v>
       </c>
-      <c r="H26" s="85" t="s">
-        <v>298</v>
-      </c>
-      <c r="I26" s="85" t="s">
-        <v>299</v>
-      </c>
-      <c r="J26" s="85">
+      <c r="H26" s="83" t="s">
+        <v>212</v>
+      </c>
+      <c r="I26" s="83" t="s">
+        <v>213</v>
+      </c>
+      <c r="J26" s="83">
         <v>3202645748</v>
       </c>
-      <c r="K26" s="96" t="s">
-        <v>297</v>
+      <c r="K26" s="94" t="s">
+        <v>211</v>
       </c>
       <c r="L26" s="48"/>
       <c r="M26" s="48"/>
@@ -42923,37 +43139,37 @@
       <c r="Z26" s="48"/>
     </row>
     <row r="27" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A27" s="77">
+      <c r="A27" s="75">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B27" s="79" t="s">
-        <v>196</v>
-      </c>
-      <c r="C27" s="86" t="s">
+      <c r="B27" s="77" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="84" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" s="83">
+        <v>5932469</v>
+      </c>
+      <c r="E27" s="87"/>
+      <c r="F27" s="100" t="s">
+        <v>147</v>
+      </c>
+      <c r="G27" s="95">
+        <v>3009962270</v>
+      </c>
+      <c r="H27" s="83" t="s">
         <v>215</v>
       </c>
-      <c r="D27" s="85">
-        <v>5932469</v>
-      </c>
-      <c r="E27" s="89"/>
-      <c r="F27" s="94" t="s">
-        <v>233</v>
-      </c>
-      <c r="G27" s="97">
-        <v>3009962270</v>
-      </c>
-      <c r="H27" s="85" t="s">
-        <v>301</v>
-      </c>
-      <c r="I27" s="85" t="s">
-        <v>302</v>
-      </c>
-      <c r="J27" s="85">
+      <c r="I27" s="83" t="s">
+        <v>216</v>
+      </c>
+      <c r="J27" s="83">
         <v>3046212989</v>
       </c>
-      <c r="K27" s="96" t="s">
-        <v>300</v>
+      <c r="K27" s="94" t="s">
+        <v>214</v>
       </c>
       <c r="L27" s="48"/>
       <c r="M27" s="48"/>
@@ -42972,37 +43188,37 @@
       <c r="Z27" s="48"/>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A28" s="77">
+      <c r="A28" s="75">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B28" s="79" t="s">
-        <v>197</v>
-      </c>
-      <c r="C28" s="86" t="s">
-        <v>215</v>
-      </c>
-      <c r="D28" s="85">
+      <c r="B28" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="84" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="83">
         <v>5932265</v>
       </c>
-      <c r="E28" s="88"/>
-      <c r="F28" s="95" t="s">
-        <v>234</v>
-      </c>
-      <c r="G28" s="97">
+      <c r="E28" s="86"/>
+      <c r="F28" s="98" t="s">
+        <v>148</v>
+      </c>
+      <c r="G28" s="95">
         <v>3108720583</v>
       </c>
-      <c r="H28" s="85" t="s">
-        <v>304</v>
-      </c>
-      <c r="I28" s="85" t="s">
-        <v>302</v>
-      </c>
-      <c r="J28" s="85">
+      <c r="H28" s="83" t="s">
+        <v>218</v>
+      </c>
+      <c r="I28" s="83" t="s">
+        <v>216</v>
+      </c>
+      <c r="J28" s="83">
         <v>3214225742</v>
       </c>
-      <c r="K28" s="96" t="s">
-        <v>303</v>
+      <c r="K28" s="94" t="s">
+        <v>217</v>
       </c>
       <c r="L28" s="48"/>
       <c r="M28" s="48"/>
@@ -43021,37 +43237,37 @@
       <c r="Z28" s="48"/>
     </row>
     <row r="29" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A29" s="77">
+      <c r="A29" s="75">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B29" s="79" t="s">
-        <v>198</v>
-      </c>
-      <c r="C29" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D29" s="85">
+      <c r="B29" s="77" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="83">
         <v>1011102362</v>
       </c>
-      <c r="E29" s="90"/>
-      <c r="F29" s="94" t="s">
-        <v>235</v>
-      </c>
-      <c r="G29" s="97" t="s">
-        <v>306</v>
-      </c>
-      <c r="H29" s="85" t="s">
-        <v>307</v>
-      </c>
-      <c r="I29" s="85" t="s">
-        <v>308</v>
-      </c>
-      <c r="J29" s="85">
+      <c r="E29" s="88"/>
+      <c r="F29" s="100" t="s">
+        <v>149</v>
+      </c>
+      <c r="G29" s="95" t="s">
+        <v>220</v>
+      </c>
+      <c r="H29" s="83" t="s">
+        <v>221</v>
+      </c>
+      <c r="I29" s="83" t="s">
+        <v>222</v>
+      </c>
+      <c r="J29" s="83">
         <v>3214225742</v>
       </c>
-      <c r="K29" s="96" t="s">
-        <v>305</v>
+      <c r="K29" s="94" t="s">
+        <v>219</v>
       </c>
       <c r="L29" s="48"/>
       <c r="M29" s="48"/>
@@ -43070,37 +43286,37 @@
       <c r="Z29" s="48"/>
     </row>
     <row r="30" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A30" s="77">
+      <c r="A30" s="75">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B30" s="79" t="s">
-        <v>199</v>
-      </c>
-      <c r="C30" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D30" s="85">
+      <c r="B30" s="77" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" s="83">
         <v>1011325429</v>
       </c>
-      <c r="E30" s="90"/>
-      <c r="F30" s="95" t="s">
-        <v>236</v>
-      </c>
-      <c r="G30" s="97">
+      <c r="E30" s="88"/>
+      <c r="F30" s="98" t="s">
+        <v>150</v>
+      </c>
+      <c r="G30" s="95">
         <v>3237429353</v>
       </c>
-      <c r="H30" s="85" t="s">
-        <v>311</v>
-      </c>
-      <c r="I30" s="85" t="s">
-        <v>312</v>
-      </c>
-      <c r="J30" s="97" t="s">
-        <v>309</v>
-      </c>
-      <c r="K30" s="96" t="s">
-        <v>310</v>
+      <c r="H30" s="83" t="s">
+        <v>225</v>
+      </c>
+      <c r="I30" s="83" t="s">
+        <v>226</v>
+      </c>
+      <c r="J30" s="95" t="s">
+        <v>223</v>
+      </c>
+      <c r="K30" s="94" t="s">
+        <v>224</v>
       </c>
       <c r="L30" s="48"/>
       <c r="M30" s="48"/>
@@ -43119,37 +43335,37 @@
       <c r="Z30" s="48"/>
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A31" s="77">
+      <c r="A31" s="75">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B31" s="79" t="s">
-        <v>200</v>
-      </c>
-      <c r="C31" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D31" s="85">
+      <c r="B31" s="77" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" s="83">
         <v>1012921389</v>
       </c>
-      <c r="E31" s="90"/>
-      <c r="F31" s="94" t="s">
-        <v>237</v>
-      </c>
-      <c r="G31" s="97" t="s">
-        <v>314</v>
-      </c>
-      <c r="H31" s="85" t="s">
-        <v>315</v>
-      </c>
-      <c r="I31" s="85" t="s">
-        <v>316</v>
-      </c>
-      <c r="J31" s="97">
+      <c r="E31" s="88"/>
+      <c r="F31" s="92" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" s="95" t="s">
+        <v>228</v>
+      </c>
+      <c r="H31" s="83" t="s">
+        <v>229</v>
+      </c>
+      <c r="I31" s="83" t="s">
+        <v>230</v>
+      </c>
+      <c r="J31" s="95">
         <v>3012605559</v>
       </c>
-      <c r="K31" s="96" t="s">
-        <v>313</v>
+      <c r="K31" s="94" t="s">
+        <v>227</v>
       </c>
       <c r="L31" s="59"/>
       <c r="M31" s="59"/>
@@ -43168,37 +43384,37 @@
       <c r="Z31" s="59"/>
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A32" s="77">
+      <c r="A32" s="75">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B32" s="79" t="s">
-        <v>201</v>
-      </c>
-      <c r="C32" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D32" s="85">
+      <c r="B32" s="77" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="83">
         <v>1085186179</v>
       </c>
-      <c r="E32" s="88"/>
-      <c r="F32" s="95" t="s">
-        <v>238</v>
-      </c>
-      <c r="G32" s="97">
+      <c r="E32" s="86"/>
+      <c r="F32" s="93" t="s">
+        <v>152</v>
+      </c>
+      <c r="G32" s="95">
         <v>3106455950</v>
       </c>
-      <c r="H32" s="85" t="s">
-        <v>319</v>
-      </c>
-      <c r="I32" s="85" t="s">
-        <v>320</v>
-      </c>
-      <c r="J32" s="97" t="s">
-        <v>317</v>
-      </c>
-      <c r="K32" s="96" t="s">
-        <v>318</v>
+      <c r="H32" s="83" t="s">
+        <v>233</v>
+      </c>
+      <c r="I32" s="83" t="s">
+        <v>234</v>
+      </c>
+      <c r="J32" s="95" t="s">
+        <v>231</v>
+      </c>
+      <c r="K32" s="94" t="s">
+        <v>232</v>
       </c>
       <c r="L32" s="59"/>
       <c r="M32" s="59"/>
@@ -43217,37 +43433,37 @@
       <c r="Z32" s="59"/>
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A33" s="77">
+      <c r="A33" s="75">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B33" s="79" t="s">
-        <v>202</v>
-      </c>
-      <c r="C33" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D33" s="85">
+      <c r="B33" s="77" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" s="83">
         <v>1019903589</v>
       </c>
-      <c r="E33" s="89"/>
-      <c r="F33" s="94" t="s">
-        <v>239</v>
-      </c>
-      <c r="G33" s="97">
+      <c r="E33" s="87"/>
+      <c r="F33" s="100" t="s">
+        <v>153</v>
+      </c>
+      <c r="G33" s="95">
         <v>3118613964</v>
       </c>
-      <c r="H33" s="85" t="s">
-        <v>323</v>
-      </c>
-      <c r="I33" s="85" t="s">
-        <v>324</v>
-      </c>
-      <c r="J33" s="97" t="s">
-        <v>321</v>
-      </c>
-      <c r="K33" s="96" t="s">
-        <v>322</v>
+      <c r="H33" s="83" t="s">
+        <v>237</v>
+      </c>
+      <c r="I33" s="83" t="s">
+        <v>238</v>
+      </c>
+      <c r="J33" s="95" t="s">
+        <v>235</v>
+      </c>
+      <c r="K33" s="94" t="s">
+        <v>236</v>
       </c>
       <c r="L33" s="48"/>
       <c r="M33" s="48"/>
@@ -43266,37 +43482,37 @@
       <c r="Z33" s="48"/>
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A34" s="77">
+      <c r="A34" s="75">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B34" s="79" t="s">
-        <v>203</v>
-      </c>
-      <c r="C34" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D34" s="85">
+      <c r="B34" s="77" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="83">
         <v>1011205655</v>
       </c>
-      <c r="E34" s="89"/>
-      <c r="F34" s="95" t="s">
+      <c r="E34" s="87"/>
+      <c r="F34" s="98" t="s">
+        <v>154</v>
+      </c>
+      <c r="G34" s="95">
+        <v>3202642900</v>
+      </c>
+      <c r="H34" s="83" t="s">
         <v>240</v>
       </c>
-      <c r="G34" s="97">
-        <v>3202642900</v>
-      </c>
-      <c r="H34" s="85" t="s">
-        <v>326</v>
-      </c>
-      <c r="I34" s="85" t="s">
-        <v>327</v>
-      </c>
-      <c r="J34" s="97">
+      <c r="I34" s="83" t="s">
+        <v>241</v>
+      </c>
+      <c r="J34" s="95">
         <v>3142328792</v>
       </c>
-      <c r="K34" s="96" t="s">
-        <v>325</v>
+      <c r="K34" s="94" t="s">
+        <v>239</v>
       </c>
       <c r="L34" s="48"/>
       <c r="M34" s="48"/>
@@ -43315,37 +43531,37 @@
       <c r="Z34" s="48"/>
     </row>
     <row r="35" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A35" s="77">
+      <c r="A35" s="75">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B35" s="79" t="s">
-        <v>204</v>
-      </c>
-      <c r="C35" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D35" s="85">
+      <c r="B35" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" s="83">
         <v>1021399838</v>
       </c>
-      <c r="E35" s="88"/>
-      <c r="F35" s="94" t="s">
-        <v>241</v>
-      </c>
-      <c r="G35" s="97" t="s">
-        <v>329</v>
-      </c>
-      <c r="H35" s="85" t="s">
-        <v>330</v>
-      </c>
-      <c r="I35" s="85" t="s">
-        <v>331</v>
-      </c>
-      <c r="J35" s="85">
+      <c r="E35" s="86"/>
+      <c r="F35" s="100" t="s">
+        <v>155</v>
+      </c>
+      <c r="G35" s="95" t="s">
+        <v>243</v>
+      </c>
+      <c r="H35" s="83" t="s">
+        <v>244</v>
+      </c>
+      <c r="I35" s="83" t="s">
+        <v>245</v>
+      </c>
+      <c r="J35" s="83">
         <v>3108402758</v>
       </c>
-      <c r="K35" s="96" t="s">
-        <v>328</v>
+      <c r="K35" s="94" t="s">
+        <v>242</v>
       </c>
       <c r="L35" s="48"/>
       <c r="M35" s="48"/>
@@ -43364,37 +43580,37 @@
       <c r="Z35" s="48"/>
     </row>
     <row r="36" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A36" s="77">
+      <c r="A36" s="75">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B36" s="79" t="s">
-        <v>205</v>
-      </c>
-      <c r="C36" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D36" s="85">
+      <c r="B36" s="77" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D36" s="83">
         <v>1145225413</v>
       </c>
-      <c r="E36" s="89"/>
-      <c r="F36" s="95" t="s">
-        <v>242</v>
-      </c>
-      <c r="G36" s="97">
+      <c r="E36" s="87"/>
+      <c r="F36" s="98" t="s">
+        <v>156</v>
+      </c>
+      <c r="G36" s="95">
         <v>3222881325</v>
       </c>
-      <c r="H36" s="85" t="s">
-        <v>334</v>
-      </c>
-      <c r="I36" s="85" t="s">
-        <v>335</v>
-      </c>
-      <c r="J36" s="97" t="s">
-        <v>332</v>
-      </c>
-      <c r="K36" s="96" t="s">
-        <v>333</v>
+      <c r="H36" s="83" t="s">
+        <v>248</v>
+      </c>
+      <c r="I36" s="83" t="s">
+        <v>249</v>
+      </c>
+      <c r="J36" s="95" t="s">
+        <v>246</v>
+      </c>
+      <c r="K36" s="94" t="s">
+        <v>247</v>
       </c>
       <c r="L36" s="48"/>
       <c r="M36" s="48"/>
@@ -43413,37 +43629,37 @@
       <c r="Z36" s="48"/>
     </row>
     <row r="37" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A37" s="77">
+      <c r="A37" s="75">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B37" s="79" t="s">
-        <v>206</v>
-      </c>
-      <c r="C37" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D37" s="85">
+      <c r="B37" s="77" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" s="83">
         <v>1141124373</v>
       </c>
-      <c r="E37" s="89"/>
-      <c r="F37" s="94" t="s">
-        <v>243</v>
-      </c>
-      <c r="G37" s="97">
+      <c r="E37" s="87"/>
+      <c r="F37" s="100" t="s">
+        <v>157</v>
+      </c>
+      <c r="G37" s="95">
         <v>3150643029</v>
       </c>
-      <c r="H37" s="85" t="s">
-        <v>337</v>
-      </c>
-      <c r="I37" s="85" t="s">
-        <v>338</v>
-      </c>
-      <c r="J37" s="85">
+      <c r="H37" s="83" t="s">
+        <v>251</v>
+      </c>
+      <c r="I37" s="83" t="s">
+        <v>252</v>
+      </c>
+      <c r="J37" s="83">
         <v>3145102047</v>
       </c>
-      <c r="K37" s="96" t="s">
-        <v>336</v>
+      <c r="K37" s="94" t="s">
+        <v>250</v>
       </c>
       <c r="L37" s="48"/>
       <c r="M37" s="48"/>
@@ -43462,37 +43678,37 @@
       <c r="Z37" s="48"/>
     </row>
     <row r="38" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A38" s="77">
+      <c r="A38" s="75">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B38" s="79" t="s">
-        <v>207</v>
-      </c>
-      <c r="C38" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D38" s="85">
+      <c r="B38" s="77" t="s">
+        <v>121</v>
+      </c>
+      <c r="C38" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D38" s="83">
         <v>1014238934</v>
       </c>
-      <c r="E38" s="89"/>
-      <c r="F38" s="95" t="s">
-        <v>244</v>
-      </c>
-      <c r="G38" s="97">
+      <c r="E38" s="87"/>
+      <c r="F38" s="98" t="s">
+        <v>158</v>
+      </c>
+      <c r="G38" s="95">
         <v>3223228166</v>
       </c>
-      <c r="H38" s="85" t="s">
-        <v>340</v>
-      </c>
-      <c r="I38" s="85" t="s">
-        <v>341</v>
-      </c>
-      <c r="J38" s="85">
+      <c r="H38" s="83" t="s">
+        <v>254</v>
+      </c>
+      <c r="I38" s="83" t="s">
+        <v>255</v>
+      </c>
+      <c r="J38" s="83">
         <v>3192221388</v>
       </c>
-      <c r="K38" s="96" t="s">
-        <v>339</v>
+      <c r="K38" s="94" t="s">
+        <v>253</v>
       </c>
       <c r="L38" s="48"/>
       <c r="M38" s="48"/>
@@ -43511,37 +43727,37 @@
       <c r="Z38" s="48"/>
     </row>
     <row r="39" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A39" s="77">
+      <c r="A39" s="75">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B39" s="79" t="s">
-        <v>208</v>
-      </c>
-      <c r="C39" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D39" s="85">
+      <c r="B39" s="77" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D39" s="83">
         <v>1028721344</v>
       </c>
-      <c r="E39" s="88"/>
-      <c r="F39" s="94" t="s">
-        <v>245</v>
-      </c>
-      <c r="G39" s="97">
+      <c r="E39" s="86"/>
+      <c r="F39" s="100" t="s">
+        <v>159</v>
+      </c>
+      <c r="G39" s="95">
         <v>3042704740</v>
       </c>
-      <c r="H39" s="85" t="s">
-        <v>343</v>
-      </c>
-      <c r="I39" s="85" t="s">
-        <v>344</v>
-      </c>
-      <c r="J39" s="85">
+      <c r="H39" s="83" t="s">
+        <v>257</v>
+      </c>
+      <c r="I39" s="83" t="s">
+        <v>258</v>
+      </c>
+      <c r="J39" s="83">
         <v>3214822051</v>
       </c>
-      <c r="K39" s="96" t="s">
-        <v>342</v>
+      <c r="K39" s="94" t="s">
+        <v>256</v>
       </c>
       <c r="L39" s="48"/>
       <c r="M39" s="48"/>
@@ -43560,37 +43776,37 @@
       <c r="Z39" s="48"/>
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A40" s="77">
+      <c r="A40" s="75">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B40" s="79" t="s">
-        <v>209</v>
-      </c>
-      <c r="C40" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D40" s="85">
+      <c r="B40" s="77" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D40" s="83">
         <v>1141717444</v>
       </c>
-      <c r="E40" s="88"/>
-      <c r="F40" s="95" t="s">
-        <v>246</v>
-      </c>
-      <c r="G40" s="97">
+      <c r="E40" s="86"/>
+      <c r="F40" s="98" t="s">
+        <v>160</v>
+      </c>
+      <c r="G40" s="95">
         <v>3150753380</v>
       </c>
-      <c r="H40" s="85" t="s">
-        <v>347</v>
-      </c>
-      <c r="I40" s="85" t="s">
-        <v>348</v>
-      </c>
-      <c r="J40" s="97" t="s">
-        <v>345</v>
-      </c>
-      <c r="K40" s="96" t="s">
-        <v>346</v>
+      <c r="H40" s="83" t="s">
+        <v>261</v>
+      </c>
+      <c r="I40" s="83" t="s">
+        <v>262</v>
+      </c>
+      <c r="J40" s="95" t="s">
+        <v>259</v>
+      </c>
+      <c r="K40" s="97" t="s">
+        <v>260</v>
       </c>
       <c r="L40" s="48"/>
       <c r="M40" s="48"/>
@@ -43609,36 +43825,36 @@
       <c r="Z40" s="48"/>
     </row>
     <row r="41" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A41" s="77">
+      <c r="A41" s="75">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B41" s="79" t="s">
-        <v>210</v>
-      </c>
-      <c r="C41" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D41" s="85">
+      <c r="B41" s="77" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" s="83">
         <v>1141717746</v>
       </c>
-      <c r="E41" s="88"/>
-      <c r="F41" s="94" t="s">
-        <v>247</v>
-      </c>
-      <c r="G41" s="97" t="s">
-        <v>349</v>
-      </c>
-      <c r="H41" s="85" t="s">
-        <v>350</v>
-      </c>
-      <c r="I41" s="85" t="s">
-        <v>351</v>
-      </c>
-      <c r="J41" s="85">
+      <c r="E41" s="86"/>
+      <c r="F41" s="100" t="s">
+        <v>161</v>
+      </c>
+      <c r="G41" s="95" t="s">
+        <v>263</v>
+      </c>
+      <c r="H41" s="83" t="s">
+        <v>264</v>
+      </c>
+      <c r="I41" s="83" t="s">
+        <v>265</v>
+      </c>
+      <c r="J41" s="83">
         <v>3168174774</v>
       </c>
-      <c r="K41" s="85"/>
+      <c r="K41" s="83"/>
       <c r="L41" s="48"/>
       <c r="M41" s="48"/>
       <c r="N41" s="48"/>
@@ -43656,37 +43872,37 @@
       <c r="Z41" s="48"/>
     </row>
     <row r="42" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A42" s="77">
+      <c r="A42" s="75">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B42" s="81" t="s">
-        <v>211</v>
-      </c>
-      <c r="C42" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D42" s="85">
+      <c r="B42" s="79" t="s">
+        <v>125</v>
+      </c>
+      <c r="C42" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" s="83">
         <v>114171974</v>
       </c>
-      <c r="E42" s="91"/>
-      <c r="F42" s="95" t="s">
-        <v>248</v>
-      </c>
-      <c r="G42" s="97">
+      <c r="E42" s="89"/>
+      <c r="F42" s="98" t="s">
+        <v>162</v>
+      </c>
+      <c r="G42" s="95">
         <v>3025489889</v>
       </c>
-      <c r="H42" s="85" t="s">
-        <v>353</v>
-      </c>
-      <c r="I42" s="85" t="s">
-        <v>354</v>
-      </c>
-      <c r="J42" s="85">
+      <c r="H42" s="83" t="s">
+        <v>267</v>
+      </c>
+      <c r="I42" s="83" t="s">
+        <v>268</v>
+      </c>
+      <c r="J42" s="83">
         <v>3209104377</v>
       </c>
-      <c r="K42" s="96" t="s">
-        <v>352</v>
+      <c r="K42" s="94" t="s">
+        <v>266</v>
       </c>
       <c r="L42" s="48"/>
       <c r="M42" s="48"/>
@@ -43705,37 +43921,37 @@
       <c r="Z42" s="48"/>
     </row>
     <row r="43" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A43" s="78">
+      <c r="A43" s="76">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B43" s="79" t="s">
-        <v>212</v>
-      </c>
-      <c r="C43" s="86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D43" s="85">
+      <c r="B43" s="77" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" s="84" t="s">
+        <v>128</v>
+      </c>
+      <c r="D43" s="83">
         <v>1031655444</v>
       </c>
-      <c r="E43" s="92"/>
-      <c r="F43" s="94" t="s">
-        <v>249</v>
-      </c>
-      <c r="G43" s="97">
+      <c r="E43" s="90"/>
+      <c r="F43" s="100" t="s">
+        <v>163</v>
+      </c>
+      <c r="G43" s="95">
         <v>3027002402</v>
       </c>
-      <c r="H43" s="85" t="s">
-        <v>356</v>
-      </c>
-      <c r="I43" s="85" t="s">
-        <v>357</v>
-      </c>
-      <c r="J43" s="85">
+      <c r="H43" s="83" t="s">
+        <v>270</v>
+      </c>
+      <c r="I43" s="83" t="s">
+        <v>271</v>
+      </c>
+      <c r="J43" s="83">
         <v>3152205485</v>
       </c>
-      <c r="K43" s="96" t="s">
-        <v>355</v>
+      <c r="K43" s="94" t="s">
+        <v>269</v>
       </c>
       <c r="L43" s="48"/>
       <c r="M43" s="48"/>
@@ -43754,37 +43970,37 @@
       <c r="Z43" s="48"/>
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A44" s="82">
+      <c r="A44" s="80">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B44" s="79" t="s">
-        <v>213</v>
-      </c>
-      <c r="C44" s="86" t="s">
-        <v>215</v>
-      </c>
-      <c r="D44" s="85">
+      <c r="B44" s="77" t="s">
+        <v>127</v>
+      </c>
+      <c r="C44" s="84" t="s">
+        <v>129</v>
+      </c>
+      <c r="D44" s="83">
         <v>8119747</v>
       </c>
-      <c r="E44" s="92"/>
-      <c r="F44" s="95" t="s">
-        <v>250</v>
-      </c>
-      <c r="G44" s="97">
+      <c r="E44" s="90"/>
+      <c r="F44" s="98" t="s">
+        <v>164</v>
+      </c>
+      <c r="G44" s="95">
         <v>3508601736</v>
       </c>
-      <c r="H44" s="85" t="s">
-        <v>359</v>
-      </c>
-      <c r="I44" s="85" t="s">
-        <v>360</v>
-      </c>
-      <c r="J44" s="85">
+      <c r="H44" s="83" t="s">
+        <v>273</v>
+      </c>
+      <c r="I44" s="83" t="s">
+        <v>274</v>
+      </c>
+      <c r="J44" s="83">
         <v>3503277420</v>
       </c>
-      <c r="K44" s="96" t="s">
-        <v>358</v>
+      <c r="K44" s="94" t="s">
+        <v>272</v>
       </c>
       <c r="L44" s="48"/>
       <c r="M44" s="48"/>
@@ -43803,15 +44019,15 @@
       <c r="Z44" s="48"/>
     </row>
     <row r="45" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A45" s="82">
+      <c r="A45" s="80">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="J45" s="85">
+      <c r="J45" s="83">
         <v>3506648473</v>
       </c>
-      <c r="K45" s="191" t="s">
-        <v>361</v>
+      <c r="K45" s="96" t="s">
+        <v>275</v>
       </c>
       <c r="L45" s="48"/>
       <c r="M45" s="48"/>
@@ -43830,19 +44046,19 @@
       <c r="Z45" s="48"/>
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A46" s="83">
+      <c r="A46" s="81">
         <v>37</v>
       </c>
-      <c r="B46" s="80"/>
-      <c r="C46" s="84"/>
-      <c r="D46" s="80"/>
-      <c r="E46" s="80"/>
-      <c r="F46" s="93"/>
-      <c r="G46" s="80"/>
-      <c r="H46" s="80"/>
-      <c r="I46" s="80"/>
-      <c r="J46" s="80"/>
-      <c r="K46" s="80"/>
+      <c r="B46" s="78"/>
+      <c r="C46" s="82"/>
+      <c r="D46" s="78"/>
+      <c r="E46" s="78"/>
+      <c r="F46" s="91"/>
+      <c r="G46" s="78"/>
+      <c r="H46" s="78"/>
+      <c r="I46" s="78"/>
+      <c r="J46" s="78"/>
+      <c r="K46" s="78"/>
       <c r="L46" s="61"/>
       <c r="M46" s="61"/>
       <c r="N46" s="61"/>
@@ -43860,19 +44076,19 @@
       <c r="Z46" s="61"/>
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A47" s="83">
+      <c r="A47" s="81">
         <v>38</v>
       </c>
-      <c r="B47" s="80"/>
-      <c r="C47" s="84"/>
-      <c r="D47" s="80"/>
-      <c r="E47" s="80"/>
-      <c r="F47" s="80"/>
-      <c r="G47" s="80"/>
-      <c r="H47" s="80"/>
-      <c r="I47" s="80"/>
-      <c r="J47" s="80"/>
-      <c r="K47" s="80"/>
+      <c r="B47" s="78"/>
+      <c r="C47" s="82"/>
+      <c r="D47" s="78"/>
+      <c r="E47" s="78"/>
+      <c r="F47" s="78"/>
+      <c r="G47" s="78"/>
+      <c r="H47" s="78"/>
+      <c r="I47" s="78"/>
+      <c r="J47" s="78"/>
+      <c r="K47" s="78"/>
       <c r="L47" s="48"/>
       <c r="M47" s="48"/>
       <c r="N47" s="48"/>
@@ -43890,19 +44106,19 @@
       <c r="Z47" s="48"/>
     </row>
     <row r="48" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A48" s="83">
+      <c r="A48" s="81">
         <v>39</v>
       </c>
-      <c r="B48" s="80"/>
-      <c r="C48" s="84"/>
-      <c r="D48" s="80"/>
-      <c r="E48" s="80"/>
-      <c r="F48" s="80"/>
-      <c r="G48" s="80"/>
-      <c r="H48" s="80"/>
-      <c r="I48" s="80"/>
-      <c r="J48" s="80"/>
-      <c r="K48" s="80"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="82"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="78"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="78"/>
+      <c r="I48" s="78"/>
+      <c r="J48" s="78"/>
+      <c r="K48" s="78"/>
       <c r="L48" s="48"/>
       <c r="M48" s="48"/>
       <c r="N48" s="48"/>
@@ -43920,19 +44136,19 @@
       <c r="Z48" s="48"/>
     </row>
     <row r="49" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A49" s="83">
+      <c r="A49" s="81">
         <v>40</v>
       </c>
-      <c r="B49" s="80"/>
-      <c r="C49" s="84"/>
-      <c r="D49" s="80"/>
-      <c r="E49" s="80"/>
-      <c r="F49" s="80"/>
-      <c r="G49" s="80"/>
-      <c r="H49" s="80"/>
-      <c r="I49" s="80"/>
-      <c r="J49" s="80"/>
-      <c r="K49" s="80"/>
+      <c r="B49" s="78"/>
+      <c r="C49" s="82"/>
+      <c r="D49" s="78"/>
+      <c r="E49" s="78"/>
+      <c r="F49" s="78"/>
+      <c r="G49" s="78"/>
+      <c r="H49" s="78"/>
+      <c r="I49" s="78"/>
+      <c r="J49" s="78"/>
+      <c r="K49" s="78"/>
       <c r="L49" s="48"/>
       <c r="M49" s="48"/>
       <c r="N49" s="48"/>
@@ -43950,21 +44166,21 @@
       <c r="Z49" s="48"/>
     </row>
     <row r="50" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A50" s="83">
+      <c r="A50" s="81">
         <v>41</v>
       </c>
-      <c r="B50" s="80"/>
-      <c r="C50" s="84"/>
-      <c r="D50" s="80"/>
-      <c r="E50" s="80"/>
-      <c r="F50" s="80" t="s">
-        <v>102</v>
-      </c>
-      <c r="G50" s="80"/>
-      <c r="H50" s="80"/>
-      <c r="I50" s="80"/>
-      <c r="J50" s="80"/>
-      <c r="K50" s="80"/>
+      <c r="B50" s="78"/>
+      <c r="C50" s="82"/>
+      <c r="D50" s="78"/>
+      <c r="E50" s="78"/>
+      <c r="F50" s="78" t="s">
+        <v>80</v>
+      </c>
+      <c r="G50" s="78"/>
+      <c r="H50" s="78"/>
+      <c r="I50" s="78"/>
+      <c r="J50" s="78"/>
+      <c r="K50" s="78"/>
       <c r="L50" s="48"/>
       <c r="M50" s="48"/>
       <c r="N50" s="48"/>
@@ -43982,19 +44198,19 @@
       <c r="Z50" s="48"/>
     </row>
     <row r="51" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A51" s="83">
+      <c r="A51" s="81">
         <v>42</v>
       </c>
-      <c r="B51" s="80"/>
-      <c r="C51" s="84"/>
-      <c r="D51" s="80"/>
-      <c r="E51" s="80"/>
-      <c r="F51" s="80"/>
-      <c r="G51" s="80"/>
-      <c r="H51" s="80"/>
-      <c r="I51" s="80"/>
-      <c r="J51" s="80"/>
-      <c r="K51" s="80"/>
+      <c r="B51" s="78"/>
+      <c r="C51" s="82"/>
+      <c r="D51" s="78"/>
+      <c r="E51" s="78"/>
+      <c r="F51" s="78"/>
+      <c r="G51" s="78"/>
+      <c r="H51" s="78"/>
+      <c r="I51" s="78"/>
+      <c r="J51" s="78"/>
+      <c r="K51" s="78"/>
       <c r="L51" s="48"/>
       <c r="M51" s="48"/>
       <c r="N51" s="48"/>
@@ -52593,12 +52809,46 @@
     <hyperlink ref="K43" r:id="rId33" xr:uid="{2B54C594-10D1-4D11-8811-CB5AEEB8A56B}"/>
     <hyperlink ref="K44" r:id="rId34" xr:uid="{72B58B83-3316-4EA5-BC43-41CEA99943E3}"/>
     <hyperlink ref="K45" r:id="rId35" xr:uid="{71C46DDC-792D-4564-98D6-FF8183321EC1}"/>
+    <hyperlink ref="F10" r:id="rId36" xr:uid="{06195F10-28B0-4654-BDC9-276B90A09041}"/>
+    <hyperlink ref="F14" r:id="rId37" xr:uid="{CBAD4172-1480-4E8A-8C81-B0DF3F77D7A2}"/>
+    <hyperlink ref="F25" r:id="rId38" xr:uid="{0AEB298D-F5FC-4C01-982F-EA56A8093A10}"/>
+    <hyperlink ref="F20" r:id="rId39" xr:uid="{464F8F04-0EB5-43AC-9670-850EEDFF1EC2}"/>
+    <hyperlink ref="F36" r:id="rId40" xr:uid="{484F7A66-268D-4180-8AA3-15C175A100A0}"/>
+    <hyperlink ref="F12" r:id="rId41" xr:uid="{762E7B6D-721D-4CB9-A139-3A21D0D2F650}"/>
+    <hyperlink ref="F26" r:id="rId42" xr:uid="{065D685E-D83E-4CC0-BC7F-37B15812A9A2}"/>
+    <hyperlink ref="F27" r:id="rId43" xr:uid="{73E20E56-6016-44AC-91A1-F2CF62E3F4EE}"/>
+    <hyperlink ref="F40" r:id="rId44" xr:uid="{A2EA4D74-0B29-4FFF-8BC3-3E9D25011FF0}"/>
+    <hyperlink ref="F35" r:id="rId45" xr:uid="{24E28F3A-9274-415B-B11D-26E330EF3361}"/>
+    <hyperlink ref="F11" r:id="rId46" xr:uid="{2D53C129-9206-444C-B349-E42A121EB717}"/>
+    <hyperlink ref="F18" r:id="rId47" xr:uid="{B28AB0EE-3129-4220-A976-E5D1C961809D}"/>
+    <hyperlink ref="F33" r:id="rId48" xr:uid="{8F599942-FD0E-41EC-B2BE-4736D50881C4}"/>
+    <hyperlink ref="F17" r:id="rId49" xr:uid="{FA867DBF-8590-4B06-BD80-F011D8BC8199}"/>
+    <hyperlink ref="F41" r:id="rId50" xr:uid="{21E788F2-F2C8-4119-85AE-BB5867E89563}"/>
+    <hyperlink ref="F13" r:id="rId51" xr:uid="{EB8D46B1-0A75-4BE2-BFCF-54FD8EEC35BC}"/>
+    <hyperlink ref="F22" r:id="rId52" xr:uid="{6BCE0850-51AD-44E8-A613-565D242E0123}"/>
+    <hyperlink ref="F24" r:id="rId53" xr:uid="{02D4E4BE-1C77-43A1-81FD-06E357E515D1}"/>
+    <hyperlink ref="F30" r:id="rId54" xr:uid="{3286FD17-354E-4DB5-B6C7-E47266BDE3C6}"/>
+    <hyperlink ref="F15" r:id="rId55" xr:uid="{EB3E4174-9BCA-4CCD-8680-EC6D2FC50048}"/>
+    <hyperlink ref="F44" r:id="rId56" xr:uid="{5C7F701B-91A3-4A0C-BC33-BD0E52170A58}"/>
+    <hyperlink ref="F43" r:id="rId57" xr:uid="{AC3B37CB-B8B2-4820-A929-EE41311EB425}"/>
+    <hyperlink ref="F21" r:id="rId58" xr:uid="{9086B549-7257-45EA-877F-D1CE6D223B1D}"/>
+    <hyperlink ref="F16" r:id="rId59" xr:uid="{A6F46DB5-A361-4692-B251-4046168AFF4A}"/>
+    <hyperlink ref="F37" r:id="rId60" xr:uid="{5405AEED-5704-4664-9F39-8B0B97B5EEBA}"/>
+    <hyperlink ref="F23" r:id="rId61" xr:uid="{4F6930E6-4EFF-4736-AC46-1620BA8F1068}"/>
+    <hyperlink ref="F42" r:id="rId62" xr:uid="{2425373E-28BF-481B-9E8B-591859734267}"/>
+    <hyperlink ref="F19" r:id="rId63" xr:uid="{462B358E-7B49-471E-996C-65655AF21B87}"/>
+    <hyperlink ref="F34" r:id="rId64" xr:uid="{69150A4C-D73B-426C-8552-889231ADA844}"/>
+    <hyperlink ref="F38" r:id="rId65" xr:uid="{6864798C-E7F3-4000-B80E-38C7C2D7C6FB}"/>
+    <hyperlink ref="F29" r:id="rId66" xr:uid="{B45A4EFB-C5CE-4382-90CA-B68EA7DB6A67}"/>
+    <hyperlink ref="F28" r:id="rId67" xr:uid="{F93A3CB2-FAFD-4156-BEE9-90884652E95C}"/>
+    <hyperlink ref="F39" r:id="rId68" xr:uid="{877453C2-3D24-48C8-9978-C1EF10847AEE}"/>
+    <hyperlink ref="K10" r:id="rId69" xr:uid="{EEB931DE-1060-4127-8B07-76840ED456D1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId36"/>
-  <legacyDrawing r:id="rId37"/>
+  <pageSetup orientation="landscape" r:id="rId70"/>
+  <legacyDrawing r:id="rId71"/>
   <tableParts count="1">
-    <tablePart r:id="rId38"/>
+    <tablePart r:id="rId72"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -52621,7 +52871,7 @@
     <tabColor rgb="FF00B050"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="27.125" customWidth="1"/>
@@ -52630,474 +52880,606 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1">
-      <c r="A1" s="190" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
+      <c r="A1" s="206" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="174"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
       <c r="E1" s="62"/>
       <c r="F1" s="62"/>
     </row>
     <row r="2" spans="1:6" ht="15.75">
       <c r="A2" s="63" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="B2" s="64" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D2" s="65" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75">
-      <c r="A3" s="187" t="s">
-        <v>108</v>
+      <c r="A3" s="200" t="s">
+        <v>86</v>
       </c>
       <c r="B3" s="66" t="s">
-        <v>109</v>
+        <v>281</v>
       </c>
       <c r="C3" s="66" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="67" t="s">
-        <v>98</v>
+        <v>282</v>
+      </c>
+      <c r="D3" s="99" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15.75">
-      <c r="A4" s="188"/>
+      <c r="A4" s="201"/>
       <c r="B4" s="66" t="s">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="C4" s="66" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="67" t="s">
-        <v>86</v>
+        <v>284</v>
+      </c>
+      <c r="D4" s="99" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15.75">
-      <c r="A5" s="188"/>
+      <c r="A5" s="201"/>
       <c r="B5" s="66" t="s">
-        <v>113</v>
+        <v>285</v>
       </c>
       <c r="C5" s="66" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="67" t="s">
-        <v>89</v>
+        <v>286</v>
+      </c>
+      <c r="D5" s="99" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75">
-      <c r="A6" s="188"/>
+      <c r="A6" s="201"/>
       <c r="B6" s="66" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="C6" s="66" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="67" t="s">
-        <v>117</v>
+        <v>288</v>
+      </c>
+      <c r="D6" s="99" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75">
-      <c r="A7" s="189"/>
-      <c r="B7" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="69" t="s">
-        <v>120</v>
+      <c r="A7" s="202"/>
+      <c r="B7" s="67" t="s">
+        <v>289</v>
+      </c>
+      <c r="C7" s="67" t="s">
+        <v>290</v>
+      </c>
+      <c r="D7" s="101" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75">
-      <c r="B8" s="70"/>
+      <c r="B8" s="68"/>
     </row>
     <row r="9" spans="1:6" ht="15.75">
       <c r="A9" s="63" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D9" s="65" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75">
-      <c r="A10" s="187" t="s">
-        <v>108</v>
+      <c r="A10" s="200" t="s">
+        <v>86</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>122</v>
+        <v>291</v>
       </c>
       <c r="C10" s="66" t="s">
-        <v>123</v>
-      </c>
-      <c r="D10" s="67" t="s">
-        <v>87</v>
+        <v>292</v>
+      </c>
+      <c r="D10" s="99" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75">
-      <c r="A11" s="188"/>
+      <c r="A11" s="201"/>
       <c r="B11" s="66" t="s">
-        <v>124</v>
+        <v>294</v>
       </c>
       <c r="C11" s="66" t="s">
-        <v>125</v>
-      </c>
-      <c r="D11" s="67" t="s">
-        <v>101</v>
+        <v>295</v>
+      </c>
+      <c r="D11" s="99" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75">
-      <c r="A12" s="188"/>
+      <c r="A12" s="201"/>
       <c r="B12" s="66" t="s">
-        <v>126</v>
+        <v>296</v>
       </c>
       <c r="C12" s="66" t="s">
-        <v>127</v>
-      </c>
-      <c r="D12" s="67" t="s">
-        <v>83</v>
+        <v>297</v>
+      </c>
+      <c r="D12" s="99" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75">
-      <c r="A13" s="188"/>
+      <c r="A13" s="201"/>
       <c r="B13" s="66" t="s">
-        <v>128</v>
+        <v>352</v>
       </c>
       <c r="C13" s="66" t="s">
-        <v>129</v>
-      </c>
-      <c r="D13" s="67" t="s">
-        <v>84</v>
+        <v>353</v>
+      </c>
+      <c r="D13" s="99" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75">
-      <c r="A14" s="189"/>
-      <c r="B14" s="68"/>
-      <c r="C14" s="68"/>
-      <c r="D14" s="69"/>
+      <c r="A14" s="202"/>
+      <c r="B14" s="67" t="s">
+        <v>300</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>301</v>
+      </c>
+      <c r="D14" s="101" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="15.75">
       <c r="A16" s="63" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D16" s="65" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75">
-      <c r="A17" s="187" t="s">
-        <v>108</v>
+      <c r="A17" s="200" t="s">
+        <v>86</v>
       </c>
       <c r="B17" s="66" t="s">
+        <v>302</v>
+      </c>
+      <c r="C17" s="66" t="s">
+        <v>303</v>
+      </c>
+      <c r="D17" s="99" t="s">
         <v>131</v>
       </c>
-      <c r="C17" s="66" t="s">
-        <v>132</v>
-      </c>
-      <c r="D17" s="67" t="s">
-        <v>90</v>
-      </c>
     </row>
     <row r="18" spans="1:4" ht="15.75">
-      <c r="A18" s="188"/>
-      <c r="B18" s="66" t="s">
-        <v>133</v>
+      <c r="A18" s="201"/>
+      <c r="B18" s="102" t="s">
+        <v>317</v>
       </c>
       <c r="C18" s="66" t="s">
-        <v>134</v>
-      </c>
-      <c r="D18" s="67" t="s">
-        <v>135</v>
+        <v>304</v>
+      </c>
+      <c r="D18" s="99" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75">
-      <c r="A19" s="188"/>
+      <c r="A19" s="201"/>
       <c r="B19" s="66" t="s">
-        <v>136</v>
+        <v>305</v>
       </c>
       <c r="C19" s="66" t="s">
+        <v>306</v>
+      </c>
+      <c r="D19" s="99" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75">
+      <c r="A20" s="201"/>
+      <c r="B20" s="66" t="s">
+        <v>307</v>
+      </c>
+      <c r="C20" s="66" t="s">
+        <v>308</v>
+      </c>
+      <c r="D20" s="99" t="s">
         <v>137</v>
       </c>
-      <c r="D19" s="67" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.75">
-      <c r="A20" s="188"/>
-      <c r="B20" s="66" t="s">
-        <v>138</v>
-      </c>
-      <c r="C20" s="66" t="s">
-        <v>139</v>
-      </c>
-      <c r="D20" s="67"/>
     </row>
     <row r="21" spans="1:4" ht="15.75">
-      <c r="A21" s="189"/>
-      <c r="B21" s="68" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" s="68" t="s">
-        <v>141</v>
-      </c>
-      <c r="D21" s="69" t="s">
-        <v>88</v>
-      </c>
+      <c r="A21" s="202"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="101"/>
     </row>
     <row r="23" spans="1:4" ht="15.75">
       <c r="A23" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="65" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75">
+      <c r="A24" s="200" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" s="66" t="s">
+        <v>311</v>
+      </c>
+      <c r="C24" s="66" t="s">
+        <v>312</v>
+      </c>
+      <c r="D24" s="99" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75">
+      <c r="A25" s="201"/>
+      <c r="B25" s="66" t="s">
+        <v>313</v>
+      </c>
+      <c r="C25" s="66" t="s">
+        <v>314</v>
+      </c>
+      <c r="D25" s="99" t="s">
         <v>142</v>
       </c>
-      <c r="B23" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="D23" s="65" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15.75">
-      <c r="A24" s="187" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="66" t="s">
+    </row>
+    <row r="26" spans="1:4" ht="15.75">
+      <c r="A26" s="201"/>
+      <c r="B26" s="66" t="s">
+        <v>315</v>
+      </c>
+      <c r="C26" s="66" t="s">
+        <v>316</v>
+      </c>
+      <c r="D26" s="99" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75">
+      <c r="A27" s="201"/>
+      <c r="B27" s="66" t="s">
+        <v>318</v>
+      </c>
+      <c r="C27" s="66" t="s">
+        <v>319</v>
+      </c>
+      <c r="D27" s="99" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75">
+      <c r="A28" s="202"/>
+      <c r="B28" s="67" t="s">
+        <v>309</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>310</v>
+      </c>
+      <c r="D28" s="101" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" thickBot="1"/>
+    <row r="30" spans="1:4" ht="15.75">
+      <c r="A30" s="104" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="105" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="105" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="106" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75">
+      <c r="A31" s="203" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="66" t="s">
+        <v>320</v>
+      </c>
+      <c r="C31" s="66" t="s">
+        <v>321</v>
+      </c>
+      <c r="D31" s="107" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75">
+      <c r="A32" s="204"/>
+      <c r="B32" s="66" t="s">
+        <v>322</v>
+      </c>
+      <c r="C32" s="66" t="s">
+        <v>323</v>
+      </c>
+      <c r="D32" s="107" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75">
+      <c r="A33" s="204"/>
+      <c r="B33" s="66" t="s">
+        <v>324</v>
+      </c>
+      <c r="C33" s="66" t="s">
+        <v>325</v>
+      </c>
+      <c r="D33" s="107" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75">
+      <c r="A34" s="204"/>
+      <c r="B34" s="66" t="s">
+        <v>326</v>
+      </c>
+      <c r="C34" s="66" t="s">
+        <v>327</v>
+      </c>
+      <c r="D34" s="107" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75">
+      <c r="A35" s="204"/>
+      <c r="B35" s="103" t="s">
+        <v>328</v>
+      </c>
+      <c r="C35" s="103" t="s">
+        <v>329</v>
+      </c>
+      <c r="D35" s="108" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="16.5" thickBot="1">
+      <c r="A36" s="205"/>
+      <c r="B36" s="109" t="s">
+        <v>330</v>
+      </c>
+      <c r="C36" s="109" t="s">
+        <v>331</v>
+      </c>
+      <c r="D36" s="110" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15" customHeight="1" thickBot="1"/>
+    <row r="38" spans="1:4" ht="15.75">
+      <c r="A38" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="D38" s="65" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75">
+      <c r="A39" s="200" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="66" t="s">
+        <v>333</v>
+      </c>
+      <c r="C39" s="66" t="s">
+        <v>334</v>
+      </c>
+      <c r="D39" s="99" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75">
+      <c r="A40" s="201"/>
+      <c r="B40" s="66" t="s">
+        <v>335</v>
+      </c>
+      <c r="C40" s="66" t="s">
+        <v>336</v>
+      </c>
+      <c r="D40" s="99" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.75">
+      <c r="A41" s="201"/>
+      <c r="B41" s="66" t="s">
+        <v>337</v>
+      </c>
+      <c r="C41" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="D41" s="99" t="s">
         <v>143</v>
       </c>
-      <c r="C24" s="66" t="s">
-        <v>144</v>
-      </c>
-      <c r="D24" s="67" t="s">
+    </row>
+    <row r="42" spans="1:4" ht="15.75">
+      <c r="A42" s="201"/>
+      <c r="B42" s="66" t="s">
+        <v>339</v>
+      </c>
+      <c r="C42" s="66" t="s">
+        <v>340</v>
+      </c>
+      <c r="D42" s="99" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.75">
+      <c r="A43" s="202"/>
+      <c r="B43" s="67" t="s">
+        <v>298</v>
+      </c>
+      <c r="C43" s="67" t="s">
+        <v>299</v>
+      </c>
+      <c r="D43" s="101" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" thickBot="1"/>
+    <row r="45" spans="1:4" ht="15" customHeight="1">
+      <c r="A45" s="63" t="s">
+        <v>332</v>
+      </c>
+      <c r="B45" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="D45" s="65" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.75">
-      <c r="A25" s="188"/>
-      <c r="B25" s="66" t="s">
-        <v>145</v>
-      </c>
-      <c r="C25" s="66" t="s">
-        <v>146</v>
-      </c>
-      <c r="D25" s="67" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15.75">
-      <c r="A26" s="188"/>
-      <c r="B26" s="66" t="s">
-        <v>148</v>
-      </c>
-      <c r="C26" s="66" t="s">
+    <row r="46" spans="1:4" ht="15" customHeight="1">
+      <c r="A46" s="200" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" s="66" t="s">
+        <v>341</v>
+      </c>
+      <c r="C46" s="66" t="s">
+        <v>342</v>
+      </c>
+      <c r="D46" s="99" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1">
+      <c r="A47" s="201"/>
+      <c r="B47" s="66" t="s">
+        <v>343</v>
+      </c>
+      <c r="C47" s="66" t="s">
+        <v>344</v>
+      </c>
+      <c r="D47" s="99" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1">
+      <c r="A48" s="201"/>
+      <c r="B48" s="66" t="s">
+        <v>345</v>
+      </c>
+      <c r="C48" s="66" t="s">
+        <v>346</v>
+      </c>
+      <c r="D48" s="99" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1">
+      <c r="A49" s="201"/>
+      <c r="B49" s="66" t="s">
+        <v>347</v>
+      </c>
+      <c r="C49" s="66" t="s">
+        <v>348</v>
+      </c>
+      <c r="D49" s="99" t="s">
         <v>149</v>
       </c>
-      <c r="D26" s="67" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.75">
-      <c r="A27" s="188"/>
-      <c r="B27" s="66" t="s">
-        <v>150</v>
-      </c>
-      <c r="C27" s="66" t="s">
-        <v>151</v>
-      </c>
-      <c r="D27" s="67" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.75">
-      <c r="A28" s="189"/>
-      <c r="B28" s="68" t="s">
-        <v>152</v>
-      </c>
-      <c r="C28" s="68" t="s">
-        <v>153</v>
-      </c>
-      <c r="D28" s="69" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15.75">
-      <c r="A30" s="63" t="s">
-        <v>154</v>
-      </c>
-      <c r="B30" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="D30" s="65" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15.75">
-      <c r="A31" s="187" t="s">
-        <v>108</v>
-      </c>
-      <c r="B31" s="66" t="s">
-        <v>155</v>
-      </c>
-      <c r="C31" s="66" t="s">
-        <v>156</v>
-      </c>
-      <c r="D31" s="67" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.75">
-      <c r="A32" s="188"/>
-      <c r="B32" s="66" t="s">
-        <v>158</v>
-      </c>
-      <c r="C32" s="66" t="s">
-        <v>159</v>
-      </c>
-      <c r="D32" s="67" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.75">
-      <c r="A33" s="188"/>
-      <c r="B33" s="66" t="s">
-        <v>160</v>
-      </c>
-      <c r="C33" s="66" t="s">
-        <v>161</v>
-      </c>
-      <c r="D33" s="67" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.75">
-      <c r="A34" s="188"/>
-      <c r="B34" s="66" t="s">
-        <v>163</v>
-      </c>
-      <c r="C34" s="66" t="s">
-        <v>164</v>
-      </c>
-      <c r="D34" s="67"/>
-    </row>
-    <row r="35" spans="1:4" ht="15.75">
-      <c r="A35" s="189"/>
-      <c r="B35" s="68" t="s">
-        <v>165</v>
-      </c>
-      <c r="C35" s="68" t="s">
-        <v>166</v>
-      </c>
-      <c r="D35" s="69" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.75">
-      <c r="A37" s="63" t="s">
-        <v>167</v>
-      </c>
-      <c r="B37" s="64" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" s="64" t="s">
-        <v>106</v>
-      </c>
-      <c r="D37" s="65" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.75">
-      <c r="A38" s="187" t="s">
-        <v>108</v>
-      </c>
-      <c r="B38" s="66" t="s">
-        <v>168</v>
-      </c>
-      <c r="C38" s="66" t="s">
-        <v>169</v>
-      </c>
-      <c r="D38" s="67" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="15.75">
-      <c r="A39" s="188"/>
-      <c r="B39" s="66" t="s">
-        <v>170</v>
-      </c>
-      <c r="C39" s="66" t="s">
-        <v>171</v>
-      </c>
-      <c r="D39" s="67" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15.75">
-      <c r="A40" s="188"/>
-      <c r="B40" s="66" t="s">
-        <v>172</v>
-      </c>
-      <c r="C40" s="66" t="s">
-        <v>173</v>
-      </c>
-      <c r="D40" s="67" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15.75">
-      <c r="A41" s="188"/>
-      <c r="B41" s="66" t="s">
-        <v>174</v>
-      </c>
-      <c r="C41" s="66" t="s">
-        <v>175</v>
-      </c>
-      <c r="D41" s="67" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15.75">
-      <c r="A42" s="189"/>
-      <c r="B42" s="68" t="s">
-        <v>170</v>
-      </c>
-      <c r="C42" s="68" t="s">
-        <v>176</v>
-      </c>
-      <c r="D42" s="69" t="s">
-        <v>81</v>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1" thickBot="1">
+      <c r="A50" s="202"/>
+      <c r="B50" s="67" t="s">
+        <v>349</v>
+      </c>
+      <c r="C50" s="67" t="s">
+        <v>350</v>
+      </c>
+      <c r="D50" s="101" t="s">
+        <v>351</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A31:A35"/>
-    <mergeCell ref="A38:A42"/>
+  <mergeCells count="8">
+    <mergeCell ref="A46:A50"/>
+    <mergeCell ref="A31:A36"/>
+    <mergeCell ref="A39:A43"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="A10:A14"/>
     <mergeCell ref="A17:A21"/>
     <mergeCell ref="A24:A28"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{49D6D5A6-591B-4A14-9E62-FD6834E43235}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{975BAF1C-6F9C-47ED-B8B3-8F08440A70F6}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{5676E464-F732-4320-99DC-98D3CF787FF0}"/>
+    <hyperlink ref="D6" r:id="rId4" xr:uid="{3955D51B-A3D7-4227-B2A6-8F2A1BAEE296}"/>
+    <hyperlink ref="D7" r:id="rId5" xr:uid="{E4AAF675-1DBF-4BBD-84FA-34F91EEE7F88}"/>
+    <hyperlink ref="D10" r:id="rId6" xr:uid="{09C17B6E-B0B1-4F47-AC43-70D4AD64D919}"/>
+    <hyperlink ref="D11" r:id="rId7" xr:uid="{D3EED372-7DA5-4726-B6CC-D9C46DB71DBA}"/>
+    <hyperlink ref="D12" r:id="rId8" xr:uid="{509D4ECA-A37A-41DF-BA97-1D086F0D508F}"/>
+    <hyperlink ref="D14" r:id="rId9" xr:uid="{AE554132-669E-4901-ACFB-45E511C7A0CC}"/>
+    <hyperlink ref="D17" r:id="rId10" xr:uid="{4038FFC4-31BD-406B-9253-31B1A0D114FD}"/>
+    <hyperlink ref="D18" r:id="rId11" xr:uid="{55C849A4-65F0-47D4-AAEA-01E2771D47D2}"/>
+    <hyperlink ref="D19" r:id="rId12" xr:uid="{AC11FFB5-944A-465E-8B76-464EB9205E2B}"/>
+    <hyperlink ref="D20" r:id="rId13" xr:uid="{F2183C6E-1165-4ED1-AC5E-2203BC69BAB4}"/>
+    <hyperlink ref="D24" r:id="rId14" xr:uid="{53CBB5A6-FBD9-42F6-9ACF-C5867ABAF431}"/>
+    <hyperlink ref="D25" r:id="rId15" xr:uid="{8AB0D75C-973F-4246-AB67-709C670115ED}"/>
+    <hyperlink ref="D26" r:id="rId16" xr:uid="{6F64CCA4-B2D5-4FC9-A996-CC6F664C1A1D}"/>
+    <hyperlink ref="D27" r:id="rId17" xr:uid="{D28BA087-C1CD-495E-8429-8CAD39483436}"/>
+    <hyperlink ref="D28" r:id="rId18" xr:uid="{E745CBF8-00A3-4120-88A2-4820F4E650E1}"/>
+    <hyperlink ref="D31" r:id="rId19" xr:uid="{CE567103-4FD8-41B5-BA08-880568F0A84C}"/>
+    <hyperlink ref="D32" r:id="rId20" xr:uid="{D7776E82-42E5-4D0B-A598-056AD593F9EE}"/>
+    <hyperlink ref="D33" r:id="rId21" xr:uid="{8D56464F-152E-4CF6-81B0-DE5557C62AC6}"/>
+    <hyperlink ref="D34" r:id="rId22" xr:uid="{B6D776EC-ACD7-4050-B1F1-7D2BF58FE5D5}"/>
+    <hyperlink ref="D39" r:id="rId23" xr:uid="{23C70EC7-62F1-4EF8-AF9A-D6BE8BFD8C33}"/>
+    <hyperlink ref="D40" r:id="rId24" xr:uid="{910EF204-F981-43D9-854A-7F82701C3594}"/>
+    <hyperlink ref="D41" r:id="rId25" xr:uid="{04A015A5-B215-4A16-842C-81C9315C988B}"/>
+    <hyperlink ref="D42" r:id="rId26" xr:uid="{673FB219-8BD7-4D77-904D-D4DC9B3910DA}"/>
+    <hyperlink ref="D43" r:id="rId27" xr:uid="{5576D482-4097-49DA-B303-1FA74448973A}"/>
+    <hyperlink ref="D46" r:id="rId28" xr:uid="{B659F67F-CC94-44F1-9F36-FAD15550D65C}"/>
+    <hyperlink ref="D47" r:id="rId29" xr:uid="{1BD56535-8BBA-439C-826A-2F115159499D}"/>
+    <hyperlink ref="D48" r:id="rId30" xr:uid="{CB4D6C9D-F441-4C66-98D9-37E9DD948ADC}"/>
+    <hyperlink ref="D49" r:id="rId31" xr:uid="{79EB01E4-D00F-4DC7-A25E-052513AF0407}"/>
+    <hyperlink ref="D50" r:id="rId32" xr:uid="{319FA363-6229-4EBA-A120-BE28F50EDB26}"/>
+    <hyperlink ref="D13" r:id="rId33" xr:uid="{46FB88AF-139D-41F0-8C10-7654E1EE7198}"/>
+  </hyperlinks>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId34"/>
 </worksheet>
 </file>